--- a/features/RC-001-red-score/docs/v2/test-spec/test-case-report.xlsx
+++ b/features/RC-001-red-score/docs/v2/test-spec/test-case-report.xlsx
@@ -2094,7 +2094,7 @@
     <row r="277">
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>3. Khi xét, `T` = kết quả dòng cuối (tính đúng ở case “Công thức hai dòng theo Figma: (A÷2)×0.8, xuống p1 ở dòng 2”).</t>
+          <t>3. Khi xét, `T` = kết quả dòng cuối (tính đúng ở case “Công thức hai dòng theo Figma: (A÷2)×0.8, dòng 1 làm tròn xuống”).</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
     <row r="325">
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh danh sách; ảnh kết quả trích xuất; SELECT `active` của quy tắc mới chỉ có điều kiện, chưa có ngưỡng (khi có schema; kỳ vọng `active=0` — thiết kế DB v2 mục 4.1 “Loại ngưỡng và tính hợp lệ”: "Quy tắc nhập dở không được có `active=1`").</t>
+          <t>・Bằng chứng cần chụp: Ảnh danh sách; ảnh kết quả trích xuất; SELECT `setting_status` của quy tắc mới chỉ có điều kiện, chưa có ngưỡng (khi có schema; kỳ vọng `setting_status=0` — thiết kế DB v2 mục 4.1: trạng thái 0 là đang thiết lập/vô hiệu và không tham gia xét).</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:F838"/>
+  <dimension ref="C2:F860"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.13" customWidth="1" min="1" max="1"/>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>40 test case TC-RS-BR-…, nguồn: 03-test-cases.vi.md. Điền 結果（Kết quả） và dán 証跡（Bằng chứng） khi chạy.</t>
+          <t>41 test case TC-RS-BR-…, nguồn: 03-test-cases.vi.md. Điền 結果（Kết quả） và dán 証跡（Bằng chứng） khi chạy.</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
     <row r="84">
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>5. TC-RS-BR-005 — Toàn bộ đối tượng（全員が対象） không vượt phạm vi mục, trường, năm</t>
+          <t>5. TC-RS-BR-041 — Điều kiện trung bình cùng nguồn kết hợp AND</t>
         </is>
       </c>
     </row>
@@ -9009,14 +9009,14 @@
     <row r="87">
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: mục số nguyên (M=100) có quy tắc “Cố định 30” (dưới 30) (Toàn bộ). Trường B (trường B (trường khác)) có học sinh điểm 10 ở mục tương tự. Mục mục số thập phân (M=100) (không có quy tắc) có S09=29.5.</t>
+          <t>・Điều kiện: Một rule có hai điều kiện trung bình cùng nguồn `A`: `A≥50` và `A&lt;70`, cùng dấu/ngưỡng theo thiết kế; các học sinh có A lần lượt là 40, 50, 60 và 70. Các học sinh đều thỏa bộ lọc đối tượng khác của rule.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: mục số nguyên (M=100), mục số thập phân (M=100); quy tắc “Cố định 30” (dưới 30), trường B (trường khác), học sinh S09 (mục số thập phân 29.5)</t>
+          <t>・Dữ liệu test: nguồn tổng hợp cùng phạm vi; P9 `A=40`, P10 `A=50`, P11 `A=60`, P12 `A=70`; cùng điểm đầu vào để khi rule khớp tạo cùng ngưỡng đỏ.</t>
         </is>
       </c>
     </row>
@@ -9030,380 +9030,380 @@
     <row r="90">
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>1. Chạy xét hàng loạt cho trường A.</t>
+          <t>1. Lưu một rule chứa đồng thời `A≥50` và `A&lt;70`.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2. Xem kết quả S09 ở mục số thập phân (M=100) và dữ liệu trường B.</t>
+          <t>2. Chạy xét cho P9–P12.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="D92" s="1" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>3. Mở lại rule và kiểm tra hai điều kiện vẫn thuộc cùng một rule/nguồn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="D93" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>・Chỉ ô của mục số nguyên (M=100) trong trường A năm 2026 được xét. S09 ở mục số thập phân (M=100) và học sinh trường B không bị ảnh hưởng.</t>
-        </is>
-      </c>
-    </row>
     <row r="94">
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>1. P9 (`A=40`) và P12 (`A=70`) không thỏa điều kiện → Không áp dụng.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 5.1 “Đối tượng áp dụng”; Figma MW “chương 02 – điều kiện áp dụng và nguồn trung bình” (58:8728) 「全員は、この評価項目の対象者全員。全校指定や全員赤点の意味ではない。」 (toàn bộ = mọi đối tượng của mục này, không phải toàn trường hay mọi người đều đỏ)</t>
+          <t>2. P10 (`A=50`) và P11 (`A=60`) thỏa cả hai điều kiện → được xét theo ngưỡng của rule.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả; SELECT kết quả theo trường/năm (khi có schema).</t>
+          <t>3. Không diễn giải hai điều kiện cùng nguồn thành OR; không ghép hai rule riêng biệt bằng AND.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="D97" s="1" t="inlineStr">
         <is>
+          <t>補足（Bổ sung）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: đặc tả v2 (R18) mục 5.1 và 5.2; xác nhận thiết kế ngày 30/09 (Q35: `A≥50` và `A&lt;70` nghĩa là `50≤A&lt;70`; 40/70 không thỏa, 50/60 thỏa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh form mở lại; ảnh kết quả bốn học sinh; log hoặc SELECT kết quả nếu có schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="D100" s="1" t="inlineStr">
+        <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="E98" s="2" t="n"/>
-    </row>
-    <row r="99">
-      <c r="D99" s="1" t="inlineStr">
+    <row r="101">
+      <c r="E101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="D102" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>6. TC-RS-BR-006 — Nhóm tham chiếu tách khỏi đối tượng áp dụng và danh sách đang lọc ở đầu ra</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Đúng phạm vi tham chiếu” (AC-G12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
     <row r="106">
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Quy tắc chỉ áp dụng cho lớp G-A (bộ lọc lớp), công thức `A×0.5`, nguồn có nhóm tham chiếu là một nhóm tổng hợp chứa cả G-A và G-B, `A=50` (G-A riêng có trung bình 40). Đã xét: `T=25`.</t>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>6. TC-RS-BR-005 — Toàn bộ đối tượng（全員が対象） không vượt phạm vi mục, trường, năm</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: Nguồn theo nhóm tổng hợp chứa G-A và G-B (không dùng nhóm theo khối vì G-A thuộc khối 1, G-B thuộc khối 2); các lớp học phần G-A, G-B, G-C</t>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Đối tượng áp dụng và nhu cầu nguồn” (AC-G05)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>操作（Thao tác）</t>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>1. Xem kết quả của học sinh G-A điểm 24 (Đỏ) và 26 (Không đỏ).</t>
+          <t>・Điều kiện: mục số nguyên (M=100) có quy tắc “Cố định 30” (dưới 30) (Toàn bộ). Trường B (trường B (trường khác)) có học sinh điểm 10 ở mục tương tự. Mục mục số thập phân (M=100) (không có quy tắc) có S09=29.5.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>2. Chạy trích xuất chỉ lọc lớp G-A.</t>
+          <t>・Dữ liệu test: mục số nguyên (M=100), mục số thập phân (M=100); quy tắc “Cố định 30” (dưới 30), trường B (trường khác), học sinh S09 (mục số thập phân 29.5)</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>3. Chạy lại xét.</t>
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>1. Chạy xét hàng loạt cho trường A.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>・Kết quả vẫn dùng `T=25` (từ `A=50` của cả nhóm). Lọc lớp ở đầu ra hoặc đối tượng chỉ G-A không làm trung bình thành 40 (`T=20`).</t>
+          <t>2. Xem kết quả S09 ở mục số thập phân (M=100) và dữ liệu trường B.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>補足（Bổ sung）</t>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lấy trung bình của nhóm nào và kết quả tổng hợp nào?” (Q9); đặc tả v2 (R18) mục 5.4 “Bộ thông tin nguồn”; Figma MW “chương 05 – trích xuất thành tích và kết quả Excel” (58:6233) 「抽出結果の絞り込みは平均の母集団を変更しません。」 (lọc kết quả trích xuất không đổi tập tham chiếu trung bình)</t>
+          <t>・Chỉ ô của mục số nguyên (M=100) trong trường A năm 2026 được xét. S09 ở mục số thập phân (M=100) và học sinh trường B không bị ảnh hưởng.</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: Ảnh cấu hình nguồn; ảnh kết quả trước/sau lọc.</t>
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: đặc tả v2 (R18) mục 5.1 “Đối tượng áp dụng”; Figma MW “chương 02 – điều kiện áp dụng và nguồn trung bình” (58:8728) 「全員は、この評価項目の対象者全員。全校指定や全員赤点の意味ではない。」 (toàn bộ = mọi đối tượng của mục này, không phải toàn trường hay mọi người đều đỏ)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="E118" s="2" t="n"/>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả; SELECT kết quả theo trường/năm (khi có schema).</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="D119" s="1" t="inlineStr">
         <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="E120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="D121" s="1" t="inlineStr">
+        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>7. TC-RS-BR-007 — Nguồn: bản đã chốt được ưu tiên hơn tổng hợp mới hơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13); tiêu chí nghiệm thu “Phạm vi từng đợt” (AC-G40)</t>
-        </is>
-      </c>
-    </row>
     <row r="125">
-      <c r="D125" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>7. TC-RS-BR-006 — Nhóm tham chiếu tách khỏi đối tượng áp dụng và danh sách đang lọc ở đầu ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Đúng phạm vi tham chiếu” (AC-G12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="D127" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Có bản tổng hợp đã chốt (trung bình 49.99) (chốt, `A=49.99`) và bản tổng hợp mới nhất chưa chốt (trung bình 62) (mới hơn, `A=62`) cùng phạm vi. mục số nguyên (M=100) có cặp quy tắc phân nhánh theo trung bình 60. Dummy data (dữ liệu giả cho bản tổng hợp đã chốt).</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: mục số nguyên (M=100); bản tổng hợp đã chốt (trung bình 49.99), bản tổng hợp mới nhất chưa chốt (trung bình 62), cặp quy tắc phân nhánh theo trung bình 60; học sinh điểm 24 và 26</t>
-        </is>
-      </c>
-    </row>
     <row r="128">
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: Quy tắc chỉ áp dụng cho lớp G-A (bộ lọc lớp), công thức `A×0.5`, nguồn có nhóm tham chiếu là một nhóm tổng hợp chứa cả G-A và G-B, `A=50` (G-A riêng có trung bình 40). Đã xét: `T=25`.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>1. Chạy nút cam.</t>
+          <t>・Dữ liệu test: Nguồn theo nhóm tổng hợp chứa G-A và G-B (không dùng nhóm theo khối vì G-A thuộc khối 1, G-B thuộc khối 2); các lớp học phần G-A, G-B, G-C</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>2. Xem kết quả.</t>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>1. Xem kết quả của học sinh G-A điểm 24 (Đỏ) và 26 (Không đỏ).</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>・Dùng `A=49.99` → nhánh ưu tiên 2 (`A&lt;60`), `T=24.995` → điểm 24 Đỏ, điểm 26 Không đỏ. Không dùng `A=62` (sẽ vào nhánh `A≥60`, `T=30`, điểm 26 Đỏ).</t>
+          <t>2. Chạy trích xuất chỉ lọc lớp G-A.</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>3. Chạy lại xét.</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lấy trung bình của nhóm nào và kết quả tổng hợp nào?” (Q9), câu “Quy trình vận hành khi có đánh giá tương đối là gì?” (Q12); đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” bước 1, mục 7.4 “Quy trình vận hành khi dùng trung bình/tỷ lệ nhóm” bước 4; Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:6946) 「確定平均を優先するため、常に直前の青ボタンの結果とは限らない。」 (vì ưu tiên trung bình đã chốt, không phải lúc nào cũng là kết quả nút xanh vừa bấm)</t>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh/SELECT hai nguồn (ghi dummy data); ảnh kết quả.</t>
+          <t>・Kết quả vẫn dùng `T=25` (từ `A=50` của cả nhóm). Lọc lớp ở đầu ra hoặc đối tượng chỉ G-A không làm trung bình thành 40 (`T=20`).</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>・Ghi chú: Không có radio bỏ qua bản chốt. Thời điểm tích hợp nguồn thật chưa chốt (đặc tả v2 mục 13.1). PASS trên dummy data chưa đủ cho tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn”/tiêu chí nghiệm thu “Phạm vi từng đợt”: phải chạy lại case với bản chốt thật (sau PR thêm trạng thái xác nhận kết quả tổng hợp xếp hạng, còn mở) trước khi đánh dấu đạt hai tiêu chí này.</t>
+      <c r="D136" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="D137" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lấy trung bình của nhóm nào và kết quả tổng hợp nào?” (Q9); đặc tả v2 (R18) mục 5.4 “Bộ thông tin nguồn”; Figma MW “chương 05 – trích xuất thành tích và kết quả Excel” (58:6233) 「抽出結果の絞り込みは平均の母集団を変更しません。」 (lọc kết quả trích xuất không đổi tập tham chiếu trung bình)</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="E138" s="2" t="n"/>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh cấu hình nguồn; ảnh kết quả trước/sau lọc.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="D139" s="1" t="inlineStr">
         <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="E140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="D141" s="1" t="inlineStr">
+        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="C143" s="1" t="inlineStr">
-        <is>
-          <t>8. TC-RS-BR-008 — Nguồn: chưa có bản chốt → dùng tổng hợp hoàn tất mới nhất cùng phạm vi</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13)</t>
-        </is>
-      </c>
-    </row>
     <row r="145">
-      <c r="D145" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>8. TC-RS-BR-007 — Nguồn: bản đã chốt được ưu tiên hơn tổng hợp mới hơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13); tiêu chí nghiệm thu “Phạm vi từng đợt” (AC-G40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="D147" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Chỉ có bản tổng hợp mới nhất chưa chốt (trung bình 62) (`A=62`), không có bản chốt; có thêm một tổng hợp cũ hơn `A=55` và một tổng hợp khác kỳ mới hơn `A=40`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: bản tổng hợp mới nhất chưa chốt (trung bình 62), cặp quy tắc phân nhánh theo trung bình 60</t>
-        </is>
-      </c>
-    </row>
     <row r="148">
-      <c r="D148" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: Có bản tổng hợp đã chốt (trung bình 49.99) (chốt, `A=49.99`) và bản tổng hợp mới nhất chưa chốt (trung bình 62) (mới hơn, `A=62`) cùng phạm vi. mục số nguyên (M=100) có cặp quy tắc phân nhánh theo trung bình 60. Dummy data (dữ liệu giả cho bản tổng hợp đã chốt).</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>1. Chạy nút cam.</t>
+          <t>・Dữ liệu test: mục số nguyên (M=100); bản tổng hợp đã chốt (trung bình 49.99), bản tổng hợp mới nhất chưa chốt (trung bình 62), cặp quy tắc phân nhánh theo trung bình 60; học sinh điểm 24 và 26</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>2. Xem kết quả học sinh điểm 26 và 29.</t>
+      <c r="D150" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>3. Bắt đầu một lượt tổng hợp mới cùng phạm vi sau bản tổng hợp mới nhất chưa chốt (trung bình 62) nhưng chưa hoàn tất (đang chạy hoặc thất bại); chạy lại nút cam.</t>
+          <t>1. Chạy nút cam.</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="D152" s="1" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>2. Xem kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="D153" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>・1–2. Dùng `A=62` (mới nhất, cùng kỳ) → nhánh `A≥60`, `T=30` → 26 và 29 Đỏ. Không dùng bản cũ hơn hoặc bản khác kỳ.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>3. Vẫn dùng `A=62` của bản hoàn tất mới nhất; không đọc lượt tổng hợp chưa hoàn tất.</t>
+          <t>・Dùng `A=49.99` → nhánh ưu tiên 2 (`A&lt;60`), `T=24.995` → điểm 24 Đỏ, điểm 26 Không đỏ. Không dùng `A=62` (sẽ vào nhánh `A≥60`, `T=30`, điểm 26 Đỏ).</t>
         </is>
       </c>
     </row>
@@ -9417,345 +9417,345 @@
     <row r="156">
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lấy trung bình của nhóm nào và kết quả tổng hợp nào?” (Q9); đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” bước 2 ("kết quả tổng hợp hoàn tất mới nhất"); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13)</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lấy trung bình của nhóm nào và kết quả tổng hợp nào?” (Q9), câu “Quy trình vận hành khi có đánh giá tương đối là gì?” (Q12); đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” bước 1, mục 7.4 “Quy trình vận hành khi dùng trung bình/tỷ lệ nhóm” bước 4; Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:6946) 「確定平均を優先するため、常に直前の青ボタンの結果とは限らない。」 (vì ưu tiên trung bình đã chốt, không phải lúc nào cũng là kết quả nút xanh vừa bấm)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh danh sách tổng hợp; ảnh kết quả.</t>
+          <t>・Bằng chứng cần chụp: Ảnh/SELECT hai nguồn (ghi dummy data); ảnh kết quả.</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="D158" s="1" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: Không có radio bỏ qua bản chốt. Thời điểm tích hợp nguồn thật chưa chốt (đặc tả v2 mục 13.1). PASS trên dummy data chưa đủ cho tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn”/tiêu chí nghiệm thu “Phạm vi từng đợt”: phải chạy lại case với bản chốt thật (sau PR thêm trạng thái xác nhận kết quả tổng hợp xếp hạng, còn mở) trước khi đánh dấu đạt hai tiêu chí này.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="D159" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="E159" s="2" t="n"/>
-    </row>
     <row r="160">
-      <c r="D160" s="1" t="inlineStr">
+      <c r="E160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="D161" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="C164" s="1" t="inlineStr">
-        <is>
-          <t>9. TC-RS-BR-009 — Nguồn: bản đã chốt thiếu dữ liệu → Chưa xét được, không chuyển sang bản thường</t>
-        </is>
-      </c>
-    </row>
     <row r="165">
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13); tiêu chí nghiệm thu “Phạm vi từng đợt” (AC-G40)</t>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>9. TC-RS-BR-008 — Nguồn: chưa có bản chốt → dùng tổng hợp hoàn tất mới nhất cùng phạm vi</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="D166" s="1" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="D167" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Có bản đã chốt thiếu dữ liệu của ô (chốt, thiếu dòng cho môn/mục) và bản tổng hợp mới nhất chưa chốt (trung bình 62) (thường, đầy đủ). cặp quy tắc phân nhánh theo trung bình 60. Ô trước đó Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: bản đã chốt thiếu dữ liệu của ô, bản tổng hợp mới nhất chưa chốt (trung bình 62), cặp quy tắc phân nhánh theo trung bình 60</t>
+          <t>・Điều kiện: Chỉ có bản tổng hợp mới nhất chưa chốt (trung bình 62) (`A=62`), không có bản chốt; có thêm một tổng hợp cũ hơn `A=55` và một tổng hợp khác kỳ mới hơn `A=40`.</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="D169" s="1" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: bản tổng hợp mới nhất chưa chốt (trung bình 62), cặp quy tắc phân nhánh theo trung bình 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="D170" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>1. Chạy nút cam.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>2. Xem kết quả và ba đầu ra.</t>
+          <t>1. Chạy nút cam.</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="D172" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>2. Xem kết quả học sinh điểm 26 và 29.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>・Chưa xét được; ngừng dùng dấu/lọc đỏ cũ; điểm giữ nguyên. Không dùng bản tổng hợp mới nhất chưa chốt (trung bình 62) hay bản khác kỳ.</t>
+          <t>3. Bắt đầu một lượt tổng hợp mới cùng phạm vi sau bản tổng hợp mới nhất chưa chốt (trung bình 62) nhưng chưa hoàn tất (đang chạy hoặc thất bại); chạy lại nút cam.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="D174" s="1" t="inlineStr">
         <is>
-          <t>補足（Bổ sung）</t>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” bước 3, mục 8.3 “Không tạo được ngưỡng hợp lệ”; Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lấy trung bình của nhóm nào và kết quả tổng hợp nào?” (Q9), câu “Đã xét lại nhưng không tạo được ngưỡng hợp lệ thì dùng kết quả cũ không?” (Q26)</t>
+          <t>・1–2. Dùng `A=62` (mới nhất, cùng kỳ) → nhánh `A≥60`, `T=30` → 26 và 29 Đỏ. Không dùng bản cũ hơn hoặc bản khác kỳ.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh/SELECT nguồn; ảnh kết quả và thông báo nguyên nhân. SELECT `reason_code` (khi có schema; đề xuất `source_missing` — thiết kế DB v2 mục 4.3 “Trạng thái kết quả”, PROPOSED).</t>
+          <t>3. Vẫn dùng `A=62` của bản hoàn tất mới nhất; không đọc lượt tổng hợp chưa hoàn tất.</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>・Ghi chú: Dummy data (dữ liệu giả cho bản tổng hợp đã chốt). PASS trên dummy data chưa đủ cho tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn”/tiêu chí nghiệm thu “Phạm vi từng đợt”: phải chạy lại với bản chốt thật (sau PR thêm trạng thái xác nhận kết quả tổng hợp xếp hạng, còn mở).</t>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="D178" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lấy trung bình của nhóm nào và kết quả tổng hợp nào?” (Q9); đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” bước 2 ("kết quả tổng hợp hoàn tất mới nhất"); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13)</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="E179" s="2" t="n"/>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh danh sách tổng hợp; ảnh kết quả.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="D180" s="1" t="inlineStr">
         <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="E181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="D182" s="1" t="inlineStr">
+        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="C184" s="1" t="inlineStr">
-        <is>
-          <t>10. TC-RS-BR-010 — Chưa có kết quả tổng hợp → Chưa xét được, không thay bằng 0 hay nhóm khác</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13)</t>
-        </is>
-      </c>
-    </row>
     <row r="186">
-      <c r="D186" s="1" t="inlineStr">
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>10. TC-RS-BR-009 — Nguồn: bản đã chốt thiếu dữ liệu → Chưa xét được, không chuyển sang bản thường</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13); tiêu chí nghiệm thu “Phạm vi từng đợt” (AC-G40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="D188" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Công thức `A×0.5` với nguồn nguồn chưa có kết quả tổng hợp (chưa tổng hợp). Ô trước đó Đỏ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: nguồn chưa có kết quả tổng hợp</t>
-        </is>
-      </c>
-    </row>
     <row r="189">
-      <c r="D189" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: Có bản đã chốt thiếu dữ liệu của ô (chốt, thiếu dòng cho môn/mục) và bản tổng hợp mới nhất chưa chốt (trung bình 62) (thường, đầy đủ). cặp quy tắc phân nhánh theo trung bình 60. Ô trước đó Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="E190" s="2" t="inlineStr">
         <is>
+          <t>・Dữ liệu test: bản đã chốt thiếu dữ liệu của ô, bản tổng hợp mới nhất chưa chốt (trung bình 62), cặp quy tắc phân nhánh theo trung bình 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="D191" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="E192" s="2" t="inlineStr">
+        <is>
           <t>1. Chạy nút cam.</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>2. Xem kết quả.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="D192" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>・Chưa xét được; `A` không bị coi là 0 (nếu coi 0 thì `T=0`, mọi điểm dương Không đỏ); không dùng nhóm khác; ngừng dấu đỏ cũ.</t>
+          <t>2. Xem kết quả và ba đầu ra.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>補足（Bổ sung）</t>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Thiếu dữ liệu xét có chặn công khai hoặc phát hành không?” (Q15), câu “Đã xét lại nhưng không tạo được ngưỡng hợp lệ thì dùng kết quả cũ không?” (Q26); đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” bước 4; Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7053) 「参照する平均点がありません。」 (không có trung bình tham chiếu), (58:7058) 「前回の判定結果は使用しません。」 (không dùng kết quả xét lần trước)</t>
+          <t>・Chưa xét được; ngừng dùng dấu/lọc đỏ cũ; điểm giữ nguyên. Không dùng bản tổng hợp mới nhất chưa chốt (trung bình 62) hay bản khác kỳ.</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả, thông báo. SELECT `reason_code` (khi có schema; đề xuất `source_missing` — thiết kế DB v2 mục 4.3 “Trạng thái kết quả”, PROPOSED).</t>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="D197" s="1" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” bước 3, mục 8.3 “Không tạo được ngưỡng hợp lệ”; Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lấy trung bình của nhóm nào và kết quả tổng hợp nào?” (Q9), câu “Đã xét lại nhưng không tạo được ngưỡng hợp lệ thì dùng kết quả cũ không?” (Q26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh/SELECT nguồn; ảnh kết quả và thông báo nguyên nhân. SELECT `reason_code` (khi có schema; đề xuất `source_missing` — thiết kế DB v2 mục 4.3 “Trạng thái kết quả”, PROPOSED).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: Dummy data (dữ liệu giả cho bản tổng hợp đã chốt). PASS trên dummy data chưa đủ cho tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn”/tiêu chí nghiệm thu “Phạm vi từng đợt”: phải chạy lại với bản chốt thật (sau PR thêm trạng thái xác nhận kết quả tổng hợp xếp hạng, còn mở).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="D200" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="E198" s="2" t="n"/>
-    </row>
-    <row r="199">
-      <c r="D199" s="1" t="inlineStr">
+    <row r="201">
+      <c r="E201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="D202" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="C203" s="1" t="inlineStr">
-        <is>
-          <t>11. TC-RS-BR-011 — Nguồn chỉ cần khi quy tắc đọc trung bình/tỷ lệ nhóm</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Đối tượng áp dụng và nhu cầu nguồn” (AC-G05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="D205" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
     <row r="206">
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Không có kết quả tổng hợp nào (nguồn chưa có kết quả tổng hợp).</t>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>11. TC-RS-BR-010 — Chưa có kết quả tổng hợp → Chưa xét được, không thay bằng 0 hay nhóm khác</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30), quy tắc tỷ lệ 30%, nguồn chưa có kết quả tổng hợp, học sinh S01 (điểm 29)</t>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>操作（Thao tác）</t>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>1. Chỉ có quy tắc “Cố định 30” (dưới 30) (Toàn bộ, không điều kiện trung bình): đăng ký S01=29.</t>
+          <t>・Điều kiện: Công thức `A×0.5` với nguồn nguồn chưa có kết quả tổng hợp (chưa tổng hợp). Ô trước đó Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>2. Chỉ có quy tắc tỷ lệ 30%: đăng ký S01=29.</t>
+          <t>・Dữ liệu test: nguồn chưa có kết quả tổng hợp</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>3. Chỉ có quy tắc "cố định 30 `&lt;`, điều kiện `A≥60`": đăng ký S01=29.</t>
+      <c r="D211" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="D212" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>1. Chạy nút cam.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>1. Đỏ (không cần nguồn).</t>
+          <t>2. Xem kết quả.</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="E214" s="2" t="inlineStr">
-        <is>
-          <t>2. Đỏ (`M=100`, `T=30`; không cần nguồn).</t>
+      <c r="D214" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>3. Chưa xét được; không bỏ điều kiện để áp 30 cho mọi học sinh.</t>
+          <t>・Chưa xét được; `A` không bị coi là 0 (nếu coi 0 thì `T=0`, mọi điểm dương Không đỏ); không dùng nhóm khác; ngừng dấu đỏ cũ.</t>
         </is>
       </c>
     </row>
@@ -9769,14 +9769,14 @@
     <row r="217">
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Điều kiện nào không cần nguồn trung bình?” (Q10); đặc tả v2 (R18) mục 5.6 “Khi nào không cần nguồn?” (ví dụ cố định 30 khi `A≥60`); Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:6945) 「平均に依存しない設定は成績登録で判定。平均を使う適用条件があれば参照元が必要。」 (thiết lập không phụ thuộc trung bình xét khi đăng ký điểm; có điều kiện dùng trung bình thì cần nguồn)</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Thiếu dữ liệu xét có chặn công khai hoặc phát hành không?” (Q15), câu “Đã xét lại nhưng không tạo được ngưỡng hợp lệ thì dùng kết quả cũ không?” (Q26); đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” bước 4; Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7053) 「参照する平均点がありません。」 (không có trung bình tham chiếu), (58:7058) 「前回の判定結果は使用しません。」 (không dùng kết quả xét lần trước)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả ba lần.</t>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả, thông báo. SELECT `reason_code` (khi có schema; đề xuất `source_missing` — thiết kế DB v2 mục 4.3 “Trạng thái kết quả”, PROPOSED).</t>
         </is>
       </c>
     </row>
@@ -9800,14 +9800,14 @@
     <row r="225">
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>12. TC-RS-BR-012 — Điểm được xét là điểm cuối đã lưu (dự kiến, sửa tay, sau giới hạn miền điểm)</t>
+          <t>12. TC-RS-BR-011 — Nguồn chỉ cần khi quy tắc đọc trung bình/tỷ lệ nhóm</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Dùng điểm cuối cùng” (AC-G19)</t>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Đối tượng áp dụng và nhu cầu nguồn” (AC-G05)</t>
         </is>
       </c>
     </row>
@@ -9821,14 +9821,14 @@
     <row r="228">
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: mục số nguyên (M=100) có quy tắc “Cố định 30” (dưới 30) và (cho biến thể c) mục số nguyên có thêm tính tự động có quy tắc tính tự động cho kết quả vượt 100.</t>
+          <t>・Điều kiện: Không có kết quả tổng hợp nào (nguồn chưa có kết quả tổng hợp).</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: mục số nguyên (M=100), mục số nguyên có thêm tính tự động; học sinh S06 (điểm dự kiến 24), học sinh S08 (sửa tay 28 thành 35), quy tắc “Cố định 30” (dưới 30)</t>
+          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30), quy tắc tỷ lệ 30%, nguồn chưa có kết quả tổng hợp, học sinh S01 (điểm 29)</t>
         </is>
       </c>
     </row>
@@ -9842,21 +9842,21 @@
     <row r="231">
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>(a) S06 = 24 là Điểm dự kiến（見込点）: đăng ký.</t>
+          <t>1. Chỉ có quy tắc “Cố định 30” (dưới 30) (Toàn bộ, không điều kiện trung bình): đăng ký S01=29.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>(b) S08: nhập 28, lưu; sửa tay thành 35, lưu.</t>
+          <t>2. Chỉ có quy tắc tỷ lệ 30%: đăng ký S01=29.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>(c) Tạo dữ liệu mà phép tính cho 120 nhưng điểm lưu hợp lệ là 100; áp quy tắc cố định 100 `&lt;` và 100 `≤`.</t>
+          <t>3. Chỉ có quy tắc "cố định 30 `&lt;`, điều kiện `A≥60`": đăng ký S01=29.</t>
         </is>
       </c>
     </row>
@@ -9870,21 +9870,21 @@
     <row r="235">
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>(a) Đỏ.</t>
+          <t>1. Đỏ (không cần nguồn).</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>(b) Sau lần lưu thứ hai: xét 35 → Không đỏ.</t>
+          <t>2. Đỏ (`M=100`, `T=30`; không cần nguồn).</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>(c) Xét `S=100`: `&lt;100` Không đỏ; `≤100` Đỏ.</t>
+          <t>3. Chưa xét được; không bỏ điều kiện để áp 30 cho mọi học sinh.</t>
         </is>
       </c>
     </row>
@@ -9898,258 +9898,258 @@
     <row r="239">
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Dùng điểm nào để xét, và phân biệt điểm 0 với ô trống thế nào?” (Q3); đặc tả v2 (R18) mục 2.3 “Điểm được đưa vào xét” (ví dụ 28→35, 120→100)</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Điều kiện nào không cần nguồn trung bình?” (Q10); đặc tả v2 (R18) mục 5.6 “Khi nào không cần nguồn?” (ví dụ cố định 30 khi `A≥60`); Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:6945) 「平均に依存しない設定は成績登録で判定。平均を使う適用条件があれば参照元が必要。」 (thiết lập không phụ thuộc trung bình xét khi đăng ký điểm; có điều kiện dùng trung bình thì cần nguồn)</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh điểm đã lưu và kết quả mỗi biến thể.</t>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả ba lần.</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>・Ghi chú: (c) cần cách tạo dữ liệu giới hạn miền điểm — hỏi team dev khi chuẩn bị.</t>
+      <c r="D241" s="1" t="inlineStr">
+        <is>
+          <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="D242" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
-        </is>
-      </c>
+      <c r="E242" s="2" t="n"/>
     </row>
     <row r="243">
-      <c r="E243" s="2" t="n"/>
-    </row>
-    <row r="244">
-      <c r="D244" s="1" t="inlineStr">
+      <c r="D243" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>13. TC-RS-BR-012 — Điểm được xét là điểm cuối đã lưu (dự kiến, sửa tay, sau giới hạn miền điểm)</t>
+        </is>
+      </c>
+    </row>
     <row r="248">
-      <c r="C248" s="1" t="inlineStr">
-        <is>
-          <t>13. TC-RS-BR-013 — Cờ Chưa dự thi（未受験） không loại điểm số khỏi xét</t>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Dùng điểm cuối cùng” (AC-G19)</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Dùng điểm cuối cùng” (AC-G19)</t>
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="D250" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: mục số nguyên (M=100) có quy tắc “Cố định 30” (dưới 30) và (cho biến thể c) mục số nguyên có thêm tính tự động có quy tắc tính tự động cho kết quả vượt 100.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30) (`&lt;30`).</t>
+          <t>・Dữ liệu test: mục số nguyên (M=100), mục số nguyên có thêm tính tự động; học sinh S06 (điểm dự kiến 24), học sinh S08 (sửa tay 28 thành 35), quy tắc “Cố định 30” (dưới 30)</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30); học sinh S07 (điểm 35, cờ Chưa dự thi（未受験）) (35, cờ Chưa dự thi) và biến thể S07 = 25 cùng cờ; học sinh S09 (mục số thập phân 29.5) (mục số thập phân (M=100) = 29.5) được thiết lập loại khỏi xếp hạng; mục số thập phân (M=100) có quy tắc “Cố định 30” (dưới 30)</t>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="D253" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>(a) S06 = 24 là Điểm dự kiến（見込点）: đăng ký.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng ký S07=35 kèm cờ Chưa dự thi（未受験）.</t>
+          <t>(b) S08: nhập 28, lưu; sửa tay thành 35, lưu.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>2. Sửa S07=25, giữ cờ.</t>
+          <t>(c) Tạo dữ liệu mà phép tính cho 120 nhưng điểm lưu hợp lệ là 100; áp quy tắc cố định 100 `&lt;` và 100 `≤`.</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>3. Đăng ký điểm 29.5 cho S09 (học sinh bị loại khỏi xếp hạng); chạy nút xanh rồi nút cam.</t>
+      <c r="D256" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="D257" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>(a) Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>1. Được xét → Không đỏ.</t>
+          <t>(b) Sau lần lưu thứ hai: xét 35 → Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>2. Được xét → Đỏ.</t>
+          <t>(c) Xét `S=100`: `&lt;100` Không đỏ; `≤100` Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>3. S09 được xét → Đỏ (29.5 `&lt;30`); việc bị loại khỏi xếp hạng không loại ô khỏi xét đỏ.</t>
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="D261" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Dùng điểm nào để xét, và phân biệt điểm 0 với ô trống thế nào?” (Q3); đặc tả v2 (R18) mục 2.3 “Điểm được đưa vào xét” (ví dụ 28→35, 120→100)</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Dùng điểm nào để xét, và phân biệt điểm 0 với ô trống thế nào?” (Q3); đặc tả v2 (R18) mục 2.3 “Điểm được đưa vào xét”; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Dùng điểm cuối cùng” (AC-G19) ("không phụ thuộc AutoRating hay đối tượng xếp hạng")</t>
+          <t>・Bằng chứng cần chụp: Ảnh điểm đã lưu và kết quả mỗi biến thể.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả ba lần; ảnh thiết lập loại khỏi xếp hạng của S09.</t>
+          <t>・Ghi chú: (c) cần cách tạo dữ liệu giới hạn miền điểm — hỏi team dev khi chuẩn bị.</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="E264" s="2" t="inlineStr">
-        <is>
-          <t>・Sau khi chạy: Gỡ thiết lập loại khỏi xếp hạng của S09.</t>
+      <c r="D264" s="1" t="inlineStr">
+        <is>
+          <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="E265" s="2" t="inlineStr">
-        <is>
-          <t>・Ghi chú: Loại khỏi xếp hạng chỉ ảnh hưởng tổng hợp thứ hạng (mẫu số trung bình: case “Mẫu số trung bình khi có học sinh bị loại khỏi xếp hạng”), không ảnh hưởng việc xét ô.</t>
-        </is>
-      </c>
+      <c r="E265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="D266" s="1" t="inlineStr">
         <is>
-          <t>結果（Kết quả）</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="E267" s="2" t="n"/>
-    </row>
-    <row r="268">
-      <c r="D268" s="1" t="inlineStr">
-        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="C270" s="1" t="inlineStr">
+        <is>
+          <t>14. TC-RS-BR-013 — Cờ Chưa dự thi（未受験） không loại điểm số khỏi xét</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Dùng điểm cuối cùng” (AC-G19)</t>
+        </is>
+      </c>
+    </row>
     <row r="272">
-      <c r="C272" s="1" t="inlineStr">
-        <is>
-          <t>14. TC-RS-BR-014 — Ô trống không bị coi là 0 (trạng thái Không có điểm)</t>
+      <c r="D272" s="1" t="inlineStr">
+        <is>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="D273" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Dùng điểm cuối cùng” (AC-G19)</t>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30) (`&lt;30`).</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="D274" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30); học sinh S07 (điểm 35, cờ Chưa dự thi（未受験）) (35, cờ Chưa dự thi) và biến thể S07 = 25 cùng cờ; học sinh S09 (mục số thập phân 29.5) (mục số thập phân (M=100) = 29.5) được thiết lập loại khỏi xếp hạng; mục số thập phân (M=100) có quy tắc “Cố định 30” (dưới 30)</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="E275" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30) (`&lt;30`) và quy tắc cố định 30 với Nhỏ hơn hoặc bằng（以下） biến thể cố định 0 `≤`.</t>
+      <c r="D275" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30), quy tắc cố định 30 với Nhỏ hơn hoặc bằng（以下）; học sinh S05 (ô trống) (trống), học sinh S04 (điểm 0) (0)</t>
+          <t>1. Đăng ký S07=35 kèm cờ Chưa dự thi（未受験）.</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="D277" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>2. Sửa S07=25, giữ cờ.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>1. Với quy tắc “Cố định 30” (dưới 30): đăng ký S04=0, để S05 trống.</t>
+          <t>3. Đăng ký điểm 29.5 cho S09 (học sinh bị loại khỏi xếp hạng); chạy nút xanh rồi nút cam.</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="E279" s="2" t="inlineStr">
-        <is>
-          <t>2. Đổi thành quy tắc cố định 0 `≤`, chạy lại.</t>
+      <c r="D279" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="D280" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>1. Được xét → Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>1. S04 Đỏ (0 hợp lệ là số); S05 Không có điểm, không dấu đỏ.</t>
+          <t>2. Được xét → Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>2. S04 Đỏ (`0≤0`); S05 vẫn Không có điểm (không thành Đỏ như thể là 0).</t>
+          <t>3. S09 được xét → Đỏ (29.5 `&lt;30`); việc bị loại khỏi xếp hạng không loại ô khỏi xét đỏ.</t>
         </is>
       </c>
     </row>
@@ -10163,401 +10163,401 @@
     <row r="284">
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Dùng điểm nào để xét, và phân biệt điểm 0 với ô trống thế nào?” (Q3); đặc tả v2 (R18) mục 2.3 “Điểm được đưa vào xét”, mục 8.1 “Các trạng thái phải phân biệt”</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Dùng điểm nào để xét, và phân biệt điểm 0 với ô trống thế nào?” (Q3); đặc tả v2 (R18) mục 2.3 “Điểm được đưa vào xét”; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Dùng điểm cuối cùng” (AC-G19) ("không phụ thuộc AutoRating hay đối tượng xếp hạng")</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả; bằng chứng trạng thái lưu (khi có schema).</t>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả ba lần; ảnh thiết lập loại khỏi xếp hạng của S09.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>・Ghi chú: Cách lưu trạng thái Không có điểm (`judgment_status=4`, `reason_code=no_score`) theo thiết kế DB v2 là PROPOSED, chờ review (đặc tả v2 mục 13.1).</t>
+          <t>・Sau khi chạy: Gỡ thiết lập loại khỏi xếp hạng của S09.</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="D287" s="1" t="inlineStr">
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: Loại khỏi xếp hạng chỉ ảnh hưởng tổng hợp thứ hạng (mẫu số trung bình: case “Mẫu số trung bình khi có học sinh bị loại khỏi xếp hạng”), không ảnh hưởng việc xét ô.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="D288" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="E288" s="2" t="n"/>
-    </row>
     <row r="289">
-      <c r="D289" s="1" t="inlineStr">
+      <c r="E289" s="2" t="n"/>
+    </row>
+    <row r="290">
+      <c r="D290" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="C293" s="1" t="inlineStr">
-        <is>
-          <t>15. TC-RS-BR-015 — Lưu cấu hình không xét; kết quả trước giữ tới lần chạy lại</t>
-        </is>
-      </c>
-    </row>
     <row r="294">
-      <c r="D294" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giữ kết quả trước khi chạy lại” (AC-G21)</t>
+      <c r="C294" s="1" t="inlineStr">
+        <is>
+          <t>15. TC-RS-BR-014 — Ô trống không bị coi là 0 (trạng thái Không có điểm)</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="D295" s="1" t="inlineStr">
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Dùng điểm cuối cùng” (AC-G19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="D296" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="E296" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30); S03 sửa thành 32 và đã xét → Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30)</t>
+          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30) (`&lt;30`) và quy tắc cố định 30 với Nhỏ hơn hoặc bằng（以下） biến thể cố định 0 `≤`.</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="D298" s="1" t="inlineStr">
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30), quy tắc cố định 30 với Nhỏ hơn hoặc bằng（以下）; học sinh S05 (ô trống) (trống), học sinh S04 (điểm 0) (0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="D299" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="E299" s="2" t="inlineStr">
-        <is>
-          <t>1. Đổi ngưỡng thành 35 `&lt;`, lưu.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>2. Xem ba đầu ra.</t>
+          <t>1. Với quy tắc “Cố định 30” (dưới 30): đăng ký S04=0, để S05 trống.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>3. Đổi thứ tự quy tắc/đổi nguồn (nếu có), lưu, xem lại.</t>
+          <t>2. Đổi thành quy tắc cố định 0 `≤`, chạy lại.</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="E302" s="2" t="inlineStr">
-        <is>
-          <t>4. Chỉ đổi dấu (`&lt;35` → `≤35`), lưu, xem lại. Nếu công thức thuộc đợt phát hành: chỉ đổi công thức của một quy tắc công thức, lưu, xem lại.</t>
+      <c r="D302" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>5. Chạy lại (đăng ký lại điểm S03 hoặc nút cam), xem ba đầu ra.</t>
+          <t>1. S04 Đỏ (0 hợp lệ là số); S05 Không có điểm, không dấu đỏ.</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="D304" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>2. S04 Đỏ (`0≤0`); S05 vẫn Không có điểm (không thành Đỏ như thể là 0).</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="E305" s="2" t="inlineStr">
-        <is>
-          <t>1. Sau lưu: không báo "đã cập nhật điểm đỏ học sinh"; có hướng dẫn chạy lại.</t>
+      <c r="D305" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>・2–4. S03 vẫn Không đỏ theo kết quả trước; hiệu ứng hiển thị trước đó giữ nguyên.</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Dùng điểm nào để xét, và phân biệt điểm 0 với ô trống thế nào?” (Q3); đặc tả v2 (R18) mục 2.3 “Điểm được đưa vào xét”, mục 8.1 “Các trạng thái phải phân biệt”</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>5. Sau chạy lại thành công: S03 Đỏ.</t>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả; bằng chứng trạng thái lưu (khi có schema).</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="D308" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: Cách lưu trạng thái Không có điểm (`judgment_status=4`, `reason_code=no_score`) theo thiết kế DB v2 là PROPOSED, chờ review (đặc tả v2 mục 13.1).</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="E309" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lưu điều kiện hoặc thay nguồn có cập nhật ngay kết quả không?” (Q13) (ví dụ 32, `&lt;30`→`&lt;35`); đặc tả v2 (R18) mục 4.4 “Lưu, đổi thứ tự và xóa”, mục 7.2 “Bảng sự kiện”, mục 8.2 “Bảng chuyển trạng thái” dòng 1–2; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Giữ kết quả trước khi chạy lại” (AC-G21) ("Chỉ đổi ngưỡng/dấu/công thức/ưu tiên/đối tượng/nguồn… thì vẫn giữ kết quả"); Figma MW “màn danh sách thiết lập điểm đỏ” (58:10158) 「設定を変更した場合は、成績登録または成績集計の自動算出を再実行してください。」 (đổi thiết lập thì chạy lại đăng ký điểm hoặc tính tự động), “chương 01 – lối vào, danh sách, xóa thiết lập” (58:10179)</t>
+      <c r="D309" s="1" t="inlineStr">
+        <is>
+          <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="E310" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: Ảnh thông báo sau lưu; ảnh đầu ra trước/sau chạy lại.</t>
-        </is>
-      </c>
+      <c r="E310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="D311" s="1" t="inlineStr">
         <is>
-          <t>結果（Kết quả）</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="E312" s="2" t="n"/>
-    </row>
-    <row r="313">
-      <c r="D313" s="1" t="inlineStr">
-        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="C315" s="1" t="inlineStr">
+        <is>
+          <t>16. TC-RS-BR-015 — Lưu cấu hình không xét; kết quả trước giữ tới lần chạy lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giữ kết quả trước khi chạy lại” (AC-G21)</t>
+        </is>
+      </c>
+    </row>
     <row r="317">
-      <c r="C317" s="1" t="inlineStr">
-        <is>
-          <t>16. TC-RS-BR-016 — Sửa điểm 29 → 40 được lưu và xét trong cùng lượt</t>
+      <c r="D317" s="1" t="inlineStr">
+        <is>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="D318" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Lưu thành công và thông báo an toàn” (AC-G26)</t>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30); S03 sửa thành 32 và đã xét → Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="D319" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30)</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="E320" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30); S01=29 Đỏ.</t>
+      <c r="D320" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30); học sinh S01 (điểm 29)</t>
+          <t>1. Đổi ngưỡng thành 35 `&lt;`, lưu.</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="D322" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>2. Xem ba đầu ra.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>1. Sửa S01 thành 40, lưu thành công.</t>
+          <t>3. Đổi thứ tự quy tắc/đổi nguồn (nếu có), lưu, xem lại.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>2. Xem ba đầu ra ngay sau đó.</t>
+          <t>4. Chỉ đổi dấu (`&lt;35` → `≤35`), lưu, xem lại. Nếu công thức thuộc đợt phát hành: chỉ đổi công thức của một quy tắc công thức, lưu, xem lại.</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="D325" s="1" t="inlineStr">
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>5. Chạy lại (đăng ký lại điểm S03 hoặc nút cam), xem ba đầu ra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="D326" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
-    <row r="326">
-      <c r="E326" s="2" t="inlineStr">
-        <is>
-          <t>・S01 Không đỏ; không cần bật một chế độ thủ công/tự động riêng.</t>
-        </is>
-      </c>
-    </row>
     <row r="327">
-      <c r="D327" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>1. Sau lưu: không báo "đã cập nhật điểm đỏ học sinh"; có hướng dẫn chạy lại.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Khi nào xét điểm đỏ và có cần chế độ thủ công/tự động riêng không?” (Q11) (ví dụ 29→40); đặc tả v2 (R18) mục 8.2 “Bảng chuyển trạng thái” dòng 3</t>
+          <t>・2–4. S03 vẫn Không đỏ theo kết quả trước; hiệu ứng hiển thị trước đó giữ nguyên.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh trước/sau.</t>
+          <t>5. Sau chạy lại thành công: S03 Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="D330" s="1" t="inlineStr">
         <is>
+          <t>補足（Bổ sung）</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lưu điều kiện hoặc thay nguồn có cập nhật ngay kết quả không?” (Q13) (ví dụ 32, `&lt;30`→`&lt;35`); đặc tả v2 (R18) mục 4.4 “Lưu, đổi thứ tự và xóa”, mục 7.2 “Bảng sự kiện”, mục 8.2 “Bảng chuyển trạng thái” dòng 1–2; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Giữ kết quả trước khi chạy lại” (AC-G21) ("Chỉ đổi ngưỡng/dấu/công thức/ưu tiên/đối tượng/nguồn… thì vẫn giữ kết quả"); Figma MW “màn danh sách thiết lập điểm đỏ” (58:10158) 「設定を変更した場合は、成績登録または成績集計の自動算出を再実行してください。」 (đổi thiết lập thì chạy lại đăng ký điểm hoặc tính tự động), “chương 01 – lối vào, danh sách, xóa thiết lập” (58:10179)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh thông báo sau lưu; ảnh đầu ra trước/sau chạy lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="D333" s="1" t="inlineStr">
+        <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="331">
-      <c r="E331" s="2" t="n"/>
-    </row>
-    <row r="332">
-      <c r="D332" s="1" t="inlineStr">
+    <row r="334">
+      <c r="E334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="D335" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="336">
-      <c r="C336" s="1" t="inlineStr">
-        <is>
-          <t>17. TC-RS-BR-017 — Chạy lại không tạo được ngưỡng hợp lệ → Chưa xét được, ngừng kết quả cũ, giữ điểm</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="D337" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Trạng thái sau lần chạy” (AC-G20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="D338" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
     <row r="339">
-      <c r="E339" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Ô S01=29 Đỏ theo công thức `A×0.5` (nguồn bản tổng hợp mới nhất chưa chốt (trung bình 62)).</t>
+      <c r="C339" s="1" t="inlineStr">
+        <is>
+          <t>17. TC-RS-BR-016 — Sửa điểm 29 → 40 được lưu và xét trong cùng lượt</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="E340" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: mục có M không hợp lệ, quy tắc công thức 100 ÷ trung bình, bản tổng hợp mới nhất chưa chốt (trung bình 62); học sinh S01 (điểm 29), nguồn chưa có kết quả tổng hợp</t>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Lưu thành công và thông báo an toàn” (AC-G26)</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="D341" s="1" t="inlineStr">
         <is>
-          <t>操作（Thao tác）</t>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>1. Biến thể (a): đổi nguồn sang nguồn chưa có kết quả tổng hợp (không có tổng hợp), lưu, chạy lại.</t>
+          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30); S01=29 Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>2. Biến thể (b): quy tắc tỷ lệ với M không hợp lệ (mục có M không hợp lệ), chạy lại.</t>
+          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30); học sinh S01 (điểm 29)</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="E344" s="2" t="inlineStr">
-        <is>
-          <t>3. Biến thể (c): quy tắc công thức 100 ÷ trung bình với `A=0`, chạy lại.</t>
+      <c r="D344" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>4. Sau mỗi biến thể: xem ba đầu ra và điểm S01.</t>
+          <t>1. Sửa S01 thành 40, lưu thành công.</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="D346" s="1" t="inlineStr">
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>2. Xem ba đầu ra ngay sau đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="D347" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
-    <row r="347">
-      <c r="E347" s="2" t="inlineStr">
-        <is>
-          <t>・Mỗi biến thể: trạng thái Chưa xét được; dấu/lọc đỏ cũ ngừng ở cả ba đầu ra; điểm S01 vẫn 29; không đi xuống quy tắc thấp hơn; không bật lại ngưỡng cũ `red_score`.</t>
-        </is>
-      </c>
-    </row>
     <row r="348">
-      <c r="D348" s="1" t="inlineStr">
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>・S01 Không đỏ; không cần bật một chế độ thủ công/tự động riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="D349" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="E349" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Đã xét lại nhưng không tạo được ngưỡng hợp lệ thì dùng kết quả cũ không?” (Q26); đặc tả v2 (R18) mục 8.2 “Bảng chuyển trạng thái” dòng 4, mục 8.3 “Không tạo được ngưỡng hợp lệ”; Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7047) 「処理が完了しました。判定できない項目は判定不能とし、旧結果を停止しました。」 (xử lý xong; mục không xét được chuyển thành Không xét được（判定不能） và ngừng kết quả cũ), (58:7066) (file cũ 4592:2537, 4592:2554 ghi 未判定 (chưa xét))</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh đầu ra trước/sau; ảnh thông báo; ảnh điểm. SELECT `judgment_status`/`reason_code` (khi có schema; thiết kế DB v2 mục 4.3 “Trạng thái kết quả”, PROPOSED).</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Khi nào xét điểm đỏ và có cần chế độ thủ công/tự động riêng không?” (Q11) (ví dụ 29→40); đặc tả v2 (R18) mục 8.2 “Bảng chuyển trạng thái” dòng 3</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>・Ghi chú: (b) phụ thuộc cách tạo M không hợp lệ.</t>
+          <t>・Bằng chứng cần chụp: Ảnh trước/sau.</t>
         </is>
       </c>
     </row>
@@ -10581,14 +10581,14 @@
     <row r="358">
       <c r="C358" s="1" t="inlineStr">
         <is>
-          <t>18. TC-RS-BR-018 — Đổi phạm vi làm ô không còn quy tắc áp dụng: giữ khi chưa chạy; chạy lại → Không áp dụng</t>
+          <t>18. TC-RS-BR-017 — Chạy lại không tạo được ngưỡng hợp lệ → Chưa xét được, ngừng kết quả cũ, giữ điểm</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giữ kết quả trước khi chạy lại” (AC-G21)</t>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Trạng thái sau lần chạy” (AC-G20)</t>
         </is>
       </c>
     </row>
@@ -10602,14 +10602,14 @@
     <row r="361">
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: Quy tắc lọc lớp G-A; S01 (G-A) = 29 Đỏ.</t>
+          <t>・Điều kiện: Ô S01=29 Đỏ theo công thức `A×0.5` (nguồn bản tổng hợp mới nhất chưa chốt (trung bình 62)).</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: học sinh S01 (điểm 29)</t>
+          <t>・Dữ liệu test: mục có M không hợp lệ, quy tắc công thức 100 ÷ trung bình, bản tổng hợp mới nhất chưa chốt (trung bình 62); học sinh S01 (điểm 29), nguồn chưa có kết quả tổng hợp</t>
         </is>
       </c>
     </row>
@@ -10623,143 +10623,143 @@
     <row r="364">
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>1. Đổi bộ lọc sang lớp G-B, lưu. Xem đầu ra.</t>
+          <t>1. Biến thể (a): đổi nguồn sang nguồn chưa có kết quả tổng hợp (không có tổng hợp), lưu, chạy lại.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>2. Chạy lại. Xem đầu ra.</t>
+          <t>2. Biến thể (b): quy tắc tỷ lệ với M không hợp lệ (mục có M không hợp lệ), chạy lại.</t>
         </is>
       </c>
     </row>
     <row r="366">
-      <c r="D366" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>3. Biến thể (c): quy tắc công thức 100 ÷ trung bình với `A=0`, chạy lại.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>1. S01 vẫn Đỏ (kết quả trước).</t>
+          <t>4. Sau mỗi biến thể: xem ba đầu ra và điểm S01.</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="E368" s="2" t="inlineStr">
-        <is>
-          <t>2. S01 Không áp dụng; ngừng dấu/lọc đỏ cũ; điểm giữ nguyên.</t>
+      <c r="D368" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="D369" s="1" t="inlineStr">
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>・Mỗi biến thể: trạng thái Chưa xét được; dấu/lọc đỏ cũ ngừng ở cả ba đầu ra; điểm S01 vẫn 29; không đi xuống quy tắc thấp hơn; không bật lại ngưỡng cũ `red_score`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="D370" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="E370" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Xét lại xong mà không còn thiết lập áp dụng thì làm gì?” (Q27); đặc tả v2 (R18) mục 8.2 “Bảng chuyển trạng thái” dòng 5–6; Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7067) 「再実行で適用条件なし：旧結果を停止し対象外。点数は残す。」 (chạy lại mà không có điều kiện áp dụng: ngừng kết quả cũ, ngoài đối tượng, giữ điểm)</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh đầu ra hai lần.</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Đã xét lại nhưng không tạo được ngưỡng hợp lệ thì dùng kết quả cũ không?” (Q26); đặc tả v2 (R18) mục 8.2 “Bảng chuyển trạng thái” dòng 4, mục 8.3 “Không tạo được ngưỡng hợp lệ”; Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7047) 「処理が完了しました。判定できない項目は判定不能とし、旧結果を停止しました。」 (xử lý xong; mục không xét được chuyển thành Không xét được（判定不能） và ngừng kết quả cũ), (58:7066) (file cũ 4592:2537, 4592:2554 ghi 未判定 (chưa xét))</t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="D372" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh đầu ra trước/sau; ảnh thông báo; ảnh điểm. SELECT `judgment_status`/`reason_code` (khi có schema; thiết kế DB v2 mục 4.3 “Trạng thái kết quả”, PROPOSED).</t>
         </is>
       </c>
     </row>
     <row r="373">
-      <c r="E373" s="2" t="n"/>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: (b) phụ thuộc cách tạo M không hợp lệ.</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="D374" s="1" t="inlineStr">
         <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="E375" s="2" t="n"/>
+    </row>
+    <row r="376">
+      <c r="D376" s="1" t="inlineStr">
+        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="378">
-      <c r="C378" s="1" t="inlineStr">
-        <is>
-          <t>19. TC-RS-BR-019 — Xóa quy tắc cuối: giữ kết quả tới lần chạy lại; chạy lại → Không áp dụng</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="D379" s="3" t="inlineStr">
+    <row r="380">
+      <c r="C380" s="1" t="inlineStr">
+        <is>
+          <t>19. TC-RS-BR-018 — Đổi phạm vi làm ô không còn quy tắc áp dụng: giữ khi chưa chạy; chạy lại → Không áp dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="D381" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giữ kết quả trước khi chạy lại” (AC-G21)</t>
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="D380" s="1" t="inlineStr">
+    <row r="382">
+      <c r="D382" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
-    <row r="381">
-      <c r="E381" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: mục số nguyên (M=100) chỉ có quy tắc “Cố định 30” (dưới 30); S01=29 Đỏ. Trích xuất cấu hình trích xuất: lọc, ký hiệu “*” phía trước, tô màu, công khai `*` trước, phiếu cấu hình phiếu điểm: ký tự “※” phía trước đã cấu hình.</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="E382" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: mục số nguyên (M=100), quy tắc “Cố định 30” (dưới 30); học sinh S01 (điểm 29), cấu hình trích xuất: lọc, ký hiệu “*” phía trước, tô màu, cấu hình công khai: “*” phía trước, cấu hình phiếu điểm: ký tự “※” phía trước</t>
-        </is>
-      </c>
-    </row>
     <row r="383">
-      <c r="D383" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: Quy tắc lọc lớp G-A; S01 (G-A) = 29 Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>1. Xóa quy tắc “Cố định 30” (dưới 30) (quy tắc cuối).</t>
+          <t>・Dữ liệu test: học sinh S01 (điểm 29)</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="E385" s="2" t="inlineStr">
-        <is>
-          <t>2. Xem ba đầu ra.</t>
+      <c r="D385" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>3. Chạy lại bằng đăng ký điểm lớp G-A hoặc chạy hàng loạt.</t>
+          <t>1. Đổi bộ lọc sang lớp G-B, lưu. Xem đầu ra.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>4. Xem ba đầu ra và cấu hình trình bày đầu ra.</t>
+          <t>2. Chạy lại. Xem đầu ra.</t>
         </is>
       </c>
     </row>
@@ -10773,14 +10773,14 @@
     <row r="389">
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>・1–2. Danh sách rỗng nhưng S01 vẫn hiện dấu đỏ/thỏa lọc ở ba đầu ra.</t>
+          <t>1. S01 vẫn Đỏ (kết quả trước).</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>・3–4. Lần chạy xét cả mục đã hết quy tắc: S01 Không áp dụng, ngừng dấu/lọc; điểm giữ nguyên. Cấu hình trình bày đỏ đã lưu ở đầu ra không bị xóa như tác dụng phụ.</t>
+          <t>2. S01 Không áp dụng; ngừng dấu/lọc đỏ cũ; điểm giữ nguyên.</t>
         </is>
       </c>
     </row>
@@ -10794,258 +10794,258 @@
     <row r="392">
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Xóa thiết lập cuối cùng thì dấu đỏ mất ngay hay chờ chạy lại?” (Q28); đặc tả v2 (R18) mục 4.1 “Điểm vào và trạng thái trống”, mục 4.4 “Lưu, đổi thứ tự và xóa”, mục 8.2 “Bảng chuyển trạng thái” dòng 7–8, mục 10.1 “Phạm vi và tùy chọn”; Figma MW “chương 01 – lối vào, danh sách, xóa thiết lập” (58:9618) 「削除後も再実行まで前回結果を使用します。」 (sau khi xóa vẫn dùng kết quả trước tới khi chạy lại), “chương 05 – trích xuất thành tích và kết quả Excel” (58:6248), “chương 06 – công khai thành tích và màn học sinh” (58:5598)</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Xét lại xong mà không còn thiết lập áp dụng thì làm gì?” (Q27); đặc tả v2 (R18) mục 8.2 “Bảng chuyển trạng thái” dòng 5–6; Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7067) 「再実行で適用条件なし：旧結果を停止し対象外。点数は残す。」 (chạy lại mà không có điều kiện áp dụng: ngừng kết quả cũ, ngoài đối tượng, giữ điểm)</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh/file ba đầu ra ở bước 2 và 4; ảnh cấu hình đầu ra sau bước 4.</t>
+          <t>・Bằng chứng cần chụp: Ảnh đầu ra hai lần.</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="E394" s="2" t="inlineStr">
-        <is>
-          <t>・Ghi chú: Trường không có tính tự động: chạy lại bằng thao tác hàng loạt hiện có (case “Trường chỉ có quy tắc đỏ (không có tính tự động) vẫn có đường chạy hàng loạt”). Xóa là xóa mềm (`active=0`) và kết quả giữ đến lần xét tiếp theo (thiết kế DB v2 mục 4.1 “Loại ngưỡng và tính hợp lệ”, mục 4.4 “Cập nhật và hiệu lực kết quả” — PROPOSED); có thể SELECT làm bằng chứng. Kiểm thêm (PROPOSED, khi có schema): sau bước 1, tạo một quy tắc mới → quy tắc mới có ID mới, không dùng lại ID đã xóa; kết quả cũ vẫn trỏ ID cũ (thiết kế DB v2: "không tái sử dụng ID cho quy tắc khác").</t>
+      <c r="D394" s="1" t="inlineStr">
+        <is>
+          <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="D395" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
-        </is>
-      </c>
+      <c r="E395" s="2" t="n"/>
     </row>
     <row r="396">
-      <c r="E396" s="2" t="n"/>
-    </row>
-    <row r="397">
-      <c r="D397" s="1" t="inlineStr">
+      <c r="D396" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
+    <row r="400">
+      <c r="C400" s="1" t="inlineStr">
+        <is>
+          <t>20. TC-RS-BR-019 — Xóa quy tắc cuối: giữ kết quả tới lần chạy lại; chạy lại → Không áp dụng</t>
+        </is>
+      </c>
+    </row>
     <row r="401">
-      <c r="C401" s="1" t="inlineStr">
-        <is>
-          <t>20. TC-RS-BR-020 — Xóa điểm thành trống → Không có điểm, bỏ dấu đỏ cũ</t>
+      <c r="D401" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giữ kết quả trước khi chạy lại” (AC-G21)</t>
         </is>
       </c>
     </row>
     <row r="402">
-      <c r="D402" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Dùng điểm cuối cùng” (AC-G19)</t>
+      <c r="D402" s="1" t="inlineStr">
+        <is>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="403">
-      <c r="D403" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: mục số nguyên (M=100) chỉ có quy tắc “Cố định 30” (dưới 30); S01=29 Đỏ. Trích xuất cấu hình trích xuất: lọc, ký hiệu “*” phía trước, tô màu, công khai `*` trước, phiếu cấu hình phiếu điểm: ký tự “※” phía trước đã cấu hình.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: S01=29 Đỏ.</t>
+          <t>・Dữ liệu test: mục số nguyên (M=100), quy tắc “Cố định 30” (dưới 30); học sinh S01 (điểm 29), cấu hình trích xuất: lọc, ký hiệu “*” phía trước, tô màu, cấu hình công khai: “*” phía trước, cấu hình phiếu điểm: ký tự “※” phía trước</t>
         </is>
       </c>
     </row>
     <row r="405">
-      <c r="E405" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: học sinh S01 (điểm 29), cấu hình trích xuất: lọc, ký hiệu “*” phía trước, tô màu</t>
+      <c r="D405" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="406">
-      <c r="D406" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>1. Xóa quy tắc “Cố định 30” (dưới 30) (quy tắc cuối).</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>1. Xóa điểm S01 thành trống, lưu.</t>
+          <t>2. Xem ba đầu ra.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>2. Xem ba đầu ra, chạy trích xuất có lọc đỏ.</t>
+          <t>3. Chạy lại bằng đăng ký điểm lớp G-A hoặc chạy hàng loạt.</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="D409" s="1" t="inlineStr">
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>4. Xem ba đầu ra và cấu hình trình bày đầu ra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="D410" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
-    <row r="410">
-      <c r="E410" s="2" t="inlineStr">
-        <is>
-          <t>・S01 Không có điểm; không còn dấu đỏ; không thỏa lọc đỏ nhờ ô này. Không cần chờ chạy lại.</t>
-        </is>
-      </c>
-    </row>
     <row r="411">
-      <c r="D411" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>・1–2. Danh sách rỗng nhưng S01 vẫn hiện dấu đỏ/thỏa lọc ở ba đầu ra.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 7.1 “Trình tự cho một ô” bước 2, mục 7.2 “Bảng sự kiện” (Xóa điểm số thành trống), mục 8.2 “Bảng chuyển trạng thái” dòng 9; Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Dùng điểm nào để xét, và phân biệt điểm 0 với ô trống thế nào?” (Q3)</t>
+          <t>・3–4. Lần chạy xét cả mục đã hết quy tắc: S01 Không áp dụng, ngừng dấu/lọc; điểm giữ nguyên. Cấu hình trình bày đỏ đã lưu ở đầu ra không bị xóa như tác dụng phụ.</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="E413" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: Ảnh/file đầu ra.</t>
+      <c r="D413" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="414">
-      <c r="D414" s="1" t="inlineStr">
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Xóa thiết lập cuối cùng thì dấu đỏ mất ngay hay chờ chạy lại?” (Q28); đặc tả v2 (R18) mục 4.1 “Điểm vào và trạng thái trống”, mục 4.4 “Lưu, đổi thứ tự và xóa”, mục 8.2 “Bảng chuyển trạng thái” dòng 7–8, mục 10.1 “Phạm vi và tùy chọn”; Figma MW “chương 01 – lối vào, danh sách, xóa thiết lập” (58:9618) 「削除後も再実行まで前回結果を使用します。」 (sau khi xóa vẫn dùng kết quả trước tới khi chạy lại), “chương 05 – trích xuất thành tích và kết quả Excel” (58:6248), “chương 06 – công khai thành tích và màn học sinh” (58:5598)</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh/file ba đầu ra ở bước 2 và 4; ảnh cấu hình đầu ra sau bước 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: Trường không có tính tự động: chạy lại bằng thao tác hàng loạt hiện có (case “Trường chỉ có quy tắc đỏ (không có tính tự động) vẫn có đường chạy hàng loạt”). Xóa chuyển `setting_status=2` trong cùng transaction; kết quả giữ đến lần xét tiếp theo (thiết kế DB v2 mục 4.1 và 4.4 — PROPOSED); có thể SELECT làm bằng chứng. Không dùng kiểm tra truthy/khác 0 để xác định rule có hiệu lực. Kiểm thêm (PROPOSED, khi có schema): sau bước 1, tạo một quy tắc mới → quy tắc mới có ID mới, không dùng lại ID đã xóa; kết quả cũ vẫn trỏ ID cũ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="D417" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="E415" s="2" t="n"/>
-    </row>
-    <row r="416">
-      <c r="D416" s="1" t="inlineStr">
+    <row r="418">
+      <c r="E418" s="2" t="n"/>
+    </row>
+    <row r="419">
+      <c r="D419" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="420">
-      <c r="C420" s="1" t="inlineStr">
-        <is>
-          <t>21. TC-RS-BR-021 — Tổng hợp lại hoặc đổi nhóm tham chiếu không tự xét lại</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="D421" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Thứ tự đánh giá tương đối” (AC-G25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="D422" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
     <row r="423">
-      <c r="E423" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Công thức `A×0.5`, `A=50` → `T=25`; học sinh điểm 24 Đỏ.</t>
+      <c r="C423" s="1" t="inlineStr">
+        <is>
+          <t>21. TC-RS-BR-020 — Xóa điểm thành trống → Không có điểm, bỏ dấu đỏ cũ</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="E424" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: bản tổng hợp mới nhất chưa chốt (trung bình 62)</t>
+      <c r="D424" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Dùng điểm cuối cùng” (AC-G19)</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="D425" s="1" t="inlineStr">
         <is>
-          <t>操作（Thao tác）</t>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>1. Sửa điểm nhóm để trung bình mới là 40, bấm Thực hiện tổng hợp（集計実行）.</t>
+          <t>・Điều kiện: S01=29 Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>2. Xem kết quả học sinh 24.</t>
+          <t>・Dữ liệu test: học sinh S01 (điểm 29), cấu hình trích xuất: lọc, ký hiệu “*” phía trước, tô màu</t>
         </is>
       </c>
     </row>
     <row r="428">
-      <c r="E428" s="2" t="inlineStr">
-        <is>
-          <t>3. Bấm Thực hiện tính toán tự động（自動算出実行）, xem lại.</t>
+      <c r="D428" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="429">
-      <c r="D429" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>1. Xóa điểm S01 thành trống, lưu.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>・1–2. Vẫn Đỏ theo kết quả trước (không tự xét lại).</t>
+          <t>2. Xem ba đầu ra, chạy trích xuất có lọc đỏ.</t>
         </is>
       </c>
     </row>
     <row r="431">
-      <c r="E431" s="2" t="inlineStr">
-        <is>
-          <t>3. `A=40` → `T=20` → 24 Không đỏ.</t>
+      <c r="D431" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="432">
-      <c r="D432" s="1" t="inlineStr">
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>・S01 Không có điểm; không còn dấu đỏ; không thỏa lọc đỏ nhờ ô này. Không cần chờ chạy lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="D433" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="E433" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lưu điều kiện hoặc thay nguồn có cập nhật ngay kết quả không?” (Q13); đặc tả v2 (R18) mục 7.2 “Bảng sự kiện” (Tổng hợp lại/cập nhật nhóm tham chiếu)</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả sau mỗi bước.</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 7.1 “Trình tự cho một ô” bước 2, mục 7.2 “Bảng sự kiện” (Xóa điểm số thành trống), mục 8.2 “Bảng chuyển trạng thái” dòng 9; Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Dùng điểm nào để xét, và phân biệt điểm 0 với ô trống thế nào?” (Q3)</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>・Ghi chú: Nếu có bản chốt cùng phạm vi, bước 3 vẫn dùng bản chốt (case “Nguồn: bản đã chốt được ưu tiên hơn tổng hợp mới hơn”).</t>
+          <t>・Bằng chứng cần chụp: Ảnh/file đầu ra.</t>
         </is>
       </c>
     </row>
@@ -11069,14 +11069,14 @@
     <row r="442">
       <c r="C442" s="1" t="inlineStr">
         <is>
-          <t>22. TC-RS-BR-022 — Đổi M ở Thiết lập điểm tối đa（満点設定） hoặc Giá trị tối đa（最大値） không tự xét lại</t>
+          <t>22. TC-RS-BR-021 — Tổng hợp lại hoặc đổi nhóm tham chiếu không tự xét lại</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="D443" s="3" t="inlineStr">
         <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Trigger khi đổi điểm tối đa/đơn vị” (AC-G24)</t>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Thứ tự đánh giá tương đối” (AC-G25)</t>
         </is>
       </c>
     </row>
@@ -11090,14 +11090,14 @@
     <row r="445">
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: mục số nguyên (M=100) có quy tắc tỷ lệ 30% (30%); S03 = 31, `M=100` → `T=30` → Không đỏ.</t>
+          <t>・Điều kiện: Công thức `A×0.5`, `A=50` → `T=25`; học sinh điểm 24 Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: mục số nguyên (M=100); quy tắc tỷ lệ 30%</t>
+          <t>・Dữ liệu test: bản tổng hợp mới nhất chưa chốt (trung bình 62)</t>
         </is>
       </c>
     </row>
@@ -11111,21 +11111,21 @@
     <row r="448">
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>1. Sửa Giá trị tối đa（最大値） của mục số nguyên (M=100) ở Thiết lập ô nhập（入力欄設定） thành 200, lưu. Xem kết quả.</t>
+          <t>1. Sửa điểm nhóm để trung bình mới là 40, bấm Thực hiện tổng hợp（集計実行）.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>2. Lưu một định nghĩa lựa chọn ở Thiết lập điểm tối đa（満点設定） (`/admin/grade_report_setting/manage/detail/option/register/change_max_score`) (chưa gán cho lớp). Xem kết quả.</t>
+          <t>2. Xem kết quả học sinh 24.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>3. Đăng ký lại điểm S03. Xem kết quả.</t>
+          <t>3. Bấm Thực hiện tính toán tự động（自動算出実行）, xem lại.</t>
         </is>
       </c>
     </row>
@@ -11139,14 +11139,14 @@
     <row r="452">
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>・1–2. S03 vẫn Không đỏ (kết quả trước).</t>
+          <t>・1–2. Vẫn Đỏ theo kết quả trước (không tự xét lại).</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>3. `M=200` → `T=60` → S03=31 Đỏ.</t>
+          <t>3. `A=40` → `T=20` → 24 Không đỏ.</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
     <row r="455">
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Thay điểm tối đa thì xử lý thế nào?” (Q14), câu “Những đường đổi điểm tối đa nào hiện chạy tính tự động?” (Q20); đặc tả v2 (R18) mục 7.3 “Thay đổi điểm tối đa”; Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7069) 「定義としての満点設定保存と、授業の選択肢保存・成績登録は別の操作。」 (lưu định nghĩa điểm tối đa khác với lưu lựa chọn lớp/đăng ký điểm); CODE `itemStore`, `optionStore`</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Lưu điều kiện hoặc thay nguồn có cập nhật ngay kết quả không?” (Q13); đặc tả v2 (R18) mục 7.2 “Bảng sự kiện” (Tổng hợp lại/cập nhật nhóm tham chiếu)</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
     <row r="457">
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>・Sau khi chạy: Trả M về 100.</t>
+          <t>・Ghi chú: Nếu có bản chốt cùng phạm vi, bước 3 vẫn dùng bản chốt (case “Nguồn: bản đã chốt được ưu tiên hơn tổng hợp mới hơn”).</t>
         </is>
       </c>
     </row>
@@ -11198,14 +11198,14 @@
     <row r="464">
       <c r="C464" s="1" t="inlineStr">
         <is>
-          <t>23. TC-RS-BR-023 — Nút xanh Thực hiện tổng hợp（集計実行） không xét điểm đỏ</t>
+          <t>23. TC-RS-BR-022 — Đổi M ở Thiết lập điểm tối đa（満点設定） hoặc Giá trị tối đa（最大値） không tự xét lại</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="D465" s="3" t="inlineStr">
         <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Thứ tự đánh giá tương đối” (AC-G25)</t>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Trigger khi đổi điểm tối đa/đơn vị” (AC-G24)</t>
         </is>
       </c>
     </row>
@@ -11219,14 +11219,14 @@
     <row r="467">
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30) vừa đổi từ 30 thành 35 và lưu; S03=32 Không đỏ (kết quả trước).</t>
+          <t>・Điều kiện: mục số nguyên (M=100) có quy tắc tỷ lệ 30% (30%); S03 = 31, `M=100` → `T=30` → Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30)</t>
+          <t>・Dữ liệu test: mục số nguyên (M=100); quy tắc tỷ lệ 30%</t>
         </is>
       </c>
     </row>
@@ -11240,638 +11240,638 @@
     <row r="470">
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>1. Bấm Thực hiện tổng hợp（集計実行）, chờ hoàn tất.</t>
+          <t>1. Sửa Giá trị tối đa（最大値） của mục số nguyên (M=100) ở Thiết lập ô nhập（入力欄設定） thành 200, lưu. Xem kết quả.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>2. Xem kết quả S03.</t>
+          <t>2. Lưu một định nghĩa lựa chọn ở Thiết lập điểm tối đa（満点設定） (`/admin/grade_report_setting/manage/detail/option/register/change_max_score`) (chưa gán cho lớp). Xem kết quả.</t>
         </is>
       </c>
     </row>
     <row r="472">
-      <c r="D472" s="1" t="inlineStr">
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>3. Đăng ký lại điểm S03. Xem kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="D473" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
-    <row r="473">
-      <c r="E473" s="2" t="inlineStr">
-        <is>
-          <t>・S03 vẫn Không đỏ.</t>
-        </is>
-      </c>
-    </row>
     <row r="474">
-      <c r="D474" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>・1–2. S03 vẫn Không đỏ (kết quả trước).</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Quy trình vận hành khi có đánh giá tương đối là gì?” (Q12) ("chạy nút xanh không tự chứng minh đã cập nhật kết quả đỏ"); CODE đường ghi điểm “Nút xanh 集計実行 (chạy tổng hợp – nút xanh dương)”</t>
+          <t>3. `M=200` → `T=60` → S03=31 Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="476">
-      <c r="E476" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: Ảnh Trích xuất（tài liệu “Chiến lược kiểm thử” mục 9 “Quy ước thực thi chung”） dòng S03 sau khi tổng hợp xong; ảnh thời điểm chạy trên màn Tổng hợp thành tích（成績集計）.</t>
+      <c r="D476" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="477">
-      <c r="D477" s="1" t="inlineStr">
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Thay điểm tối đa thì xử lý thế nào?” (Q14), câu “Những đường đổi điểm tối đa nào hiện chạy tính tự động?” (Q20); đặc tả v2 (R18) mục 7.3 “Thay đổi điểm tối đa”; Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7069) 「定義としての満点設定保存と、授業の選択肢保存・成績登録は別の操作。」 (lưu định nghĩa điểm tối đa khác với lưu lựa chọn lớp/đăng ký điểm); CODE `itemStore`, `optionStore`</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả sau mỗi bước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>・Sau khi chạy: Trả M về 100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="D480" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="478">
-      <c r="E478" s="2" t="n"/>
-    </row>
-    <row r="479">
-      <c r="D479" s="1" t="inlineStr">
+    <row r="481">
+      <c r="E481" s="2" t="n"/>
+    </row>
+    <row r="482">
+      <c r="D482" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="483">
-      <c r="C483" s="1" t="inlineStr">
-        <is>
-          <t>24. TC-RS-BR-024 — Xem, xuất, công khai, in lại không kích hoạt xét</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="D484" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Xem/xuất không tự xét” (AC-G28)</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="D485" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
     <row r="486">
-      <c r="E486" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Như case “Lưu cấu hình không xét; kết quả trước giữ tới lần chạy lại” bước 1 (đã lưu `&lt;35`, chưa chạy lại; S03=32 Không đỏ).</t>
+      <c r="C486" s="1" t="inlineStr">
+        <is>
+          <t>24. TC-RS-BR-023 — Nút xanh Thực hiện tổng hợp（集計実行） không xét điểm đỏ</t>
         </is>
       </c>
     </row>
     <row r="487">
-      <c r="E487" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: cấu hình trích xuất: lọc, ký hiệu “*” phía trước, tô màu, cấu hình công khai: “*” phía trước, cấu hình phiếu điểm: ký tự “※” phía trước</t>
+      <c r="D487" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Thứ tự đánh giá tương đối” (AC-G25)</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="D488" s="1" t="inlineStr">
         <is>
-          <t>操作（Thao tác）</t>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>1. Chạy trích xuất, xuất Excel.</t>
+          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30) vừa đổi từ 30 thành 35 và lưu; S03=32 Không đỏ (kết quả trước).</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>2. Mở màn công khai học sinh, tải PDF công khai.</t>
+          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30)</t>
         </is>
       </c>
     </row>
     <row r="491">
-      <c r="E491" s="2" t="inlineStr">
-        <is>
-          <t>3. Xuất PDF phiếu.</t>
+      <c r="D491" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="492">
-      <c r="D492" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>1. Bấm Thực hiện tổng hợp（集計実行）, chờ hoàn tất.</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>・S03 vẫn Không đỏ ở mọi đầu ra; không có lượt xét mới (thời điểm kết quả không đổi); không có lượt tổng hợp mới (lượt/thời điểm tổng hợp mới nhất không đổi).</t>
+          <t>2. Xem kết quả S03.</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="D494" s="1" t="inlineStr">
         <is>
-          <t>補足（Bổ sung）</t>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Ba đầu ra có dùng chung kết quả và tự xét khi xem lại không?” (Q16); đặc tả v2 (R18) mục 7.2 “Bảng sự kiện” (dòng cuối), mục 9.3 “Xuất file”, mục 10.3 “Quyền, thời điểm và đầu ra liên quan”; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Xem/xuất không tự xét” (AC-G28) ("không xét lại hoặc tổng hợp lại"); Figma MW “chương 00 – hướng dẫn đọc và luồng tổng thể” (58:10202) 「閲覧・出力だけでは再判定しない。」 (chỉ xem/xuất thì không xét lại), “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7060)</t>
+          <t>・S03 vẫn Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="496">
-      <c r="E496" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: File/ảnh đầu ra; bằng chứng thời điểm cập nhật kết quả và lượt tổng hợp mới nhất không đổi trước/sau (khi có schema).</t>
+      <c r="D496" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="497">
-      <c r="D497" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Quy trình vận hành khi có đánh giá tương đối là gì?” (Q12) ("chạy nút xanh không tự chứng minh đã cập nhật kết quả đỏ"); CODE đường ghi điểm “Nút xanh 集計実行 (chạy tổng hợp – nút xanh dương)”</t>
         </is>
       </c>
     </row>
     <row r="498">
-      <c r="E498" s="2" t="n"/>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh Trích xuất（tài liệu “Chiến lược kiểm thử” mục 9 “Quy ước thực thi chung”） dòng S03 sau khi tổng hợp xong; ảnh thời điểm chạy trên màn Tổng hợp thành tích（成績集計）.</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="D499" s="1" t="inlineStr">
         <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="E500" s="2" t="n"/>
+    </row>
+    <row r="501">
+      <c r="D501" s="1" t="inlineStr">
+        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="503">
-      <c r="C503" s="1" t="inlineStr">
-        <is>
-          <t>25. TC-RS-BR-025 — Đầu ra không bị chặn vì chưa có hoặc chưa xét được kết quả đỏ</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="D504" s="3" t="inlineStr">
+    <row r="505">
+      <c r="C505" s="1" t="inlineStr">
+        <is>
+          <t>25. TC-RS-BR-024 — Xem, xuất, công khai, in lại không kích hoạt xét</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="D506" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Xem/xuất không tự xét” (AC-G28)</t>
         </is>
       </c>
     </row>
-    <row r="505">
-      <c r="D505" s="1" t="inlineStr">
+    <row r="507">
+      <c r="D507" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
-    <row r="506">
-      <c r="E506" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Một số ô Chưa từng xét, một số Chưa xét được.</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="E507" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: cấu hình trích xuất: lọc, ký hiệu “*” phía trước, tô màu, cấu hình công khai: “*” phía trước, cấu hình phiếu điểm: ký tự “※” phía trước</t>
-        </is>
-      </c>
-    </row>
     <row r="508">
-      <c r="D508" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: Như case “Lưu cấu hình không xét; kết quả trước giữ tới lần chạy lại” bước 1 (đã lưu `&lt;35`, chưa chạy lại; S03=32 Không đỏ).</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>1. Chạy trích xuất và xuất Excel.</t>
+          <t>・Dữ liệu test: cấu hình trích xuất: lọc, ký hiệu “*” phía trước, tô màu, cấu hình công khai: “*” phía trước, cấu hình phiếu điểm: ký tự “※” phía trước</t>
         </is>
       </c>
     </row>
     <row r="510">
-      <c r="E510" s="2" t="inlineStr">
-        <is>
-          <t>2. Công khai cho học sinh, xem màn học sinh.</t>
+      <c r="D510" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>3. Xuất PDF phiếu.</t>
+          <t>1. Chạy trích xuất, xuất Excel.</t>
         </is>
       </c>
     </row>
     <row r="512">
-      <c r="D512" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>2. Mở màn công khai học sinh, tải PDF công khai.</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>・Mọi thao tác hoàn tất bình thường; ô chưa có kết quả không có dấu đỏ và hiển thị theo thiết lập hiện hữu. Quyền, lịch công khai, điều kiện ẩn hiện có vẫn giữ.</t>
+          <t>3. Xuất PDF phiếu.</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="D514" s="1" t="inlineStr">
         <is>
-          <t>補足（Bổ sung）</t>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="E515" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Thiếu dữ liệu xét có chặn công khai hoặc phát hành không?” (Q15); đặc tả v2 (R18) mục 8.4 “Lỗi kỹ thuật và thông báo” (đoạn cuối); Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7068) 「未判定だけを理由に公開・帳票発行を止めない。」 (không dừng công khai/phát hành phiếu chỉ vì chưa xét được)</t>
+          <t>・S03 vẫn Không đỏ ở mọi đầu ra; không có lượt xét mới (thời điểm kết quả không đổi); không có lượt tổng hợp mới (lượt/thời điểm tổng hợp mới nhất không đổi).</t>
         </is>
       </c>
     </row>
     <row r="516">
-      <c r="E516" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: Ảnh/file đầu ra.</t>
+      <c r="D516" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="517">
-      <c r="D517" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Ba đầu ra có dùng chung kết quả và tự xét khi xem lại không?” (Q16); đặc tả v2 (R18) mục 7.2 “Bảng sự kiện” (dòng cuối), mục 9.3 “Xuất file”, mục 10.3 “Quyền, thời điểm và đầu ra liên quan”; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Xem/xuất không tự xét” (AC-G28) ("không xét lại hoặc tổng hợp lại"); Figma MW “chương 00 – hướng dẫn đọc và luồng tổng thể” (58:10202) 「閲覧・出力だけでは再判定しない。」 (chỉ xem/xuất thì không xét lại), “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7060)</t>
         </is>
       </c>
     </row>
     <row r="518">
-      <c r="E518" s="2" t="n"/>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: File/ảnh đầu ra; bằng chứng thời điểm cập nhật kết quả và lượt tổng hợp mới nhất không đổi trước/sau (khi có schema).</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="D519" s="1" t="inlineStr">
         <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="E520" s="2" t="n"/>
+    </row>
+    <row r="521">
+      <c r="D521" s="1" t="inlineStr">
+        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="523">
-      <c r="C523" s="1" t="inlineStr">
-        <is>
-          <t>26. TC-RS-BR-026 — Không chuyển đổi và không dùng ngưỡng đỏ cũ（`red_score`） làm fallback</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="D524" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Bảo toàn điểm đỏ cũ” (AC-G38)</t>
-        </is>
-      </c>
-    </row>
     <row r="525">
-      <c r="D525" s="1" t="inlineStr">
+      <c r="C525" s="1" t="inlineStr">
+        <is>
+          <t>26. TC-RS-BR-025 — Đầu ra không bị chặn vì chưa có hoặc chưa xét được kết quả đỏ</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="D526" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Xem/xuất không tự xét” (AC-G28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="D527" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
-    <row r="526">
-      <c r="E526" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: mục số nguyên (M=100) có `red_score`=30 ở DB (nếu dữ liệu cho phép).</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="E527" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: mục số nguyên (M=100), nguồn chưa có kết quả tổng hợp; quyền đọc DB local (chỉ SELECT/SHOW), học sinh S01 (điểm 29)</t>
-        </is>
-      </c>
-    </row>
     <row r="528">
-      <c r="D528" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: Một số ô Chưa từng xét, một số Chưa xét được.</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="E529" s="2" t="inlineStr">
         <is>
-          <t>1. Không có quy tắc mới: đăng ký S01=29, xem đầu ra.</t>
+          <t>・Dữ liệu test: cấu hình trích xuất: lọc, ký hiệu “*” phía trước, tô màu, cấu hình công khai: “*” phía trước, cấu hình phiếu điểm: ký tự “※” phía trước</t>
         </is>
       </c>
     </row>
     <row r="530">
-      <c r="E530" s="2" t="inlineStr">
-        <is>
-          <t>2. Có quy tắc không khớp S01 (lọc lớp G-B): chạy lại, xem.</t>
+      <c r="D530" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="E531" s="2" t="inlineStr">
         <is>
-          <t>3. Có quy tắc thiếu dữ liệu (nguồn chưa có kết quả tổng hợp): chạy lại, xem.</t>
+          <t>1. Chạy trích xuất và xuất Excel.</t>
         </is>
       </c>
     </row>
     <row r="532">
-      <c r="D532" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>2. Công khai cho học sinh, xem màn học sinh.</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="E533" s="2" t="inlineStr">
         <is>
-          <t>・Cả ba bước: S01 không có dấu đỏ từ `red_score`; trạng thái tương ứng lần lượt là không có quy tắc / Không áp dụng / Chưa xét được.</t>
+          <t>3. Xuất PDF phiếu.</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="D534" s="1" t="inlineStr">
         <is>
-          <t>補足（Bổ sung）</t>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="E535" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Có chuyển thiết lập điểm đỏ cũ sang chức năng mới không?” (Q17); đặc tả v2 (R18) mục 8.3 “Không tạo được ngưỡng hợp lệ”, mục 12.3 “Không chuyển đổi dữ liệu đỏ cũ”; code hiện tại “`red_score`, `changed_red_score`”</t>
+          <t>・Mọi thao tác hoàn tất bình thường; ô chưa có kết quả không có dấu đỏ và hiển thị theo thiết lập hiện hữu. Quyền, lịch công khai, điều kiện ẩn hiện có vẫn giữ.</t>
         </is>
       </c>
     </row>
     <row r="536">
-      <c r="E536" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: SELECT `red_score`; ảnh đầu ra ba bước.</t>
+      <c r="D536" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="E537" s="2" t="inlineStr">
         <is>
-          <t>・Sau khi chạy: `red_score` không đổi (case “Cột ngưỡng cũ không bị chuyển đổi hay xóa”).</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Thiếu dữ liệu xét có chặn công khai hoặc phát hành không?” (Q15); đặc tả v2 (R18) mục 8.4 “Lỗi kỹ thuật và thông báo” (đoạn cuối); Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:7068) 「未判定だけを理由に公開・帳票発行を止めない。」 (không dừng công khai/phát hành phiếu chỉ vì chưa xét được)</t>
         </is>
       </c>
     </row>
     <row r="538">
-      <c r="D538" s="1" t="inlineStr">
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh/file đầu ra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="D539" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="539">
-      <c r="E539" s="2" t="n"/>
-    </row>
     <row r="540">
-      <c r="D540" s="1" t="inlineStr">
+      <c r="E540" s="2" t="n"/>
+    </row>
+    <row r="541">
+      <c r="D541" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="544">
-      <c r="C544" s="1" t="inlineStr">
-        <is>
-          <t>27. TC-RS-BR-027 — Chạy lại nhiều lần cho cùng kết quả, không nhân đôi dấu</t>
-        </is>
-      </c>
-    </row>
     <row r="545">
-      <c r="D545" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Kết quả chung và thứ tự cập nhật” (AC-G22)</t>
+      <c r="C545" s="1" t="inlineStr">
+        <is>
+          <t>27. TC-RS-BR-026 — Không chuyển đổi và không dùng ngưỡng đỏ cũ（`red_score`） làm fallback</t>
         </is>
       </c>
     </row>
     <row r="546">
-      <c r="D546" s="1" t="inlineStr">
+      <c r="D546" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Bảo toàn điểm đỏ cũ” (AC-G38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="D547" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="E547" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30); S01=29 Đỏ; trích xuất cấu hình trích xuất chỉ ký hiệu (“※” trước, “!” sau) (`※`, `!`).</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="E548" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30); học sinh S01 (điểm 29), cấu hình trích xuất chỉ ký hiệu (“※” trước, “!” sau)</t>
+          <t>・Điều kiện: mục số nguyên (M=100) có `red_score`=30 ở DB (nếu dữ liệu cho phép).</t>
         </is>
       </c>
     </row>
     <row r="549">
-      <c r="D549" s="1" t="inlineStr">
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: mục số nguyên (M=100), nguồn chưa có kết quả tổng hợp; quyền đọc DB local (chỉ SELECT/SHOW), học sinh S01 (điểm 29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="D550" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="E550" s="2" t="inlineStr">
-        <is>
-          <t>1. Chạy nút cam 3 lần liên tiếp (chờ mỗi lần hoàn tất).</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="E551" s="2" t="inlineStr">
         <is>
-          <t>2. Xem trích xuất; SELECT số kết quả hiện hành của ô S01 (khi có schema).</t>
+          <t>1. Không có quy tắc mới: đăng ký S01=29, xem đầu ra.</t>
         </is>
       </c>
     </row>
     <row r="552">
-      <c r="D552" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>2. Có quy tắc không khớp S01 (lọc lớp G-B): chạy lại, xem.</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="E553" s="2" t="inlineStr">
         <is>
-          <t>・Ô S01 hiện `※29!` (không `※※29!!`); chỉ một kết quả hiện hành cho ô.</t>
+          <t>3. Có quy tắc thiếu dữ liệu (nguồn chưa có kết quả tổng hợp): chạy lại, xem.</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="D554" s="1" t="inlineStr">
         <is>
-          <t>補足（Bổ sung）</t>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="E555" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 7.1 “Trình tự cho một ô” (đoạn cuối)</t>
+          <t>・Cả ba bước: S01 không có dấu đỏ từ `red_score`; trạng thái tương ứng lần lượt là không có quy tắc / Không áp dụng / Chưa xét được.</t>
         </is>
       </c>
     </row>
     <row r="556">
-      <c r="E556" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: Ảnh trích xuất; ảnh SELECT.</t>
+      <c r="D556" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="557">
-      <c r="D557" s="1" t="inlineStr">
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Có chuyển thiết lập điểm đỏ cũ sang chức năng mới không?” (Q17); đặc tả v2 (R18) mục 8.3 “Không tạo được ngưỡng hợp lệ”, mục 12.3 “Không chuyển đổi dữ liệu đỏ cũ”; code hiện tại “`red_score`, `changed_red_score`”</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: SELECT `red_score`; ảnh đầu ra ba bước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>・Sau khi chạy: `red_score` không đổi (case “Cột ngưỡng cũ không bị chuyển đổi hay xóa”).</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="D560" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="E558" s="2" t="n"/>
-    </row>
-    <row r="559">
-      <c r="D559" s="1" t="inlineStr">
+    <row r="561">
+      <c r="E561" s="2" t="n"/>
+    </row>
+    <row r="562">
+      <c r="D562" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="C563" s="1" t="inlineStr">
-        <is>
-          <t>28. TC-RS-BR-028 — Nhóm tham chiếu có lớp khác M không gây lỗi dừng xử lý</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="D564" s="3" t="inlineStr">
-        <is>
-          <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Kế thừa tỷ lệ nhóm” (AC-G15)</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="D565" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
     <row r="566">
-      <c r="E566" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Nguồn nhóm có M khác nhau (20/50 và 80/100) (20/50 và 80/100). quy tắc theo tỷ lệ điểm của nhóm từ 65% (cố định 70 `&lt;`). Học sinh P1 thuộc đối tượng quy tắc có S = 60.</t>
+      <c r="C566" s="1" t="inlineStr">
+        <is>
+          <t>28. TC-RS-BR-027 — Chạy lại nhiều lần cho cùng kết quả, không nhân đôi dấu</t>
         </is>
       </c>
     </row>
     <row r="567">
-      <c r="E567" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: nhóm có M khác nhau (20/50 và 80/100), quy tắc theo tỷ lệ điểm của nhóm từ 65%; P1: S = 60</t>
+      <c r="D567" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Kết quả chung và thứ tự cập nhật” (AC-G22)</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="D568" s="1" t="inlineStr">
         <is>
-          <t>操作（Thao tác）</t>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="E569" s="2" t="inlineStr">
         <is>
-          <t>1. Lưu quy tắc theo tỷ lệ điểm của nhóm từ 65% với nguồn là nhóm trên.</t>
+          <t>・Điều kiện: quy tắc “Cố định 30” (dưới 30); S01=29 Đỏ; trích xuất cấu hình trích xuất chỉ ký hiệu (“※” trước, “!” sau) (`※`, `!`).</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="E570" s="2" t="inlineStr">
         <is>
-          <t>2. Chạy nút xanh rồi nút cam cho phạm vi.</t>
+          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30); học sinh S01 (điểm 29), cấu hình trích xuất chỉ ký hiệu (“※” trước, “!” sau)</t>
         </is>
       </c>
     </row>
     <row r="571">
-      <c r="E571" s="2" t="inlineStr">
-        <is>
-          <t>3. Xem màn kết quả xử lý và kết quả P1.</t>
+      <c r="D571" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="572">
-      <c r="D572" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>1. Chạy nút cam 3 lần liên tiếp (chờ mỗi lần hoàn tất).</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="E573" s="2" t="inlineStr">
         <is>
-          <t>1. Lưu được; không bị chặn vì nhóm có lớp khác M.</t>
+          <t>2. Xem trích xuất; SELECT số kết quả hiện hành của ô S01 (khi có schema).</t>
         </is>
       </c>
     </row>
     <row r="574">
-      <c r="E574" s="2" t="inlineStr">
-        <is>
-          <t>・2–3. Xử lý hoàn tất, không lỗi dừng do khác M. `R=(20+80)/(50+100)×100≈66.7%` lấy từ kết quả tổng hợp hiện có → khớp `≥65%` → `T=70` → P1 Đỏ. Nếu tính trung bình tỷ lệ cá nhân (`(40%+80%)/2=60%` → Không áp dụng) là sai. Không có tùy chọn A/B.</t>
+      <c r="D574" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="575">
-      <c r="D575" s="1" t="inlineStr">
+      <c r="E575" s="2" t="inlineStr">
+        <is>
+          <t>・Ô S01 hiện `※29!` (không `※※29!!`); chỉ một kết quả hiện hành cho ô.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="D576" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
-      <c r="E576" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Tỷ lệ nhóm có cần xử lý riêng khi các lớp khác điểm tối đa không?” (Q31); đặc tả v2 (R18) mục 5.3 “Tỷ lệ nhóm” (công thức `R` = tổng điểm ÷ tổng điểm tối đa của cùng tập; Phạm vi vận hành, đoạn cuối); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Kế thừa tỷ lệ nhóm” (AC-G15) ("không tính lại bằng trung bình tỷ lệ cá nhân"; "không bị chặn cấu hình hoặc làm dừng xử lý"); C-01</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="E577" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh lưu quy tắc; ảnh màn kết quả xử lý và giá trị tỷ lệ nhóm của nguồn; ảnh kết quả P1; log lỗi (nếu có).</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 7.1 “Trình tự cho một ô” (đoạn cuối)</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="E578" s="2" t="inlineStr">
         <is>
-          <t>・Ghi chú: nhóm có M khác nhau (20/50 và 80/100) phân biệt được hai cách tính (66.7% và 60%); case “Tỷ lệ nhóm R = 70% khớp điều kiện ≥ 65%” thì không vì cùng M.</t>
+          <t>・Bằng chứng cần chụp: Ảnh trích xuất; ảnh SELECT.</t>
         </is>
       </c>
     </row>
@@ -11895,14 +11895,14 @@
     <row r="585">
       <c r="C585" s="1" t="inlineStr">
         <is>
-          <t>29. TC-RS-BR-029 — Mục lựa chọn không được xét, nhưng bộ lọc theo lựa chọn vẫn dùng để chọn đối tượng</t>
+          <t>29. TC-RS-BR-028 — Nhóm tham chiếu có lớp khác M không gây lỗi dừng xử lý</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="D586" s="3" t="inlineStr">
         <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Kiểu điểm được hỗ trợ” (AC-G02)</t>
+          <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Kế thừa tỷ lệ nhóm” (AC-G15)</t>
         </is>
       </c>
     </row>
@@ -11916,14 +11916,14 @@
     <row r="588">
       <c r="E588" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: mục kiểu lựa chọn A/B/C (A/B/C) có giá trị cho S01 = B, S02 = A.</t>
+          <t>・Điều kiện: Nguồn nhóm có M khác nhau (20/50 và 80/100) (20/50 và 80/100). quy tắc theo tỷ lệ điểm của nhóm từ 65% (cố định 70 `&lt;`). Học sinh P1 thuộc đối tượng quy tắc có S = 60.</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="E589" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: mục số nguyên (M=100); mục kiểu lựa chọn A/B/C, quy tắc “Cố định 30” (dưới 30)</t>
+          <t>・Dữ liệu test: nhóm có M khác nhau (20/50 và 80/100), quy tắc theo tỷ lệ điểm của nhóm từ 65%; P1: S = 60</t>
         </is>
       </c>
     </row>
@@ -11937,697 +11937,697 @@
     <row r="591">
       <c r="E591" s="2" t="inlineStr">
         <is>
-          <t>1. Tạo quy tắc cho mục số nguyên (M=100) với bộ lọc theo lựa chọn（選択肢型） mục kiểu lựa chọn A/B/C = B, cố định 30 `&lt;`.</t>
+          <t>1. Lưu quy tắc theo tỷ lệ điểm của nhóm từ 65% với nguồn là nhóm trên.</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="E592" s="2" t="inlineStr">
         <is>
-          <t>2. Đăng ký S01=29, S02=29.</t>
+          <t>2. Chạy nút xanh rồi nút cam cho phạm vi.</t>
         </is>
       </c>
     </row>
     <row r="593">
-      <c r="D593" s="1" t="inlineStr">
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>3. Xem màn kết quả xử lý và kết quả P1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="D594" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="E594" s="2" t="inlineStr">
-        <is>
-          <t>・S01 Đỏ (thuộc đối tượng); S02 Không áp dụng. Không có ô nào của mục kiểu lựa chọn A/B/C được xét đỏ.</t>
-        </is>
-      </c>
-    </row>
     <row r="595">
-      <c r="D595" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E595" s="2" t="inlineStr">
+        <is>
+          <t>1. Lưu được; không bị chặn vì nhóm có lớp khác M.</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="E596" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Những loại điểm nào thuộc đối tượng?” (Q2); đặc tả v2 (R18) mục 1.2 “Phạm vi thiết kế” (đoạn cuối)</t>
+          <t>・2–3. Xử lý hoàn tất, không lỗi dừng do khác M. `R=(20+80)/(50+100)×100≈66.7%` lấy từ kết quả tổng hợp hiện có → khớp `≥65%` → `T=70` → P1 Đỏ. Nếu tính trung bình tỷ lệ cá nhân (`(40%+80%)/2=60%` → Không áp dụng) là sai. Không có tùy chọn A/B.</t>
         </is>
       </c>
     </row>
     <row r="597">
-      <c r="E597" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: Ảnh cấu hình bộ lọc; ảnh kết quả.</t>
+      <c r="D597" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="598">
-      <c r="D598" s="1" t="inlineStr">
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Tỷ lệ nhóm có cần xử lý riêng khi các lớp khác điểm tối đa không?” (Q31); đặc tả v2 (R18) mục 5.3 “Tỷ lệ nhóm” (công thức `R` = tổng điểm ÷ tổng điểm tối đa của cùng tập; Phạm vi vận hành, đoạn cuối); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Kế thừa tỷ lệ nhóm” (AC-G15) ("không tính lại bằng trung bình tỷ lệ cá nhân"; "không bị chặn cấu hình hoặc làm dừng xử lý"); C-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="E599" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh lưu quy tắc; ảnh màn kết quả xử lý và giá trị tỷ lệ nhóm của nguồn; ảnh kết quả P1; log lỗi (nếu có).</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: nhóm có M khác nhau (20/50 và 80/100) phân biệt được hai cách tính (66.7% và 60%); case “Tỷ lệ nhóm R = 70% khớp điều kiện ≥ 65%” thì không vì cùng M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="D601" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="E599" s="2" t="n"/>
-    </row>
-    <row r="600">
-      <c r="D600" s="1" t="inlineStr">
+    <row r="602">
+      <c r="E602" s="2" t="n"/>
+    </row>
+    <row r="603">
+      <c r="D603" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="C604" s="1" t="inlineStr">
-        <is>
-          <t>30. TC-RS-BR-030 — Ô điểm đơn vị được xét riêng theo từng đơn vị</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="D605" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Kiểu điểm được hỗ trợ” (AC-G02); tiêu chí nghiệm thu “Nhận diện ô điểm” (AC-G03)</t>
-        </is>
-      </c>
-    </row>
-    <row r="606">
-      <c r="D606" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
     <row r="607">
-      <c r="E607" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: mục điểm đơn vị (đơn vị U1 có M riêng 40) có quy tắc “Cố định 30” (dưới 30) (`&lt;30`). S06 (G-B): U1 = 25, U2 = 35.</t>
+      <c r="C607" s="1" t="inlineStr">
+        <is>
+          <t>30. TC-RS-BR-029 — Mục lựa chọn không được xét, nhưng bộ lọc theo lựa chọn vẫn dùng để chọn đối tượng</t>
         </is>
       </c>
     </row>
     <row r="608">
-      <c r="E608" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30); mục điểm đơn vị (đơn vị U1 có M riêng 40)</t>
+      <c r="D608" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Kiểu điểm được hỗ trợ” (AC-G02)</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="D609" s="1" t="inlineStr">
         <is>
-          <t>操作（Thao tác）</t>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="E610" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng ký điểm U1, U2 của S06.</t>
+          <t>・Điều kiện: mục kiểu lựa chọn A/B/C (A/B/C) có giá trị cho S01 = B, S02 = A.</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="E611" s="2" t="inlineStr">
         <is>
-          <t>2. Xem ba đầu ra ở phạm vi đơn vị.</t>
+          <t>・Dữ liệu test: mục số nguyên (M=100); mục kiểu lựa chọn A/B/C, quy tắc “Cố định 30” (dưới 30)</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="D612" s="1" t="inlineStr">
         <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="E613" s="2" t="inlineStr">
         <is>
-          <t>・U1 Đỏ, U2 Không đỏ; dấu chỉ ở ô U1. Hai đơn vị không bị gộp thành một ô.</t>
+          <t>1. Tạo quy tắc cho mục số nguyên (M=100) với bộ lọc theo lựa chọn（選択肢型） mục kiểu lựa chọn A/B/C = B, cố định 30 `&lt;`.</t>
         </is>
       </c>
     </row>
     <row r="614">
-      <c r="D614" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>2. Đăng ký S01=29, S02=29.</t>
         </is>
       </c>
     </row>
     <row r="615">
-      <c r="E615" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Những loại điểm nào thuộc đối tượng?” (Q2), câu “Lấy trung bình của nhóm nào và kết quả tổng hợp nào?” (Q9); đặc tả v2 (R18) mục 2.2 “Một ô điểm được nhận diện như thế nào?”; Figma MW “chương 01 – lối vào, danh sách, xóa thiết lập” (58:9455) 「数値入力と単元別の点数が対象。」 (đối tượng là nhập số và điểm theo đơn vị), “chương 02 – điều kiện áp dụng và nguồn trung bình” (58:8855)</t>
+      <c r="D615" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="E616" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh/file đầu ra theo đơn vị.</t>
+          <t>・S01 Đỏ (thuộc đối tượng); S02 Không áp dụng. Không có ô nào của mục kiểu lựa chọn A/B/C được xét đỏ.</t>
         </is>
       </c>
     </row>
     <row r="617">
-      <c r="E617" s="2" t="inlineStr">
-        <is>
-          <t>・Ghi chú: M theo đơn vị: case “Phân giải M: mặc định → đơn vị → lựa chọn lớp”. Trung bình theo đơn vị: case “Trung bình riêng cho từng đơn vị” (nguồn trung bình theo đơn vị chưa tích hợp — đặc tả v2 mục 13.1).</t>
+      <c r="D617" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="618">
-      <c r="D618" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Những loại điểm nào thuộc đối tượng?” (Q2); đặc tả v2 (R18) mục 1.2 “Phạm vi thiết kế” (đoạn cuối)</t>
         </is>
       </c>
     </row>
     <row r="619">
-      <c r="E619" s="2" t="n"/>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh cấu hình bộ lọc; ảnh kết quả.</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="D620" s="1" t="inlineStr">
         <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="E621" s="2" t="n"/>
+    </row>
+    <row r="622">
+      <c r="D622" s="1" t="inlineStr">
+        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="C624" s="1" t="inlineStr">
-        <is>
-          <t>31. TC-RS-BR-031 — Giáo viên có quyền sửa mục cấu hình được quy tắc đỏ</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="D625" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Quyền thao tác và phạm vi dữ liệu” (AC-G01)</t>
-        </is>
-      </c>
-    </row>
     <row r="626">
-      <c r="D626" s="1" t="inlineStr">
+      <c r="C626" s="1" t="inlineStr">
+        <is>
+          <t>31. TC-RS-BR-030 — Ô điểm đơn vị được xét riêng theo từng đơn vị</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="D627" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Kiểu điểm được hỗ trợ” (AC-G02); tiêu chí nghiệm thu “Nhận diện ô điểm” (AC-G03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="D628" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="E627" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Đăng nhập tài khoản giáo viên có quyền sửa mục (giáo viên thường, không phải nhân viên nội bộ).</t>
-        </is>
-      </c>
-    </row>
-    <row r="628">
-      <c r="E628" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: tài khoản giáo viên có quyền sửa mục, mục số nguyên (M=100)</t>
-        </is>
-      </c>
-    </row>
     <row r="629">
-      <c r="D629" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E629" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: mục điểm đơn vị (đơn vị U1 có M riêng 40) có quy tắc “Cố định 30” (dưới 30) (`&lt;30`). S06 (G-B): U1 = 25, U2 = 35.</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="E630" s="2" t="inlineStr">
         <is>
-          <t>・Thêm, sửa điều kiện, sửa ngưỡng, đổi thứ tự, xóa một quy tắc của mục số nguyên (M=100).</t>
+          <t>・Dữ liệu test: quy tắc “Cố định 30” (dưới 30); mục điểm đơn vị (đơn vị U1 có M riêng 40)</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="D631" s="1" t="inlineStr">
         <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="E632" s="2" t="inlineStr">
         <is>
-          <t>・Mọi thao tác thành công.</t>
+          <t>1. Đăng ký điểm U1, U2 của S06.</t>
         </is>
       </c>
     </row>
     <row r="633">
-      <c r="D633" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E633" s="2" t="inlineStr">
+        <is>
+          <t>2. Xem ba đầu ra ở phạm vi đơn vị.</t>
         </is>
       </c>
     </row>
     <row r="634">
-      <c r="E634" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Ai được thiết lập điều kiện điểm đỏ?” (Q1); đặc tả v2 (R18) mục 1.3 “Quyền sử dụng”</t>
+      <c r="D634" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="E635" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh danh sách sau mỗi thao tác.</t>
+          <t>・U1 Đỏ, U2 Không đỏ; dấu chỉ ở ô U1. Hai đơn vị không bị gộp thành một ô.</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="D636" s="1" t="inlineStr">
         <is>
+          <t>補足（Bổ sung）</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="E637" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Những loại điểm nào thuộc đối tượng?” (Q2), câu “Lấy trung bình của nhóm nào và kết quả tổng hợp nào?” (Q9); đặc tả v2 (R18) mục 2.2 “Một ô điểm được nhận diện như thế nào?”; Figma MW “chương 01 – lối vào, danh sách, xóa thiết lập” (58:9455) 「数値入力と単元別の点数が対象。」 (đối tượng là nhập số và điểm theo đơn vị), “chương 02 – điều kiện áp dụng và nguồn trung bình” (58:8855)</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="E638" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh/file đầu ra theo đơn vị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="E639" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: M theo đơn vị: case “Phân giải M: mặc định → đơn vị → lựa chọn lớp”. Trung bình theo đơn vị: case “Trung bình riêng cho từng đơn vị” (nguồn trung bình theo đơn vị chưa tích hợp — đặc tả v2 mục 13.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="D640" s="1" t="inlineStr">
+        <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="E637" s="2" t="n"/>
-    </row>
-    <row r="638">
-      <c r="D638" s="1" t="inlineStr">
+    <row r="641">
+      <c r="E641" s="2" t="n"/>
+    </row>
+    <row r="642">
+      <c r="D642" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="C642" s="1" t="inlineStr">
-        <is>
-          <t>32. TC-RS-BR-032 — Vào được màn nhưng không có quyền sửa mục → không sửa được quy tắc của mục đó</t>
-        </is>
-      </c>
-    </row>
-    <row r="643">
-      <c r="D643" s="3" t="inlineStr">
+    <row r="646">
+      <c r="C646" s="1" t="inlineStr">
+        <is>
+          <t>32. TC-RS-BR-031 — Giáo viên có quyền sửa mục cấu hình được quy tắc đỏ</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="D647" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Quyền thao tác và phạm vi dữ liệu” (AC-G01)</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="D644" s="1" t="inlineStr">
+    <row r="648">
+      <c r="D648" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
-      <c r="E645" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Đăng nhập tài khoản giáo viên không có quyền sửa mục. mục chỉ dành nội bộ có một quy tắc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="E646" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: tài khoản giáo viên không có quyền sửa mục, mục chỉ dành nội bộ</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="D647" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="E648" s="2" t="inlineStr">
-        <is>
-          <t>1. Mở Thiết lập ô nhập（入力欄設定）.</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="E649" s="2" t="inlineStr">
         <is>
-          <t>2. Thử mở và sửa quy tắc của mục chỉ dành nội bộ.</t>
+          <t>・Điều kiện: Đăng nhập tài khoản giáo viên có quyền sửa mục (giáo viên thường, không phải nhân viên nội bộ).</t>
         </is>
       </c>
     </row>
     <row r="650">
-      <c r="D650" s="1" t="inlineStr">
+      <c r="E650" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: tài khoản giáo viên có quyền sửa mục, mục số nguyên (M=100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="D651" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="E652" s="2" t="inlineStr">
+        <is>
+          <t>・Thêm, sửa điều kiện, sửa ngưỡng, đổi thứ tự, xóa một quy tắc của mục số nguyên (M=100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="D653" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="E651" s="2" t="inlineStr">
-        <is>
-          <t>・Không có thao tác sửa/thêm/xóa cho mục chỉ dành nội bộ trên màn, hoặc lưu bị từ chối. Quy tắc không đổi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
-      <c r="D652" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="E653" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Ai được thiết lập điều kiện điểm đỏ?” (Q1); đặc tả v2 (R18) mục 1.3 “Quyền sử dụng” ("có quyền vào màn hình không đồng nghĩa sửa mọi mục")</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="E654" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh màn; phản hồi khi lưu.</t>
+          <t>・Mọi thao tác thành công.</t>
         </is>
       </c>
     </row>
     <row r="655">
-      <c r="E655" s="2" t="inlineStr">
-        <is>
-          <t>・Ghi chú: Kiểm request trực tiếp: case “Gửi request lưu quy tắc trực tiếp khi không có quyền sửa mục”.</t>
+      <c r="D655" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="656">
-      <c r="D656" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
+      <c r="E656" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Ai được thiết lập điều kiện điểm đỏ?” (Q1); đặc tả v2 (R18) mục 1.3 “Quyền sử dụng”</t>
         </is>
       </c>
     </row>
     <row r="657">
-      <c r="E657" s="2" t="n"/>
+      <c r="E657" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh danh sách sau mỗi thao tác.</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="D658" s="1" t="inlineStr">
         <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="E659" s="2" t="n"/>
+    </row>
+    <row r="660">
+      <c r="D660" s="1" t="inlineStr">
+        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="C662" s="1" t="inlineStr">
-        <is>
-          <t>33. TC-RS-BR-033 — Quyền sửa mục không tự cấp quyền chạy hàng loạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="D663" s="3" t="inlineStr">
+    <row r="664">
+      <c r="C664" s="1" t="inlineStr">
+        <is>
+          <t>33. TC-RS-BR-032 — Vào được màn nhưng không có quyền sửa mục → không sửa được quy tắc của mục đó</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="D665" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Quyền thao tác và phạm vi dữ liệu” (AC-G01)</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="D664" s="1" t="inlineStr">
+    <row r="666">
+      <c r="D666" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="E665" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Đăng nhập tài khoản sửa được mục nhưng không có quyền chạy hàng loạt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="666">
-      <c r="E666" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: tài khoản sửa được mục nhưng không có quyền chạy hàng loạt</t>
-        </is>
-      </c>
-    </row>
     <row r="667">
-      <c r="D667" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E667" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: Đăng nhập tài khoản giáo viên không có quyền sửa mục. mục chỉ dành nội bộ có một quy tắc.</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="E668" s="2" t="inlineStr">
         <is>
-          <t>1. Sửa một quy tắc (thành công).</t>
+          <t>・Dữ liệu test: tài khoản giáo viên không có quyền sửa mục, mục chỉ dành nội bộ</t>
         </is>
       </c>
     </row>
     <row r="669">
-      <c r="E669" s="2" t="inlineStr">
-        <is>
-          <t>2. Mở Tổng hợp thành tích（成績集計）, thử chạy tính toán hàng loạt.</t>
+      <c r="D669" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="670">
-      <c r="D670" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E670" s="2" t="inlineStr">
+        <is>
+          <t>1. Mở Thiết lập ô nhập（入力欄設定）.</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="E671" s="2" t="inlineStr">
         <is>
-          <t>・Không chạy được hàng loạt (thao tác không có hoặc bị từ chối theo quyền hiện hành).</t>
+          <t>2. Thử mở và sửa quy tắc của mục chỉ dành nội bộ.</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="D672" s="1" t="inlineStr">
         <is>
-          <t>補足（Bổ sung）</t>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="E673" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Ai được thiết lập điều kiện điểm đỏ?” (Q1); đặc tả v2 (R18) mục 1.3 “Quyền sử dụng” (Chạy tính toán hàng loạt); Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:6950) 「実行権限がない場合は、権限のある担当者へ再実行を依頼。」 (không có quyền chạy thì nhờ người có quyền chạy lại)</t>
+          <t>・Không có thao tác sửa/thêm/xóa cho mục chỉ dành nội bộ trên màn, hoặc lưu bị từ chối. Quy tắc không đổi.</t>
         </is>
       </c>
     </row>
     <row r="674">
-      <c r="E674" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: Ảnh màn Tổng hợp thành tích（成績集計）.</t>
+      <c r="D674" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="E675" s="2" t="inlineStr">
         <is>
-          <t>・Ghi chú: Request trực tiếp: case “Gọi trực tiếp request chạy tính toán hàng loạt khi không có quyền chạy”.</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Ai được thiết lập điều kiện điểm đỏ?” (Q1); đặc tả v2 (R18) mục 1.3 “Quyền sử dụng” ("có quyền vào màn hình không đồng nghĩa sửa mọi mục")</t>
         </is>
       </c>
     </row>
     <row r="676">
-      <c r="D676" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
+      <c r="E676" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh màn; phản hồi khi lưu.</t>
         </is>
       </c>
     </row>
     <row r="677">
-      <c r="E677" s="2" t="n"/>
+      <c r="E677" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: Kiểm request trực tiếp: case “Gửi request lưu quy tắc trực tiếp khi không có quyền sửa mục”.</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="D678" s="1" t="inlineStr">
         <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="E679" s="2" t="n"/>
+    </row>
+    <row r="680">
+      <c r="D680" s="1" t="inlineStr">
+        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="C682" s="1" t="inlineStr">
-        <is>
-          <t>34. TC-RS-BR-034 — Bật tự tổng hợp khi đăng ký: hệ thống không chặn; quy tắc độc lập với trung bình vẫn xét</t>
-        </is>
-      </c>
-    </row>
-    <row r="683">
-      <c r="D683" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Bao phủ đường đăng ký và chạy lại” (AC-G23)</t>
-        </is>
-      </c>
-    </row>
     <row r="684">
-      <c r="D684" s="1" t="inlineStr">
+      <c r="C684" s="1" t="inlineStr">
+        <is>
+          <t>34. TC-RS-BR-033 — Quyền sửa mục không tự cấp quyền chạy hàng loạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="D685" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Quyền thao tác và phạm vi dữ liệu” (AC-G01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="D686" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="E685" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Tự tổng hợp khi đăng ký = Thực hiện（実行する）. mục số nguyên (M=100) có quy tắc “Cố định 30” (dưới 30); mục số thập phân (M=100) có công thức `A×0.5`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="686">
-      <c r="E686" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: mục số nguyên (M=100), mục số thập phân (M=100); quy tắc “Cố định 30” (dưới 30), học sinh S01 (điểm 29), học sinh S09 (mục số thập phân 29.5)</t>
-        </is>
-      </c>
-    </row>
     <row r="687">
-      <c r="D687" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E687" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: Đăng nhập tài khoản sửa được mục nhưng không có quyền chạy hàng loạt.</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="E688" s="2" t="inlineStr">
         <is>
-          <t>1. Lưu quy tắc công thức (không bị chặn vì tự tổng hợp đang bật).</t>
+          <t>・Dữ liệu test: tài khoản sửa được mục nhưng không có quyền chạy hàng loạt</t>
         </is>
       </c>
     </row>
     <row r="689">
-      <c r="E689" s="2" t="inlineStr">
-        <is>
-          <t>2. Đặt tự tổng hợp = Không thực hiện（実行しない）, đăng ký S01=29.</t>
+      <c r="D689" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="690">
-      <c r="D690" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E690" s="2" t="inlineStr">
+        <is>
+          <t>1. Sửa một quy tắc (thành công).</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="E691" s="2" t="inlineStr">
         <is>
-          <t>1. Lưu được; không có ràng buộc hệ thống buộc tắt.</t>
+          <t>2. Mở Tổng hợp thành tích（成績集計）, thử chạy tính toán hàng loạt.</t>
         </is>
       </c>
     </row>
     <row r="692">
-      <c r="E692" s="2" t="inlineStr">
-        <is>
-          <t>2. S01 vẫn được xét khi đăng ký → Đỏ.</t>
+      <c r="D692" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="693">
-      <c r="D693" s="1" t="inlineStr">
+      <c r="E693" s="2" t="inlineStr">
+        <is>
+          <t>・Không chạy được hàng loạt (thao tác không có hoặc bị từ chối theo quyền hiện hành).</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="D694" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="694">
-      <c r="E694" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Quy trình vận hành khi có đánh giá tương đối là gì?” (Q12) ("tắt tự tổng hợp không tắt bước xét khi đăng ký điểm"); đặc tả v2 (R18) mục 7.4 “Quy trình vận hành khi dùng trung bình/tỷ lệ nhóm” (đoạn sau các bước)</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="E695" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh cấu hình; ảnh kết quả.</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Ai được thiết lập điều kiện điểm đỏ?” (Q1); đặc tả v2 (R18) mục 1.3 “Quyền sử dụng” (Chạy tính toán hàng loạt); Figma MW “chương 04 – đăng ký, tổng hợp, chạy lại và kết quả” (58:6950) 「実行権限がない場合は、権限のある担当者へ再実行を依頼。」 (không có quyền chạy thì nhờ người có quyền chạy lại)</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="E696" s="2" t="inlineStr">
         <is>
-          <t>・Sau khi chạy: Trả cấu hình về trạng thái ban đầu.</t>
+          <t>・Bằng chứng cần chụp: Ảnh màn Tổng hợp thành tích（成績集計）.</t>
         </is>
       </c>
     </row>
     <row r="697">
-      <c r="D697" s="1" t="inlineStr">
+      <c r="E697" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: Request trực tiếp: case “Gọi trực tiếp request chạy tính toán hàng loạt khi không có quyền chạy”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="D698" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="E698" s="2" t="n"/>
-    </row>
     <row r="699">
-      <c r="D699" s="1" t="inlineStr">
+      <c r="E699" s="2" t="n"/>
+    </row>
+    <row r="700">
+      <c r="D700" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="C703" s="1" t="inlineStr">
-        <is>
-          <t>35. TC-RS-BR-035 — Bộ lọc nhóm tổng hợp thuộc hai loại nhóm vẫn kết hợp HOẶC</t>
-        </is>
-      </c>
-    </row>
     <row r="704">
-      <c r="D704" s="3" t="inlineStr">
-        <is>
-          <t>Priority: TBD ｜ Status: PROPOSED ｜ Requirement ID: tiêu chí nghiệm thu “Đối tượng áp dụng và nhu cầu nguồn” (AC-G05)</t>
+      <c r="C704" s="1" t="inlineStr">
+        <is>
+          <t>35. TC-RS-BR-034 — Bật tự tổng hợp khi đăng ký: hệ thống không chặn; quy tắc độc lập với trung bình vẫn xét</t>
         </is>
       </c>
     </row>
     <row r="705">
-      <c r="D705" s="1" t="inlineStr">
+      <c r="D705" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Bao phủ đường đăng ký và chạy lại” (AC-G23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="D706" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="706">
-      <c r="E706" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Hai loại nhóm tổng hợp: K1 = Nhóm thành tích（成績グループ） có mục Nâng cao; K2 = một loại nhóm tổng hợp khác có mục X. Học sinh P5 thuộc Nâng cao, P6 thuộc X, P7 không thuộc cả hai; cả ba học khối 1.</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="E707" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: quy tắc lọc theo nhóm tổng hợp thuộc hai loại nhóm; S = 20 cho P5–P7</t>
+          <t>・Điều kiện: Tự tổng hợp khi đăng ký = Thực hiện（実行する）. mục số nguyên (M=100) có quy tắc “Cố định 30” (dưới 30); mục số thập phân (M=100) có công thức `A×0.5`.</t>
         </is>
       </c>
     </row>
     <row r="708">
-      <c r="D708" s="1" t="inlineStr">
+      <c r="E708" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: mục số nguyên (M=100), mục số thập phân (M=100); quy tắc “Cố định 30” (dưới 30), học sinh S01 (điểm 29), học sinh S09 (mục số thập phân 29.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="D709" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="709">
-      <c r="E709" s="2" t="inlineStr">
-        <is>
-          <t>1. Đăng ký điểm 20 cho P5–P7.</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="E710" s="2" t="inlineStr">
         <is>
-          <t>2. Xem kết quả.</t>
+          <t>1. Lưu quy tắc công thức (không bị chặn vì tự tổng hợp đang bật).</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="E711" s="2" t="inlineStr">
         <is>
-          <t>3. Mở lại quy tắc.</t>
+          <t>2. Đặt tự tổng hợp = Không thực hiện（実行しない）, đăng ký S01=29.</t>
         </is>
       </c>
     </row>
@@ -12641,14 +12641,14 @@
     <row r="713">
       <c r="E713" s="2" t="inlineStr">
         <is>
-          <t>・1–2. P5, P6: Đỏ. P7: Không áp dụng.</t>
+          <t>1. Lưu được; không có ràng buộc hệ thống buộc tắt.</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="E714" s="2" t="inlineStr">
         <is>
-          <t>3. Mỗi giá trị vẫn gắn đúng loại nhóm của nó.</t>
+          <t>2. S01 vẫn được xét khi đăng ký → Đỏ.</t>
         </is>
       </c>
     </row>
@@ -12662,21 +12662,21 @@
     <row r="716">
       <c r="E716" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 5.1 “Đối tượng áp dụng” (HOẶC trong cùng loại, VÀ giữa các loại); thiết kế DB v2 (RSD-DB) mục 3.2 “`apply_condition`” ("Các giá trị trong `values` và các phần tử cùng `type` dùng OR, kể cả khác key" — PROPOSED)</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Quy trình vận hành khi có đánh giá tương đối là gì?” (Q12) ("tắt tự tổng hợp không tắt bước xét khi đăng ký điểm"); đặc tả v2 (R18) mục 7.4 “Quy trình vận hành khi dùng trung bình/tỷ lệ nhóm” (đoạn sau các bước)</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="E717" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả ba học sinh; ảnh form mở lại.</t>
+          <t>・Bằng chứng cần chụp: Ảnh cấu hình; ảnh kết quả.</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="E718" s="2" t="inlineStr">
         <is>
-          <t>・Ghi chú: PROPOSED — không phải must-pass. P5–P7 là học sinh bổ sung ngoài TD-STU.</t>
+          <t>・Sau khi chạy: Trả cấu hình về trạng thái ban đầu.</t>
         </is>
       </c>
     </row>
@@ -12700,14 +12700,14 @@
     <row r="725">
       <c r="C725" s="1" t="inlineStr">
         <is>
-          <t>36. TC-RS-BR-036 — Cùng lượt đăng ký: ô thiếu nguồn chưa xét được, ô ngưỡng cố định vẫn được xét</t>
+          <t>36. TC-RS-BR-035 — Bộ lọc nhóm tổng hợp khác loại phải kết hợp VÀ</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="D726" s="3" t="inlineStr">
         <is>
-          <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Bao phủ đường đăng ký và chạy lại” (AC-G23)</t>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Đối tượng áp dụng và nhu cầu nguồn” (AC-G05)</t>
         </is>
       </c>
     </row>
@@ -12721,14 +12721,14 @@
     <row r="728">
       <c r="E728" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: Trên mục số nguyên (M=100): ưu tiên 1 = quy tắc công thức hai dòng (trung bình ÷ 2 × 0.8) (dùng trung bình, nguồn nguồn chưa có kết quả tổng hợp), ưu tiên 2 = quy tắc “Cố định 30” (dưới 30). Trên mục số thập phân (M=100): chỉ quy tắc “Cố định 30” (dưới 30). Lớp G-A có S01.</t>
+          <t>・Điều kiện: Hai loại nhóm tổng hợp: K1 = Nhóm thành tích（成績グループ） có mục Nâng cao; K2 = một loại nhóm tổng hợp khác có mục X. P5 chỉ thuộc Nâng cao; P6 chỉ thuộc X; P7 thuộc cả Nâng cao và X; P8 không thuộc cả hai. Cả bốn học khối 1.</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="E729" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: mục số nguyên (M=100); mục số thập phân (M=100); quy tắc công thức hai dòng (trung bình ÷ 2 × 0.8); quy tắc “Cố định 30” (dưới 30); nguồn chưa có kết quả tổng hợp; các lớp học phần G-A, G-B, G-C; học sinh S01 (điểm 29); S01 mục số thập phân (M=100) = 29.5</t>
+          <t>・Dữ liệu test: quy tắc lọc theo nhóm tổng hợp thuộc hai loại nhóm; S = 20 cho P5–P8</t>
         </is>
       </c>
     </row>
@@ -12742,42 +12742,42 @@
     <row r="731">
       <c r="E731" s="2" t="inlineStr">
         <is>
-          <t>1. Trong cùng một lượt đăng ký điểm của lớp G-A, lưu S01: mục số nguyên (M=100) = 29, mục số thập phân (M=100) = 29.5.</t>
+          <t>1. Đăng ký điểm 20 cho P5–P8.</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="E732" s="2" t="inlineStr">
         <is>
-          <t>2. Xem kết quả hai ô và thông báo.</t>
+          <t>2. Xem kết quả.</t>
         </is>
       </c>
     </row>
     <row r="733">
-      <c r="D733" s="1" t="inlineStr">
+      <c r="E733" s="2" t="inlineStr">
+        <is>
+          <t>3. Mở lại quy tắc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="D734" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="734">
-      <c r="E734" s="2" t="inlineStr">
-        <is>
-          <t>1. Lượt lưu không dừng hay báo lỗi chung vì ô mục số nguyên (M=100) thiếu nguồn.</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="E735" s="2" t="inlineStr">
         <is>
-          <t>2. Ô mục số nguyên (M=100): Chưa xét được; không dùng ưu tiên 2 (quy tắc “Cố định 30” (dưới 30)) thay thế, nên không Đỏ.</t>
+          <t>・1–2. Chỉ P7 thỏa cả hai loại nhóm và được xét → Đỏ. P5, P6, P8: Không áp dụng.</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="E736" s="2" t="inlineStr">
         <is>
-          <t>3. Ô mục số thập phân (M=100): Đỏ (29.5 `&lt;30`).</t>
+          <t>3. Mỗi giá trị vẫn gắn đúng loại nhóm của nó.</t>
         </is>
       </c>
     </row>
@@ -12791,21 +12791,21 @@
     <row r="738">
       <c r="E738" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Bao phủ đường đăng ký và chạy lại” (AC-G23) (bảng điều kiện chạy, dòng "Cùng lượt có ô phụ thuộc nguồn và ô độc lập"); đặc tả v2 (R18) mục 4.3 “Chọn quy tắc”, mục 5.5 “Chọn bản nguồn” bước 4; tài liệu chia công việc v2 (RSD-TASK) công việc “Cập nhật kết quả khi đăng ký và chạy hàng loạt” (Task 4) (Thay đổi nghiệp vụ)</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 5.1 “Đối tượng áp dụng”; xác nhận thiết kế ngày 30/09 (Q35: bộ lọc thường OR cùng loại/AND khác loại; điều kiện trung bình/tỷ lệ nhóm AND với bộ lọc); thiết kế DB v2 (RSD-DB) mục 3.2 “`apply_condition`”.</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="E739" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh màn đăng ký sau khi lưu; ảnh kết quả hai ô; thông báo hiển thị. SELECT kết quả của hai ô (khi có schema).</t>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả bốn học sinh; ảnh form mở lại xác nhận mỗi giá trị vẫn gắn đúng loại nhóm.</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="E740" s="2" t="inlineStr">
         <is>
-          <t>・Ghi chú: Tiêu chí nghiệm thu tiêu chí nghiệm thu “Bao phủ đường đăng ký và chạy lại”. Ô thiếu nguồn đơn lẻ: case “Chưa có kết quả tổng hợp → Chưa xét được, không thay bằng 0 hay nhóm khác”.</t>
+          <t>・Ghi chú: P5–P8 là học sinh bổ sung ngoài TD-STU. Oracle AND là CONFIRMED; biểu diễn JSON/schema vẫn có thể là PROPOSED.</t>
         </is>
       </c>
     </row>
@@ -12829,14 +12829,14 @@
     <row r="747">
       <c r="C747" s="1" t="inlineStr">
         <is>
-          <t>37. TC-RS-BR-037 — Xóa hoặc thôi dùng điểm đơn vị thì ngừng kết quả đỏ cũ của ô đó</t>
+          <t>37. TC-RS-BR-036 — Cùng lượt đăng ký: ô thiếu nguồn chưa xét được, ô ngưỡng cố định vẫn được xét</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="D748" s="3" t="inlineStr">
         <is>
-          <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Trigger khi đổi điểm tối đa/đơn vị” (AC-G24)</t>
+          <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Bao phủ đường đăng ký và chạy lại” (AC-G23)</t>
         </is>
       </c>
     </row>
@@ -12850,14 +12850,14 @@
     <row r="750">
       <c r="E750" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: mục điểm đơn vị (đơn vị U1 có M riêng 40) có quy tắc “Cố định 30” (dưới 30). S06 (G-B): U1 = 25, U2 = 35 đã đăng ký; U1 đang Đỏ, U2 Không đỏ (như case “Ô điểm đơn vị được xét riêng theo từng đơn vị”).</t>
+          <t>・Điều kiện: Trên mục số nguyên (M=100): ưu tiên 1 = quy tắc công thức hai dòng (trung bình ÷ 2 × 0.8) (dùng trung bình, nguồn nguồn chưa có kết quả tổng hợp), ưu tiên 2 = quy tắc “Cố định 30” (dưới 30). Trên mục số thập phân (M=100): chỉ quy tắc “Cố định 30” (dưới 30). Lớp G-A có S01.</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="E751" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: mục điểm đơn vị (đơn vị U1 có M riêng 40); quy tắc “Cố định 30” (dưới 30); các lớp học phần G-A, G-B, G-C; học sinh S06 (điểm dự kiến 24)</t>
+          <t>・Dữ liệu test: mục số nguyên (M=100); mục số thập phân (M=100); quy tắc công thức hai dòng (trung bình ÷ 2 × 0.8); quy tắc “Cố định 30” (dưới 30); nguồn chưa có kết quả tổng hợp; các lớp học phần G-A, G-B, G-C; học sinh S01 (điểm 29); S01 mục số thập phân (M=100) = 29.5</t>
         </is>
       </c>
     </row>
@@ -12871,157 +12871,157 @@
     <row r="753">
       <c r="E753" s="2" t="inlineStr">
         <is>
-          <t>1. Xác nhận U1 Đỏ ở ba đầu ra.</t>
+          <t>1. Trong cùng một lượt đăng ký điểm của lớp G-A, lưu S01: mục số nguyên (M=100) = 29, mục số thập phân (M=100) = 29.5.</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="E754" s="2" t="inlineStr">
         <is>
-          <t>2. Biến thể (a): xóa điểm U1 của S06 thành trống rồi lưu.</t>
+          <t>2. Xem kết quả hai ô và thông báo.</t>
         </is>
       </c>
     </row>
     <row r="755">
-      <c r="E755" s="2" t="inlineStr">
-        <is>
-          <t>3. Biến thể (b): thôi dùng đơn vị U1 cho lớp G-B theo thao tác hiện có (nếu màn hỗ trợ), rồi đăng ký lại hoặc chạy nút cam cho G-B.</t>
+      <c r="D755" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="E756" s="2" t="inlineStr">
         <is>
-          <t>4. Xem ba đầu ra và bộ lọc đỏ của trích xuất.</t>
+          <t>1. Lượt lưu không dừng hay báo lỗi chung vì ô mục số nguyên (M=100) thiếu nguồn.</t>
         </is>
       </c>
     </row>
     <row r="757">
-      <c r="D757" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E757" s="2" t="inlineStr">
+        <is>
+          <t>2. Ô mục số nguyên (M=100): Chưa xét được; không dùng ưu tiên 2 (quy tắc “Cố định 30” (dưới 30)) thay thế, nên không Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="E758" s="2" t="inlineStr">
         <is>
-          <t>1. Sau (a) hoặc (b), ô U1 của S06 không còn dấu đỏ ở ba đầu ra; bộ lọc đỏ không giữ S06 chỉ vì U1 cũ.</t>
+          <t>3. Ô mục số thập phân (M=100): Đỏ (29.5 `&lt;30`).</t>
         </is>
       </c>
     </row>
     <row r="759">
-      <c r="E759" s="2" t="inlineStr">
-        <is>
-          <t>2. U2 giữ kết quả Không đỏ; không bị gộp hay xét lại sai.</t>
+      <c r="D759" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="760">
-      <c r="D760" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E760" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Bao phủ đường đăng ký và chạy lại” (AC-G23) (bảng điều kiện chạy, dòng "Cùng lượt có ô phụ thuộc nguồn và ô độc lập"); đặc tả v2 (R18) mục 4.3 “Chọn quy tắc”, mục 5.5 “Chọn bản nguồn” bước 4; tài liệu chia công việc v2 (RSD-TASK) công việc “Cập nhật kết quả khi đăng ký và chạy hàng loạt” (Task 4) (Thay đổi nghiệp vụ)</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="E761" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Trigger khi đổi điểm tối đa/đơn vị” (AC-G24) ("Xóa/không dùng điểm đơn vị phải ngừng kết quả cũ"); đặc tả v2 (R18) mục 7.3 “Thay đổi điểm tối đa” (dòng "Sửa maximum/việc sử dụng theo đơn vị"), mục 7.2 “Bảng sự kiện” (dòng "Xóa điểm số thành trống"), mục 2.2 “Một ô điểm được nhận diện như thế nào?”</t>
+          <t>・Bằng chứng cần chụp: Ảnh màn đăng ký sau khi lưu; ảnh kết quả hai ô; thông báo hiển thị. SELECT kết quả của hai ô (khi có schema).</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="E762" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh/file ba đầu ra trước và sau; ảnh thao tác xóa hoặc thôi dùng đơn vị.</t>
+          <t>・Ghi chú: Tiêu chí nghiệm thu tiêu chí nghiệm thu “Bao phủ đường đăng ký và chạy lại”. Ô thiếu nguồn đơn lẻ: case “Chưa có kết quả tổng hợp → Chưa xét được, không thay bằng 0 hay nhóm khác”.</t>
         </is>
       </c>
     </row>
     <row r="763">
-      <c r="E763" s="2" t="inlineStr">
-        <is>
-          <t>・Sau khi chạy: Khôi phục điểm U1 và thiết lập đơn vị của G-B.</t>
+      <c r="D763" s="1" t="inlineStr">
+        <is>
+          <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
     <row r="764">
-      <c r="E764" s="2" t="inlineStr">
-        <is>
-          <t>・Ghi chú: Tiêu chí nghiệm thu tiêu chí nghiệm thu “Trigger khi đổi điểm tối đa/đơn vị”. Biến thể (b) BLOCKED cho tới khi xác minh màn và thao tác "thôi dùng đơn vị"; hỏi team dev.</t>
-        </is>
-      </c>
+      <c r="E764" s="2" t="n"/>
     </row>
     <row r="765">
       <c r="D765" s="1" t="inlineStr">
         <is>
-          <t>結果（Kết quả）</t>
-        </is>
-      </c>
-    </row>
-    <row r="766">
-      <c r="E766" s="2" t="n"/>
-    </row>
-    <row r="767">
-      <c r="D767" s="1" t="inlineStr">
-        <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
+    <row r="769">
+      <c r="C769" s="1" t="inlineStr">
+        <is>
+          <t>38. TC-RS-BR-037 — Xóa hoặc thôi dùng điểm đơn vị thì ngừng kết quả đỏ cũ của ô đó</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="D770" s="3" t="inlineStr">
+        <is>
+          <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Trigger khi đổi điểm tối đa/đơn vị” (AC-G24)</t>
+        </is>
+      </c>
+    </row>
     <row r="771">
-      <c r="C771" s="1" t="inlineStr">
-        <is>
-          <t>38. TC-RS-BR-038 — Nhóm lớp học（授業）: dùng kết quả tổng hợp của đúng lớp chứa ô đang xét</t>
+      <c r="D771" s="1" t="inlineStr">
+        <is>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="772">
-      <c r="D772" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Đúng phạm vi tham chiếu” (AC-G12)</t>
+      <c r="E772" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: mục điểm đơn vị (đơn vị U1 có M riêng 40) có quy tắc “Cố định 30” (dưới 30). S06 (G-B): U1 = 25, U2 = 35 đã đăng ký; U1 đang Đỏ, U2 Không đỏ (như case “Ô điểm đơn vị được xét riêng theo từng đơn vị”).</t>
         </is>
       </c>
     </row>
     <row r="773">
-      <c r="D773" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
+      <c r="E773" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: mục điểm đơn vị (đơn vị U1 có M riêng 40); quy tắc “Cố định 30” (dưới 30); các lớp học phần G-A, G-B, G-C; học sinh S06 (điểm dự kiến 24)</t>
         </is>
       </c>
     </row>
     <row r="774">
-      <c r="E774" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: thiết lập tổng hợp X đã bật thêm Lớp học（授業） (X đã bật lớp học và đã tổng hợp). S11 học cả G-A và G-D; trong X trung bình lớp G-A = 40, G-D = 70. Quy tắc trên mục số nguyên (M=100): Toàn bộ đối tượng, ngưỡng Công thức（計算式） `A×0.5`, `&lt;`; nguồn công thức = X / Lớp học（授業）.</t>
+      <c r="D774" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="E775" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: thiết lập tổng hợp X đã bật thêm Lớp học（授業）, học sinh S11 học hai lớp Toán I (G-A, G-D); mục số nguyên (M=100); S11 có điểm 25 ở cả G-A và G-D</t>
+          <t>1. Xác nhận U1 Đỏ ở ba đầu ra.</t>
         </is>
       </c>
     </row>
     <row r="776">
-      <c r="D776" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E776" s="2" t="inlineStr">
+        <is>
+          <t>2. Biến thể (a): xóa điểm U1 của S06 thành trống rồi lưu.</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="E777" s="2" t="inlineStr">
         <is>
-          <t>1. Chạy nút cam cho G-A và G-D.</t>
+          <t>3. Biến thể (b): thôi dùng đơn vị U1 cho lớp G-B theo thao tác hiện có (nếu màn hỗ trợ), rồi đăng ký lại hoặc chạy nút cam cho G-B.</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="E778" s="2" t="inlineStr">
         <is>
-          <t>2. Xem kết quả hai ô của S11 trên trích xuất.</t>
+          <t>4. Xem ba đầu ra và bộ lọc đỏ của trích xuất.</t>
         </is>
       </c>
     </row>
@@ -13035,49 +13035,49 @@
     <row r="780">
       <c r="E780" s="2" t="inlineStr">
         <is>
-          <t>・- Ô ở G-A: `T=40×0.5=20` → 25 Không đỏ.</t>
+          <t>1. Sau (a) hoặc (b), ô U1 của S06 không còn dấu đỏ ở ba đầu ra; bộ lọc đỏ không giữ S06 chỉ vì U1 cũ.</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="E781" s="2" t="inlineStr">
         <is>
-          <t>・- Ô ở G-D: `T=70×0.5=35` → 25 Đỏ.</t>
+          <t>2. U2 giữ kết quả Không đỏ; không bị gộp hay xét lại sai.</t>
         </is>
       </c>
     </row>
     <row r="782">
-      <c r="E782" s="2" t="inlineStr">
-        <is>
-          <t>・- Không ô nào dùng kết quả của lớp kia, của khối/lớp chủ nhiệm, hay trung bình chung của môn.</t>
+      <c r="D782" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="783">
-      <c r="D783" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E783" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Trigger khi đổi điểm tối đa/đơn vị” (AC-G24) ("Xóa/không dùng điểm đơn vị phải ngừng kết quả cũ"); đặc tả v2 (R18) mục 7.3 “Thay đổi điểm tối đa” (dòng "Sửa maximum/việc sử dụng theo đơn vị"), mục 7.2 “Bảng sự kiện” (dòng "Xóa điểm số thành trống"), mục 2.2 “Một ô điểm được nhận diện như thế nào?”</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="E784" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: context điểm đỏ (CTX) mục 9.6 “Ba phản hồi review DB và bài học thiết kế ngày 28/09” (quyết định DB-R3 mục 2: bật thêm lớp học thì dùng kết quả của lớp liên quan); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Đúng phạm vi tham chiếu” (AC-G12) (bảng quy tắc chọn/đọc nhóm: "không đọc kết quả lớp khác với ô đang xét"); thiết kế DB v2 (RSD-DB) mục 3.1 “Bộ thông tin nguồn” ("Loại 5 phải khớp cả lớp, không chỉ môn" — PROPOSED), mục 3.4 “`judgment_context`” (`population_key` chứa ID lớp thực tế)</t>
+          <t>・Bằng chứng cần chụp: Ảnh/file ba đầu ra trước và sau; ảnh thao tác xóa hoặc thôi dùng đơn vị.</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="E785" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả tổng hợp X theo lớp; ảnh trích xuất hai ô; SELECT `judgment_context.sources` của hai ô nếu có schema.</t>
+          <t>・Sau khi chạy: Khôi phục điểm U1 và thiết lập đơn vị của G-B.</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="E786" s="2" t="inlineStr">
         <is>
-          <t>・Ghi chú: Dữ liệu học sinh học hai lớp cùng môn: hỏi team dev khi chuẩn bị; không tạo được thì dùng hai học sinh khác lớp và ghi Notes. Phụ thuộc phạm vi đợt có công thức (phạm vi phát hành chưa chốt — đặc tả v2 mục 13.1).</t>
+          <t>・Ghi chú: Tiêu chí nghiệm thu tiêu chí nghiệm thu “Trigger khi đổi điểm tối đa/đơn vị”. Biến thể (b) BLOCKED cho tới khi xác minh màn và thao tác "thôi dùng đơn vị"; hỏi team dev.</t>
         </is>
       </c>
     </row>
@@ -13101,14 +13101,14 @@
     <row r="793">
       <c r="C793" s="1" t="inlineStr">
         <is>
-          <t>39. TC-RS-BR-039 — Nhóm môn học（科目グループ）: dùng cấu hình riêng của môn hoặc default đã lưu; thiếu/sai thì Chưa xét được</t>
+          <t>39. TC-RS-BR-038 — Nhóm lớp học（授業）: dùng kết quả tổng hợp của đúng lớp chứa ô đang xét</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="D794" s="3" t="inlineStr">
         <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Đúng phạm vi tham chiếu” (AC-G12); tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13)</t>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Đúng phạm vi tham chiếu” (AC-G12)</t>
         </is>
       </c>
     </row>
@@ -13122,14 +13122,14 @@
     <row r="796">
       <c r="E796" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: nhóm môn học “Nhóm môn Toán” có cấu hình riêng cho Toán I（数学Ⅰ） và default. Quy tắc trên mục số nguyên (M=100) dùng nguồn công thức = X / nhóm môn học “Nhóm môn Toán”, ngưỡng `A×0.5`, `&lt;`.</t>
+          <t>・Điều kiện: thiết lập tổng hợp X đã bật thêm Lớp học（授業） (X đã bật lớp học và đã tổng hợp). S11 học cả G-A và G-D; trong X trung bình lớp G-A = 40, G-D = 70. Quy tắc trên mục số nguyên (M=100): Toàn bộ đối tượng, ngưỡng Công thức（計算式） `A×0.5`, `&lt;`; nguồn công thức = X / Lớp học（授業）.</t>
         </is>
       </c>
     </row>
     <row r="797">
       <c r="E797" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: nhóm môn học “Nhóm môn Toán”; mục số nguyên (M=100); S01 = 25</t>
+          <t>・Dữ liệu test: thiết lập tổng hợp X đã bật thêm Lớp học（授業）, học sinh S11 học hai lớp Toán I (G-A, G-D); mục số nguyên (M=100); S11 có điểm 25 ở cả G-A và G-D</t>
         </is>
       </c>
     </row>
@@ -13143,249 +13143,378 @@
     <row r="799">
       <c r="E799" s="2" t="inlineStr">
         <is>
-          <t>1. Chạy nút cam; xem S01 và nhóm được dùng.</t>
+          <t>1. Chạy nút cam cho G-A và G-D.</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="E800" s="2" t="inlineStr">
         <is>
-          <t>2. Xóa cấu hình riêng của Toán I (để môn rơi về default); chạy lại; xem.</t>
+          <t>2. Xem kết quả hai ô của S11 trên trích xuất.</t>
         </is>
       </c>
     </row>
     <row r="801">
-      <c r="E801" s="2" t="inlineStr">
-        <is>
-          <t>3. Làm default thiếu hoặc trỏ tới cấu hình không hợp lệ (biến thể (b) của nhóm môn học “Nhóm môn Toán”); chạy lại; xem trạng thái và thông báo.</t>
+      <c r="D801" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="802">
-      <c r="D802" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E802" s="2" t="inlineStr">
+        <is>
+          <t>・- Ô ở G-A: `T=40×0.5=20` → 25 Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="E803" s="2" t="inlineStr">
         <is>
-          <t>1. Dùng kết quả của nhóm theo cấu hình riêng của Toán I.</t>
+          <t>・- Ô ở G-D: `T=70×0.5=35` → 25 Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="804">
       <c r="E804" s="2" t="inlineStr">
         <is>
-          <t>2. Dùng kết quả của nhóm theo default đã lưu.</t>
+          <t>・- Không ô nào dùng kết quả của lớp kia, của khối/lớp chủ nhiệm, hay trung bình chung của môn.</t>
         </is>
       </c>
     </row>
     <row r="805">
-      <c r="E805" s="2" t="inlineStr">
-        <is>
-          <t>3. S01 Chưa xét được; không thay bằng nhóm khác, bằng 0 hay bằng kết quả trước; thông báo/tiến độ tách phần chưa xét được.</t>
+      <c r="D805" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="806">
-      <c r="D806" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E806" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: context điểm đỏ (CTX) mục 9.6 “Ba phản hồi review DB và bài học thiết kế ngày 28/09” (quyết định DB-R3 mục 2: bật thêm lớp học thì dùng kết quả của lớp liên quan); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Đúng phạm vi tham chiếu” (AC-G12) (bảng quy tắc chọn/đọc nhóm: "không đọc kết quả lớp khác với ô đang xét"); thiết kế DB v2 (RSD-DB) mục 3.1 “Bộ thông tin nguồn” ("Loại 5 phải khớp cả lớp, không chỉ môn" — PROPOSED), mục 3.4 “`judgment_context`” (`population_key` chứa ID lớp thực tế)</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="E807" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Ba loại nhóm cấu hình có xuất hiện ngoài khối/HR/lớp học không?” (Q33); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Đúng phạm vi tham chiếu” (AC-G12)/G13 (bảng quy tắc chọn/đọc nhóm: "Chọn nhóm môn học — dùng cấu hình riêng của môn hoặc default đã lưu. Không thay default thiếu/tham chiếu sai bằng nhóm khác hay 0"); thiết kế DB v2 (RSD-DB) mục 3.1 “Bộ thông tin nguồn”, mục 3.4 “`judgment_context`” (PROPOSED)</t>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả tổng hợp X theo lớp; ảnh trích xuất hai ô; SELECT `judgment_context.sources` của hai ô nếu có schema.</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="E808" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh cấu hình nhóm môn ở mỗi bước; ảnh kết quả S01; SELECT `reason_code` và `judgment_context.sources` nếu có schema.</t>
+          <t>・Ghi chú: Dữ liệu học sinh học hai lớp cùng môn: hỏi team dev khi chuẩn bị; không tạo được thì dùng hai học sinh khác lớp và ghi Notes. Phụ thuộc phạm vi đợt có công thức (phạm vi phát hành chưa chốt — đặc tả v2 mục 13.1).</t>
         </is>
       </c>
     </row>
     <row r="809">
-      <c r="E809" s="2" t="inlineStr">
-        <is>
-          <t>・Ghi chú: (PROPOSED) Bước 1–2: `sources[]` giữ `population_type=6` và ID nhóm môn đã chọn, thêm `resolved_population_type`/`resolved_population_ref_id`; bước 3: `reason_code` là `source_invalid` hoặc `membership_missing` theo thiết kế cuối. Dữ liệu nhóm tham chiếu: hỏi team dev khi chuẩn bị.</t>
+      <c r="D809" s="1" t="inlineStr">
+        <is>
+          <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
     <row r="810">
-      <c r="D810" s="1" t="inlineStr">
-        <is>
-          <t>結果（Kết quả）</t>
-        </is>
-      </c>
+      <c r="E810" s="2" t="n"/>
     </row>
     <row r="811">
-      <c r="E811" s="2" t="n"/>
-    </row>
-    <row r="812">
-      <c r="D812" s="1" t="inlineStr">
+      <c r="D811" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
+    <row r="815">
+      <c r="C815" s="1" t="inlineStr">
+        <is>
+          <t>40. TC-RS-BR-039 — Nhóm môn học（科目グループ）: dùng cấu hình riêng của môn hoặc default đã lưu; thiếu/sai thì Chưa xét được</t>
+        </is>
+      </c>
+    </row>
     <row r="816">
-      <c r="C816" s="1" t="inlineStr">
-        <is>
-          <t>40. TC-RS-BR-040 — Loại nhóm được bật nhưng chưa có kết quả, hoặc tham chiếu đã lưu không còn hợp lệ → Chưa xét được, không tự đổi nhóm</t>
+      <c r="D816" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Đúng phạm vi tham chiếu” (AC-G12); tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13)</t>
         </is>
       </c>
     </row>
     <row r="817">
-      <c r="D817" s="3" t="inlineStr">
-        <is>
-          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13); tiêu chí nghiệm thu “Giữ kết quả trước khi chạy lại” (AC-G21)</t>
+      <c r="D817" s="1" t="inlineStr">
+        <is>
+          <t>前提条件（Điều kiện trước）</t>
         </is>
       </c>
     </row>
     <row r="818">
-      <c r="D818" s="1" t="inlineStr">
-        <is>
-          <t>前提条件（Điều kiện trước）</t>
+      <c r="E818" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: nhóm môn học “Nhóm môn Toán” có cấu hình riêng cho Toán I（数学Ⅰ） và default. Quy tắc trên mục số nguyên (M=100) dùng nguồn công thức = X / nhóm môn học “Nhóm môn Toán”, ngưỡng `A×0.5`, `&lt;`.</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="E819" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: Quy tắc trên mục số nguyên (M=100) có điều kiện Trung bình `A≥50`, cố định 30 `&lt;`; S01 = 29, đang Đỏ theo nguồn X / Lớp học（授業） đã tổng hợp.</t>
+          <t>・Dữ liệu test: nhóm môn học “Nhóm môn Toán”; mục số nguyên (M=100); S01 = 25</t>
         </is>
       </c>
     </row>
     <row r="820">
-      <c r="E820" s="2" t="inlineStr">
-        <is>
-          <t>・Dữ liệu test: thiết lập tổng hợp X đã bật thêm Lớp học（授業）, nhóm tổng hợp thứ hạng “Toán I khối 1+2”; mục số nguyên (M=100); học sinh S01 (điểm 29)</t>
+      <c r="D820" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
     <row r="821">
-      <c r="D821" s="1" t="inlineStr">
-        <is>
-          <t>操作（Thao tác）</t>
+      <c r="E821" s="2" t="inlineStr">
+        <is>
+          <t>1. Chạy nút cam; xem S01 và nhóm được dùng.</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="E822" s="2" t="inlineStr">
         <is>
-          <t>1. (a) Tạo quy tắc mới dùng nhóm tổng hợp nhóm tổng hợp thứ hạng “Toán I khối 1+2” nhưng X chưa chạy tổng hợp cho nhóm này; chạy nút cam; xem S01.</t>
+          <t>2. Xóa cấu hình riêng của Toán I (để môn rơi về default); chạy lại; xem.</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="E823" s="2" t="inlineStr">
         <is>
-          <t>2. (b) Quy tắc đang dùng X / Lớp học: tắt công tắc Lớp học（授業） của trường/năm; mở danh sách quy tắc và xem S01 (chưa chạy).</t>
+          <t>3. Làm default thiếu hoặc trỏ tới cấu hình không hợp lệ (biến thể (b) của nhóm môn học “Nhóm môn Toán”); chạy lại; xem trạng thái và thông báo.</t>
         </is>
       </c>
     </row>
     <row r="824">
-      <c r="E824" s="2" t="inlineStr">
-        <is>
-          <t>3. Chạy nút cam; xem S01.</t>
+      <c r="D824" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
     <row r="825">
       <c r="E825" s="2" t="inlineStr">
         <is>
-          <t>4. (c) Xóa nhóm nhóm tổng hợp thứ hạng “Toán I khối 1+2” đang được quy tắc khác tham chiếu; chạy nút cam; xem ô dùng quy tắc đó.</t>
+          <t>1. Dùng kết quả của nhóm theo cấu hình riêng của Toán I.</t>
         </is>
       </c>
     </row>
     <row r="826">
-      <c r="D826" s="1" t="inlineStr">
-        <is>
-          <t>期待結果（Kết quả mong đợi）</t>
+      <c r="E826" s="2" t="inlineStr">
+        <is>
+          <t>2. Dùng kết quả của nhóm theo default đã lưu.</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="E827" s="2" t="inlineStr">
         <is>
-          <t>1. S01 Chưa xét được (thiếu nguồn); lựa chọn nhóm tồn tại không có nghĩa đã có dữ liệu.</t>
+          <t>3. S01 Chưa xét được; không thay bằng nhóm khác, bằng 0 hay bằng kết quả trước; thông báo/tiến độ tách phần chưa xét được.</t>
         </is>
       </c>
     </row>
     <row r="828">
-      <c r="E828" s="2" t="inlineStr">
-        <is>
-          <t>2. Chỉ đổi cấu hình: S01 vẫn giữ kết quả Đỏ trước (không bị xóa ngay).</t>
+      <c r="D828" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="829">
       <c r="E829" s="2" t="inlineStr">
         <is>
-          <t>3. S01 Chưa xét được; không tự chuyển sang khối/lớp chủ nhiệm hoặc nhóm khác, không dùng quy tắc ưu tiên thấp hơn, không dùng kết quả cũ làm hiện hành.</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Ba loại nhóm cấu hình có xuất hiện ngoài khối/HR/lớp học không?” (Q33); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Đúng phạm vi tham chiếu” (AC-G12)/G13 (bảng quy tắc chọn/đọc nhóm: "Chọn nhóm môn học — dùng cấu hình riêng của môn hoặc default đã lưu. Không thay default thiếu/tham chiếu sai bằng nhóm khác hay 0"); thiết kế DB v2 (RSD-DB) mục 3.1 “Bộ thông tin nguồn”, mục 3.4 “`judgment_context`” (PROPOSED)</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="E830" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh cấu hình nhóm môn ở mỗi bước; ảnh kết quả S01; SELECT `reason_code` và `judgment_context.sources` nếu có schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="E831" s="2" t="inlineStr">
+        <is>
+          <t>・Ghi chú: (PROPOSED) Bước 1–2: `sources[]` giữ `population_type=6` và ID nhóm môn đã chọn, thêm `resolved_population_type`/`resolved_population_ref_id`; bước 3: `reason_code` là `source_invalid` hoặc `membership_missing` theo thiết kế cuối. Dữ liệu nhóm tham chiếu: hỏi team dev khi chuẩn bị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="D832" s="1" t="inlineStr">
+        <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="E833" s="2" t="n"/>
+    </row>
+    <row r="834">
+      <c r="D834" s="1" t="inlineStr">
+        <is>
+          <t>証跡（Bằng chứng）</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="C838" s="1" t="inlineStr">
+        <is>
+          <t>41. TC-RS-BR-040 — Loại nhóm được bật nhưng chưa có kết quả, hoặc tham chiếu đã lưu không còn hợp lệ → Chưa xét được, không tự đổi nhóm</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="D839" s="3" t="inlineStr">
+        <is>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13); tiêu chí nghiệm thu “Giữ kết quả trước khi chạy lại” (AC-G21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="D840" s="1" t="inlineStr">
+        <is>
+          <t>前提条件（Điều kiện trước）</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="E841" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: Quy tắc trên mục số nguyên (M=100) có điều kiện Trung bình `A≥50`, cố định 30 `&lt;`; S01 = 29, đang Đỏ theo nguồn X / Lớp học（授業） đã tổng hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="E842" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: thiết lập tổng hợp X đã bật thêm Lớp học（授業）, nhóm tổng hợp thứ hạng “Toán I khối 1+2”; mục số nguyên (M=100); học sinh S01 (điểm 29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="D843" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="E844" s="2" t="inlineStr">
+        <is>
+          <t>1. (a) Tạo quy tắc mới dùng nhóm tổng hợp nhóm tổng hợp thứ hạng “Toán I khối 1+2” nhưng X chưa chạy tổng hợp cho nhóm này; chạy nút cam; xem S01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="E845" s="2" t="inlineStr">
+        <is>
+          <t>2. (b) Quy tắc đang dùng X / Lớp học: tắt công tắc Lớp học（授業） của trường/năm; mở danh sách quy tắc và xem S01 (chưa chạy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="E846" s="2" t="inlineStr">
+        <is>
+          <t>3. Chạy nút cam; xem S01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="E847" s="2" t="inlineStr">
+        <is>
+          <t>4. (c) Xóa nhóm nhóm tổng hợp thứ hạng “Toán I khối 1+2” đang được quy tắc khác tham chiếu; chạy nút cam; xem ô dùng quy tắc đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="D848" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="E849" s="2" t="inlineStr">
+        <is>
+          <t>1. S01 Chưa xét được (thiếu nguồn); lựa chọn nhóm tồn tại không có nghĩa đã có dữ liệu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="E850" s="2" t="inlineStr">
+        <is>
+          <t>2. Chỉ đổi cấu hình: S01 vẫn giữ kết quả Đỏ trước (không bị xóa ngay).</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>3. S01 Chưa xét được; không tự chuyển sang khối/lớp chủ nhiệm hoặc nhóm khác, không dùng quy tắc ưu tiên thấp hơn, không dùng kết quả cũ làm hiện hành.</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="E852" s="2" t="inlineStr">
+        <is>
           <t>4. Ô chịu ảnh hưởng Chưa xét được; không âm thầm đổi loại/ID nhóm đã lưu.</t>
         </is>
       </c>
     </row>
-    <row r="831">
-      <c r="D831" s="1" t="inlineStr">
+    <row r="853">
+      <c r="D853" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
-    <row r="832">
-      <c r="E832" s="2" t="inlineStr">
+    <row r="854">
+      <c r="E854" s="2" t="inlineStr">
         <is>
           <t>・Nguồn: context điểm đỏ (CTX) mục 9.6 “Ba phản hồi review DB và bài học thiết kế ngày 28/09” (quyết định DB-R3 mục 4: được bật để chọn không đồng nghĩa đã có dữ liệu hợp lệ); đặc tả v2 (R18) mục 5.4 “Bộ thông tin nguồn”, mục 5.5 “Chọn bản nguồn”; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Ưu tiên bản chốt và xử lý thiếu nguồn” (AC-G13) ("Áp dụng cùng cách xử lý thiếu/không hợp lệ khi loại tổng hợp được bật nhưng chưa có kết quả, hoặc tham chiếu đã lưu trở nên không khả dụng trước lần xét lại"), tiêu chí nghiệm thu “Giữ kết quả trước khi chạy lại” (AC-G21); thiết kế DB v2 (RSD-DB) mục 3.1 “Bộ thông tin nguồn” (PROPOSED: `source_missing`, `source_invalid`; thay đổi cấu hình đơn thuần không xóa kết quả trước)</t>
         </is>
       </c>
     </row>
-    <row r="833">
-      <c r="E833" s="2" t="inlineStr">
+    <row r="855">
+      <c r="E855" s="2" t="inlineStr">
         <is>
           <t>・Bằng chứng cần chụp: Ảnh S01 sau mỗi bước; ảnh thông báo/tiến độ; SELECT `judgment_status`, `reason_code` nếu có schema.</t>
         </is>
       </c>
     </row>
-    <row r="834">
-      <c r="E834" s="2" t="inlineStr">
+    <row r="856">
+      <c r="E856" s="2" t="inlineStr">
         <is>
           <t>・Sau khi chạy: Bật lại công tắc Lớp học, khôi phục nhóm tổng hợp thứ hạng “Toán I khối 1+2”.</t>
         </is>
       </c>
     </row>
-    <row r="835">
-      <c r="E835" s="2" t="inlineStr">
+    <row r="857">
+      <c r="E857" s="2" t="inlineStr">
         <is>
           <t>・Ghi chú: (PROPOSED) Bước 1: `reason_code`=`source_missing`; bước 3–4: `source_invalid`. Nếu hệ thống chặn xóa nhóm đang được tham chiếu ở bước 4 thì ghi hành vi thực tế, không FAIL. Dữ liệu nhóm tham chiếu: hỏi team dev khi chuẩn bị.</t>
         </is>
       </c>
     </row>
-    <row r="836">
-      <c r="D836" s="1" t="inlineStr">
+    <row r="858">
+      <c r="D858" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="837">
-      <c r="E837" s="2" t="n"/>
-    </row>
-    <row r="838">
-      <c r="D838" s="1" t="inlineStr">
+    <row r="859">
+      <c r="E859" s="2" t="n"/>
+    </row>
+    <row r="860">
+      <c r="D860" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
@@ -13402,7 +13531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:F661"/>
+  <dimension ref="C2:F662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.13" customWidth="1" min="1" max="1"/>
@@ -15009,7 +15138,7 @@
     <row r="277">
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: S = 19.5</t>
+          <t>・Dữ liệu test: S = 19.1 và S = 19.2</t>
         </is>
       </c>
     </row>
@@ -15023,14 +15152,14 @@
     <row r="279">
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>(a) Dòng 1 xuống p1, dòng 2 không xử lý.</t>
+          <t>1. Lưu đúng cấu hình: dòng 1 bật xử lý phần lẻ, vị trí 1, làm tròn xuống; dòng 2 không xử lý.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>(b) Cả hai dòng không xử lý.</t>
+          <t>2. Chạy xét với `S=19.1` và `S=19.2`.</t>
         </is>
       </c>
     </row>
@@ -15044,2204 +15173,2211 @@
     <row r="282">
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>(a) `24.85→24`; `T=24×0.8=19.2` → Không đỏ.</t>
+          <t>1. `24.85→24`; `T=24×0.8=19.2`.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>(b) `T=24.85×0.8=19.88` → Đỏ.</t>
+          <t>2. Với dấu `&lt;`: `S=19.1` Đỏ và `S=19.2` Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="D284" s="1" t="inlineStr">
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>3. Không làm tròn dòng 2 thành `19`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="D285" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="E285" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 6.5 “Xử lý phần lẻ” (ví dụ `A=49.7`); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Công thức theo dòng và phần lẻ” (AC-G16) ("Tham chiếu dòng trước nhận giá trị sau phần lẻ"; ví dụ `A=49.7` → 19.2 / 19.88)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh cấu hình, kết quả.</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 6.5 “Xử lý phần lẻ” (ví dụ `A=49.7`); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Công thức theo dòng và phần lẻ” (AC-G16); xác nhận thiết kế ngày 30/09 (Q37: dòng 1 cắt xuống, dòng 2 không xử lý; `T=19.2`, `S=19.1` với `&lt;` là đỏ).</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="E287" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh cấu hình, kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="E288" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: Là ví dụ của tiêu chí nghiệm thu “Công thức theo dòng và phần lẻ”. Chỉ chạy khi công thức nhiều dòng thuộc đợt phát hành (phạm vi phát hành chưa chốt — đặc tả v2 mục 13.1); ngoài đợt thì SKIPPED.</t>
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="D288" s="1" t="inlineStr">
+    <row r="289">
+      <c r="D289" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="E289" s="2" t="n"/>
-    </row>
     <row r="290">
-      <c r="D290" s="1" t="inlineStr">
+      <c r="E290" s="2" t="n"/>
+    </row>
+    <row r="291">
+      <c r="D291" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="294">
-      <c r="C294" s="1" t="inlineStr">
-        <is>
-          <t>15. TC-RS-CALC-015 — Công thức hai dòng theo Figma: (A÷2)×0.8, xuống p1 ở dòng 2</t>
-        </is>
-      </c>
-    </row>
     <row r="295">
-      <c r="D295" s="3" t="inlineStr">
+      <c r="C295" s="1" t="inlineStr">
+        <is>
+          <t>15. TC-RS-CALC-015 — Công thức hai dòng theo Figma: (A÷2)×0.8, dòng 1 làm tròn xuống</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="D296" s="3" t="inlineStr">
         <is>
           <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Công thức theo dòng và phần lẻ” (AC-G16)</t>
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="D296" s="1" t="inlineStr">
+    <row r="297">
+      <c r="D297" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="E297" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: quy tắc công thức hai dòng (trung bình ÷ 2 × 0.8); nguồn `A=61`.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: quy tắc công thức hai dòng (trung bình ÷ 2 × 0.8); S = 23.9, 24</t>
+          <t>・Điều kiện: quy tắc công thức hai dòng (trung bình ÷ 2 × 0.8); nguồn `A=61`.</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="D299" s="1" t="inlineStr">
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: quy tắc công thức hai dòng (trung bình ÷ 2 × 0.8); S = 24, 24.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="D300" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="300">
-      <c r="E300" s="2" t="inlineStr">
+    <row r="301">
+      <c r="E301" s="2" t="inlineStr">
         <is>
           <t>・Chạy nút cam; xét với `&lt;` rồi `≤`.</t>
         </is>
       </c>
     </row>
-    <row r="301">
-      <c r="D301" s="1" t="inlineStr">
+    <row r="302">
+      <c r="D302" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="E302" s="2" t="inlineStr">
-        <is>
-          <t>・Dòng 1 `61÷2=30.5`; dòng 2 `30.5×0.8=24.4` → xuống p1 → `T=24`.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>・`&lt;`: 23.9 Đỏ; 24 Không đỏ. `≤`: 24 Đỏ.</t>
+          <t>・Dòng 1 `61÷2=30.5`; dòng 2 `30.5×0.8=24.4`, không xử lý phần lẻ ở dòng 2 → `T=24.4`.</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="D304" s="1" t="inlineStr">
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>・`&lt;`: 24 Đỏ; 24.4 Không đỏ. `≤`: 24.4 Đỏ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="D305" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="E305" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Figma MW “màn Ngưỡng – công thức” (58:8389) (UI 04C, công thức hai dòng); đặc tả v2 (R18) mục 6.4 “Công thức dùng trung bình”; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Công thức theo dòng và phần lẻ” (AC-G16) ("Tham chiếu dòng trước nhận giá trị sau phần lẻ, dòng cuối tạo `T`")</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh cấu hình, kết quả.</t>
+          <t>・Nguồn: Figma MW “màn Ngưỡng – công thức” (58:8389) (UI 04C, công thức hai dòng); đặc tả v2 (R18) mục 6.4 “Công thức dùng trung bình”; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Công thức theo dòng và phần lẻ” (AC-G16) ("Tham chiếu dòng trước nhận giá trị sau phần lẻ, dòng cuối tạo `T`")</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="E307" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh cấu hình, kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="E308" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: Tham chiếu dòng trước là tiêu chí nghiệm thu “Công thức theo dòng và phần lẻ”; danh sách toán hạng đầy đủ vẫn theo phạm vi đợt (đề xuất thiết kế chờ review — đặc tả v2 mục 13.1). Chỉ chạy khi công thức nhiều dòng thuộc đợt phát hành (phạm vi phát hành chưa chốt — đặc tả v2 mục 13.1); ngoài đợt thì SKIPPED.</t>
         </is>
       </c>
     </row>
-    <row r="308">
-      <c r="D308" s="1" t="inlineStr">
+    <row r="309">
+      <c r="D309" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="309">
-      <c r="E309" s="2" t="n"/>
-    </row>
     <row r="310">
-      <c r="D310" s="1" t="inlineStr">
+      <c r="E310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="D311" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="314">
-      <c r="C314" s="1" t="inlineStr">
+    <row r="315">
+      <c r="C315" s="1" t="inlineStr">
         <is>
           <t>16. TC-RS-CALC-016 — Ngưỡng âm: A=15, A−20 → T=−5</t>
         </is>
       </c>
     </row>
-    <row r="315">
-      <c r="D315" s="3" t="inlineStr">
+    <row r="316">
+      <c r="D316" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Ngưỡng âm” (AC-G18)</t>
         </is>
       </c>
     </row>
-    <row r="316">
-      <c r="D316" s="1" t="inlineStr">
+    <row r="317">
+      <c r="D317" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="E317" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: quy tắc công thức trung bình − 20; nguồn `A=15`. Biến thể (b) cần mục cho phép điểm âm.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="E318" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: quy tắc công thức trung bình − 20; nguồn `A=15`. Biến thể (b) cần mục cho phép điểm âm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="E319" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: quy tắc công thức trung bình − 20; (a) Mục thường: S = 0; (b) mục cho phép điểm âm: S = −6, −5</t>
         </is>
       </c>
     </row>
-    <row r="319">
-      <c r="D319" s="1" t="inlineStr">
+    <row r="320">
+      <c r="D320" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="E320" s="2" t="inlineStr">
-        <is>
-          <t>(a) Xét S=0 với `&lt;` và `≤`.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="E321" s="2" t="inlineStr">
         <is>
+          <t>(a) Xét S=0 với `&lt;` và `≤`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="E322" s="2" t="inlineStr">
+        <is>
           <t>(b) Xét −6, −5 với `&lt;` và `≤`.</t>
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="D322" s="1" t="inlineStr">
+    <row r="323">
+      <c r="D323" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>(a) `T=−5`: `&lt;` Không đỏ; `≤` Không đỏ (nếu hệ thống ép `T` về 0 thì `≤` sẽ Đỏ — sai).</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="E324" s="2" t="inlineStr">
         <is>
+          <t>(a) `T=−5`: `&lt;` Không đỏ; `≤` Không đỏ (nếu hệ thống ép `T` về 0 thì `≤` sẽ Đỏ — sai).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="E325" s="2" t="inlineStr">
+        <is>
           <t>(b) `&lt;`: −6 Đỏ; −5 Không đỏ. `≤`: −6 Đỏ; −5 Đỏ.</t>
         </is>
       </c>
     </row>
-    <row r="325">
-      <c r="D325" s="1" t="inlineStr">
+    <row r="326">
+      <c r="D326" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="E326" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Công thức cho ngưỡng âm thì xử lý thế nào?” (Q25); đặc tả v2 (R18) mục 6.6 “Ngưỡng âm và cảnh báo biên”</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh nguồn `A=15`; Ảnh Trích xuất（tài liệu “Chiến lược kiểm thử” mục 9 “Quy ước thực thi chung”） các ô (a), (b) với `&lt;` và với `≤`.</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Công thức cho ngưỡng âm thì xử lý thế nào?” (Q25); đặc tả v2 (R18) mục 6.6 “Ngưỡng âm và cảnh báo biên”</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="E328" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh nguồn `A=15`; Ảnh Trích xuất（tài liệu “Chiến lược kiểm thử” mục 9 “Quy ước thực thi chung”） các ô (a), (b) với `&lt;` và với `≤`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="E329" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: (b) phụ thuộc cách tạo dữ liệu đặc biệt (hỏi team dev khi chuẩn bị).</t>
         </is>
       </c>
     </row>
-    <row r="329">
-      <c r="D329" s="1" t="inlineStr">
+    <row r="330">
+      <c r="D330" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="330">
-      <c r="E330" s="2" t="n"/>
-    </row>
     <row r="331">
-      <c r="D331" s="1" t="inlineStr">
+      <c r="E331" s="2" t="n"/>
+    </row>
+    <row r="332">
+      <c r="D332" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="335">
-      <c r="C335" s="1" t="inlineStr">
+    <row r="336">
+      <c r="C336" s="1" t="inlineStr">
         <is>
           <t>17. TC-RS-CALC-017 — Ngưỡng công thức vượt M vẫn hợp lệ</t>
         </is>
       </c>
     </row>
-    <row r="336">
-      <c r="D336" s="3" t="inlineStr">
+    <row r="337">
+      <c r="D337" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Công thức theo dòng và phần lẻ” (AC-G16)</t>
         </is>
       </c>
     </row>
-    <row r="337">
-      <c r="D337" s="1" t="inlineStr">
+    <row r="338">
+      <c r="D338" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="E338" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Nguồn `A=80`; công thức `A×1.5`; mục số nguyên (M=100) (M=100).</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="E339" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: Nguồn `A=80`; công thức `A×1.5`; mục số nguyên (M=100) (M=100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="E340" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: mục số nguyên (M=100); S = 100</t>
         </is>
       </c>
     </row>
-    <row r="340">
-      <c r="D340" s="1" t="inlineStr">
+    <row r="341">
+      <c r="D341" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="341">
-      <c r="E341" s="2" t="inlineStr">
+    <row r="342">
+      <c r="E342" s="2" t="inlineStr">
         <is>
           <t>・Chạy nút cam; xem kết quả.</t>
         </is>
       </c>
     </row>
-    <row r="342">
-      <c r="D342" s="1" t="inlineStr">
+    <row r="343">
+      <c r="D343" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
-    <row r="343">
-      <c r="E343" s="2" t="inlineStr">
+    <row r="344">
+      <c r="E344" s="2" t="inlineStr">
         <is>
           <t>・`T=120`; `100&lt;120` → Đỏ. Không bị Chưa xét được, không ép `T` về 100.</t>
         </is>
       </c>
     </row>
-    <row r="344">
-      <c r="D344" s="1" t="inlineStr">
+    <row r="345">
+      <c r="D345" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="E345" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 6.6 “Ngưỡng âm và cảnh báo biên” (đoạn cuối: "ngưỡng công thức vượt maximum không tự trở thành lỗi")</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="E346" s="2" t="inlineStr">
         <is>
+          <t>・Nguồn: đặc tả v2 (R18) mục 6.6 “Ngưỡng âm và cảnh báo biên” (đoạn cuối: "ngưỡng công thức vượt maximum không tự trở thành lỗi")</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="E347" s="2" t="inlineStr">
+        <is>
           <t>・Bằng chứng cần chụp: Ảnh Trích xuất（tài liệu “Chiến lược kiểm thử” mục 9 “Quy ước thực thi chung”） ô S=100; ảnh SELECT `judgment_context` có ngưỡng 120 (khi có schema).</t>
         </is>
       </c>
     </row>
-    <row r="347">
-      <c r="D347" s="1" t="inlineStr">
+    <row r="348">
+      <c r="D348" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="348">
-      <c r="E348" s="2" t="n"/>
-    </row>
     <row r="349">
-      <c r="D349" s="1" t="inlineStr">
+      <c r="E349" s="2" t="n"/>
+    </row>
+    <row r="350">
+      <c r="D350" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="C353" s="1" t="inlineStr">
+    <row r="354">
+      <c r="C354" s="1" t="inlineStr">
         <is>
           <t>18. TC-RS-CALC-018 — Công thức A−0 cho ngưỡng bằng A</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="D354" s="3" t="inlineStr">
+    <row r="355">
+      <c r="D355" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Biên so sánh và cảnh báo” (AC-G07)</t>
         </is>
       </c>
     </row>
-    <row r="355">
-      <c r="D355" s="1" t="inlineStr">
+    <row r="356">
+      <c r="D356" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="E356" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Nguồn `A=50`; công thức `A−0`, `&lt;`.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="E357" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: Nguồn `A=50`; công thức `A−0`, `&lt;`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="E358" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: S = 49, 50</t>
         </is>
       </c>
     </row>
-    <row r="358">
-      <c r="D358" s="1" t="inlineStr">
+    <row r="359">
+      <c r="D359" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="E359" s="2" t="inlineStr">
-        <is>
-          <t>1. Lưu công thức (quan sát cảnh báo).</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="E360" s="2" t="inlineStr">
         <is>
+          <t>1. Lưu công thức (quan sát cảnh báo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="E361" s="2" t="inlineStr">
+        <is>
           <t>2. Chạy nút cam.</t>
         </is>
       </c>
     </row>
-    <row r="361">
-      <c r="D361" s="1" t="inlineStr">
+    <row r="362">
+      <c r="D362" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="E362" s="2" t="inlineStr">
-        <is>
-          <t>1. Có cảnh báo giúp hiểu ngưỡng là A (câu chữ TBD), vẫn lưu được.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="E363" s="2" t="inlineStr">
         <is>
+          <t>1. Có cảnh báo giúp hiểu ngưỡng là A (câu chữ TBD), vẫn lưu được.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="E364" s="2" t="inlineStr">
+        <is>
           <t>2. `T=50`: 49 Đỏ; 50 Không đỏ.</t>
         </is>
       </c>
     </row>
-    <row r="364">
-      <c r="D364" s="1" t="inlineStr">
+    <row r="365">
+      <c r="D365" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="E365" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 6.6 “Ngưỡng âm và cảnh báo biên” (bảng cảnh báo: "Công thức `A−0`: ngưỡng là `A`, không phải 0")</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh cảnh báo, kết quả.</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 6.6 “Ngưỡng âm và cảnh báo biên” (bảng cảnh báo: "Công thức `A−0`: ngưỡng là `A`, không phải 0")</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh cảnh báo, kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="E368" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: Câu chữ cảnh báo: chưa chốt.</t>
         </is>
       </c>
     </row>
-    <row r="368">
-      <c r="D368" s="1" t="inlineStr">
+    <row r="369">
+      <c r="D369" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="369">
-      <c r="E369" s="2" t="n"/>
-    </row>
     <row r="370">
-      <c r="D370" s="1" t="inlineStr">
+      <c r="E370" s="2" t="n"/>
+    </row>
+    <row r="371">
+      <c r="D371" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="374">
-      <c r="C374" s="1" t="inlineStr">
+    <row r="375">
+      <c r="C375" s="1" t="inlineStr">
         <is>
           <t>19. TC-RS-CALC-019 — Định nghĩa phương thức làm tròn, số âm và p=9</t>
         </is>
       </c>
     </row>
-    <row r="375">
-      <c r="D375" s="3" t="inlineStr">
+    <row r="376">
+      <c r="D376" s="3" t="inlineStr">
         <is>
           <t>Priority: TBD ｜ Status: PROPOSED ｜ Requirement ID: tiêu chí nghiệm thu “Công thức theo dòng và phần lẻ” (AC-G16)</t>
         </is>
       </c>
     </row>
-    <row r="376">
-      <c r="D376" s="1" t="inlineStr">
+    <row r="377">
+      <c r="D377" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="E377" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Dùng công thức một dòng `A+0` hoặc `A×1` để đưa giá trị vào bước làm tròn (nguồn dummy có `A` bằng giá trị cần thử).</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="E378" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: Dùng công thức một dòng `A+0` hoặc `A×1` để đưa giá trị vào bước làm tròn (nguồn dummy có `A` bằng giá trị cần thử).</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="E379" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: Bảng ở Expected Result</t>
         </is>
       </c>
     </row>
-    <row r="379">
-      <c r="D379" s="1" t="inlineStr">
+    <row r="380">
+      <c r="D380" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="E380" s="2" t="inlineStr">
-        <is>
-          <t>1. Với từng dòng của Expected Result: đặt `A` (nguồn dummy, dữ liệu giả cho bản tổng hợp đã chốt), chọn xử lý phần lẻ.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>2. Chạy lại (nút cam).</t>
+          <t>1. Với từng dòng của Expected Result: đặt `A` (nguồn dummy, dữ liệu giả cho bản tổng hợp đã chốt), chọn xử lý phần lẻ.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="E382" s="2" t="inlineStr">
         <is>
+          <t>2. Chạy lại (nút cam).</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="E383" s="2" t="inlineStr">
+        <is>
           <t>3. Đọc `T` qua thông tin giải thích (case “Lưu thông tin giải thích kết quả”) hoặc qua kết quả xét với S sát ngưỡng.</t>
         </is>
       </c>
     </row>
-    <row r="383">
-      <c r="D383" s="1" t="inlineStr">
+    <row r="384">
+      <c r="D384" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="E384" s="2" t="inlineStr">
-        <is>
-          <t>・29.7 không xử lý → 29.7.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>・29.7 xuống p1 → 29.</t>
+          <t>・29.7 không xử lý → 29.7.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>・29.75 gần nhất p2 → 29.8.</t>
+          <t>・29.7 xuống p1 → 29.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>・−5.2 lên p1 → −5.</t>
+          <t>・29.75 gần nhất p2 → 29.8.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>・−5.2 xuống p1 → −6.</t>
+          <t>・−5.2 lên p1 → −5.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>・−5.5 gần nhất p1 → −6.</t>
+          <t>・−5.2 xuống p1 → −6.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>・12.5 gần nhất p1 → 13; −12.5 gần nhất p1 → −13; −12.5 lên p1 → −12; −12.5 xuống p1 → −13.</t>
+          <t>・−5.5 gần nhất p1 → −6.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>・12.345 gần nhất p2 → 12.3; lên p2 → 12.4.</t>
+          <t>・12.5 gần nhất p1 → 13; −12.5 gần nhất p1 → −13; −12.5 lên p1 → −12; −12.5 xuống p1 → −13.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>・2.675 gần nhất p3 → 2.68.</t>
+          <t>・12.345 gần nhất p2 → 12.3; lên p2 → 12.4.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="E393" s="2" t="inlineStr">
         <is>
+          <t>・2.675 gần nhất p3 → 2.68.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="E394" s="2" t="inlineStr">
+        <is>
           <t>・1.123456789 gần nhất p9 → 1.12345679; xuống p9 → 1.12345678.</t>
         </is>
       </c>
     </row>
-    <row r="394">
-      <c r="D394" s="1" t="inlineStr">
+    <row r="395">
+      <c r="D395" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="E395" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 6.5 “Xử lý phần lẻ” (bảng ví dụ, định nghĩa gần nhất = nửa đơn vị ra xa 0, lên = `ceil`, xuống = `floor`); CODE `AutoRating.php::calcDecimalPlace` :3896–3915</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Bảng thực tế đối chiếu từng dòng.</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 6.5 “Xử lý phần lẻ” (bảng ví dụ, định nghĩa gần nhất = nửa đơn vị ra xa 0, lên = `ceil`, xuống = `floor`); CODE `AutoRating.php::calcDecimalPlace` :3896–3915</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="E397" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Bảng thực tế đối chiếu từng dòng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="E398" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: PROPOSED. 2.675 kiểm việc tránh sai số nhị phân (đặc tả v2 mục 6.8 “Yêu cầu độ chính xác”). Giá trị âm cần mục cho phép điểm âm nếu kiểm qua kết quả xét.</t>
         </is>
       </c>
     </row>
-    <row r="398">
-      <c r="D398" s="1" t="inlineStr">
+    <row r="399">
+      <c r="D399" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="399">
-      <c r="E399" s="2" t="n"/>
-    </row>
     <row r="400">
-      <c r="D400" s="1" t="inlineStr">
+      <c r="E400" s="2" t="n"/>
+    </row>
+    <row r="401">
+      <c r="D401" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="404">
-      <c r="C404" s="1" t="inlineStr">
+    <row r="405">
+      <c r="C405" s="1" t="inlineStr">
         <is>
           <t>20. TC-RS-CALC-020 — Làm tròn ngưỡng, không làm tròn điểm học sinh</t>
         </is>
       </c>
     </row>
-    <row r="405">
-      <c r="D405" s="3" t="inlineStr">
+    <row r="406">
+      <c r="D406" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Công thức theo dòng và phần lẻ” (AC-G16)</t>
         </is>
       </c>
     </row>
-    <row r="406">
-      <c r="D406" s="1" t="inlineStr">
+    <row r="407">
+      <c r="D407" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="E407" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: mục số thập phân (M=100) với M=99; tỷ lệ 30% (`T_thô=29.7`), `&lt;`.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="E408" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: mục số thập phân (M=100) với M=99; tỷ lệ 30% (`T_thô=29.7`), `&lt;`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="E409" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: mục số thập phân (M=100); S = 29.5</t>
         </is>
       </c>
     </row>
-    <row r="409">
-      <c r="D409" s="1" t="inlineStr">
+    <row r="410">
+      <c r="D410" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="E410" s="2" t="inlineStr">
-        <is>
-          <t>(a) Xuống p1.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="E411" s="2" t="inlineStr">
         <is>
+          <t>(a) Xuống p1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="E412" s="2" t="inlineStr">
+        <is>
           <t>(b) Gần nhất p1.</t>
         </is>
       </c>
     </row>
-    <row r="412">
-      <c r="D412" s="1" t="inlineStr">
+    <row r="413">
+      <c r="D413" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="E413" s="2" t="inlineStr">
-        <is>
-          <t>(a) `T=29`; `29.5&lt;29` sai → Không đỏ. (Nếu làm tròn S thành 29 và giữ `T=29.7` → Đỏ — sai.)</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>(b) `T=30`; `29.5&lt;30` → Đỏ. (Nếu làm tròn S thành 30 → Không đỏ — sai.)</t>
+          <t>(a) `T=29`; `29.5&lt;29` sai → Không đỏ. (Nếu làm tròn S thành 29 và giữ `T=29.7` → Đỏ — sai.)</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="E415" s="2" t="inlineStr">
         <is>
+          <t>(b) `T=30`; `29.5&lt;30` → Đỏ. (Nếu làm tròn S thành 30 → Không đỏ — sai.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="E416" s="2" t="inlineStr">
+        <is>
           <t>・Điểm lưu vẫn 29.5.</t>
         </is>
       </c>
     </row>
-    <row r="416">
-      <c r="D416" s="1" t="inlineStr">
+    <row r="417">
+      <c r="D417" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="E417" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Tỷ lệ điểm tối đa có cho chọn xử lý phần lẻ không?” (Q24) ("Không cắt/làm tròn điểm của học sinh thay cho ngưỡng"); đặc tả v2 (R18) mục 6.5 “Xử lý phần lẻ” (đoạn cuối)</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả, điểm.</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Tỷ lệ điểm tối đa có cho chọn xử lý phần lẻ không?” (Q24) ("Không cắt/làm tròn điểm của học sinh thay cho ngưỡng"); đặc tả v2 (R18) mục 6.5 “Xử lý phần lẻ” (đoạn cuối)</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="E419" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả, điểm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="E420" s="2" t="inlineStr">
+        <is>
           <t>・Sau khi chạy: Trả M về 100.</t>
         </is>
       </c>
     </row>
-    <row r="420">
-      <c r="D420" s="1" t="inlineStr">
+    <row r="421">
+      <c r="D421" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="421">
-      <c r="E421" s="2" t="n"/>
-    </row>
     <row r="422">
-      <c r="D422" s="1" t="inlineStr">
+      <c r="E422" s="2" t="n"/>
+    </row>
+    <row r="423">
+      <c r="D423" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="426">
-      <c r="C426" s="1" t="inlineStr">
+    <row r="427">
+      <c r="C427" s="1" t="inlineStr">
         <is>
           <t>21. TC-RS-CALC-021 — Chia 0 phát sinh khi chạy → Chưa xét được</t>
         </is>
       </c>
     </row>
-    <row r="427">
-      <c r="D427" s="3" t="inlineStr">
+    <row r="428">
+      <c r="D428" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: đặc tả v2 mục 6.4 “Công thức dùng trung bình”, mục 8.3 “Không tạo được ngưỡng hợp lệ”</t>
         </is>
       </c>
     </row>
-    <row r="428">
-      <c r="D428" s="1" t="inlineStr">
+    <row r="429">
+      <c r="D429" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="E429" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: quy tắc công thức 100 ÷ trung bình (`100÷A`), `&lt;`, mục số thập phân (M=100).</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="E430" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: quy tắc công thức 100 ÷ trung bình (`100÷A`), `&lt;`, mục số thập phân (M=100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="E431" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: mục số thập phân (M=100), quy tắc công thức 100 ÷ trung bình; (a) nhóm có trung bình 0 `A=0`; (b) `A=4`, S = 24; (c) `A=3`, S = 33.33, 33.34</t>
         </is>
       </c>
     </row>
-    <row r="431">
-      <c r="D431" s="1" t="inlineStr">
+    <row r="432">
+      <c r="D432" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="432">
-      <c r="E432" s="2" t="inlineStr">
+    <row r="433">
+      <c r="E433" s="2" t="inlineStr">
         <is>
           <t>・Chạy nút cam cho từng nguồn.</t>
         </is>
       </c>
     </row>
-    <row r="433">
-      <c r="D433" s="1" t="inlineStr">
+    <row r="434">
+      <c r="D434" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="E434" s="2" t="inlineStr">
-        <is>
-          <t>(a) Chưa xét được; không dùng ưu tiên thấp hơn.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>(b) `T=25` → 24 Đỏ.</t>
+          <t>(a) Chưa xét được; không dùng ưu tiên thấp hơn.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="E436" s="2" t="inlineStr">
         <is>
+          <t>(b) `T=25` → 24 Đỏ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="E437" s="2" t="inlineStr">
+        <is>
           <t>(c) `T=33.333…` → 33.33 Đỏ; 33.34 Không đỏ.</t>
         </is>
       </c>
     </row>
-    <row r="437">
-      <c r="D437" s="1" t="inlineStr">
+    <row r="438">
+      <c r="D438" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="E438" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 6.4 “Công thức dùng trung bình” (đoạn cuối), mục 8.3 “Không tạo được ngưỡng hợp lệ”; CODE `AutoRating.php::getformulas` :2834–2837 (trả NULL khi chia 0)</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="E439" s="2" t="inlineStr">
         <is>
+          <t>・Nguồn: đặc tả v2 (R18) mục 6.4 “Công thức dùng trung bình” (đoạn cuối), mục 8.3 “Không tạo được ngưỡng hợp lệ”; CODE `AutoRating.php::getformulas` :2834–2837 (trả NULL khi chia 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="E440" s="2" t="inlineStr">
+        <is>
           <t>・Bằng chứng cần chụp: Ảnh kết quả. SELECT `reason_code` (khi có schema; đề xuất `division_by_zero` — thiết kế DB v2 mục 4.3 “Trạng thái kết quả”, PROPOSED).</t>
         </is>
       </c>
     </row>
-    <row r="440">
-      <c r="D440" s="1" t="inlineStr">
+    <row r="441">
+      <c r="D441" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="441">
-      <c r="E441" s="2" t="n"/>
-    </row>
     <row r="442">
-      <c r="D442" s="1" t="inlineStr">
+      <c r="E442" s="2" t="n"/>
+    </row>
+    <row r="443">
+      <c r="D443" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="446">
-      <c r="C446" s="1" t="inlineStr">
+    <row r="447">
+      <c r="C447" s="1" t="inlineStr">
         <is>
           <t>22. TC-RS-CALC-022 — Phân nhánh theo trung bình: A = 40 / 50 / 49.99 (dùng A trước làm tròn)</t>
         </is>
       </c>
     </row>
-    <row r="447">
-      <c r="D447" s="3" t="inlineStr">
+    <row r="448">
+      <c r="D448" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14)</t>
         </is>
       </c>
     </row>
-    <row r="448">
-      <c r="D448" s="1" t="inlineStr">
+    <row r="449">
+      <c r="D449" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="E449" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Ưu tiên 1: `A≥50` → cố định 30 `&lt;`. Ưu tiên 2: `A&lt;50` → `A×0.5` `&lt;`. mục số thập phân (M=100).</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="E450" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: Ưu tiên 1: `A≥50` → cố định 30 `&lt;`. Ưu tiên 2: `A&lt;50` → `A×0.5` `&lt;`. mục số thập phân (M=100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="E451" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: mục số thập phân (M=100); Nguồn `A=40`, `A=50`, `A=49.99` (bản tổng hợp đã chốt (trung bình 49.99), màn tổng hợp hiện 50.0); S = 19, 20, 24.99, 25, 29, 30</t>
         </is>
       </c>
     </row>
-    <row r="451">
-      <c r="D451" s="1" t="inlineStr">
+    <row r="452">
+      <c r="D452" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="E452" s="2" t="inlineStr">
-        <is>
-          <t>1. Với từng nguồn, chạy nút cam, xem kết quả.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="E453" s="2" t="inlineStr">
         <is>
+          <t>1. Với từng nguồn, chạy nút cam, xem kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="E454" s="2" t="inlineStr">
+        <is>
           <t>2. Với `A=49.99`: bật gần nhất p1 cho dòng `A×0.5`, chạy lại.</t>
         </is>
       </c>
     </row>
-    <row r="454">
-      <c r="D454" s="1" t="inlineStr">
+    <row r="455">
+      <c r="D455" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="E455" s="2" t="inlineStr">
-        <is>
-          <t>・`A=40` → ưu tiên 2, `T=20`: 19 Đỏ; 20 Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>・`A=50` → ưu tiên 1, `T=30`: 29 Đỏ; 30 Không đỏ.</t>
+          <t>・`A=40` → ưu tiên 2, `T=20`: 19 Đỏ; 20 Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>・`A=49.99` → ưu tiên 2, `T=24.995`: 24.99 Đỏ; 25 Không đỏ; 29 Không đỏ (nếu dùng 50 thì 29 Đỏ — sai).</t>
+          <t>・`A=50` → ưu tiên 1, `T=30`: 29 Đỏ; 30 Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="E458" s="2" t="inlineStr">
         <is>
+          <t>・`A=49.99` → ưu tiên 2, `T=24.995`: 24.99 Đỏ; 25 Không đỏ; 29 Không đỏ (nếu dùng 50 thì 29 Đỏ — sai).</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="E459" s="2" t="inlineStr">
+        <is>
           <t>・Bước 2: `T=25`, vẫn ưu tiên 2: 24.99 Đỏ; 29 Không đỏ.</t>
         </is>
       </c>
     </row>
-    <row r="459">
-      <c r="D459" s="1" t="inlineStr">
+    <row r="460">
+      <c r="D460" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="E460" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Trung bình dùng để chọn nhánh là trước hay sau làm tròn?” (Q8); đặc tả v2 (R18) mục 5.2 “Điều kiện dựa trên trung bình” ("49.99 phải đi vào nhánh `&lt;50`")</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh nguồn (dummy), kết quả.</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Trung bình dùng để chọn nhánh là trước hay sau làm tròn?” (Q8); đặc tả v2 (R18) mục 5.2 “Điều kiện dựa trên trung bình” ("49.99 phải đi vào nhánh `&lt;50`")</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="E462" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh nguồn (dummy), kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="E463" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: Dạng hai dòng `A×50÷100` (ví dụ trao đổi ban đầu) cần Kết quả phép tính（式の結果） (PROPOSED); kết quả tương đương.</t>
         </is>
       </c>
     </row>
-    <row r="463">
-      <c r="D463" s="1" t="inlineStr">
+    <row r="464">
+      <c r="D464" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="464">
-      <c r="E464" s="2" t="n"/>
-    </row>
     <row r="465">
-      <c r="D465" s="1" t="inlineStr">
+      <c r="E465" s="2" t="n"/>
+    </row>
+    <row r="466">
+      <c r="D466" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="469">
-      <c r="C469" s="1" t="inlineStr">
+    <row r="470">
+      <c r="C470" s="1" t="inlineStr">
         <is>
           <t>23. TC-RS-CALC-023 — Biên nhánh A=60.00 và A=59.96</t>
         </is>
       </c>
     </row>
-    <row r="470">
-      <c r="D470" s="3" t="inlineStr">
+    <row r="471">
+      <c r="D471" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14)</t>
         </is>
       </c>
     </row>
-    <row r="471">
-      <c r="D471" s="1" t="inlineStr">
+    <row r="472">
+      <c r="D472" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="E472" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Ưu tiên 1: `A≥60` → cố định 25 `&lt;`. Ưu tiên 2: `A&lt;60` → `A×0.5` `&lt;`. mục số thập phân (M=100).</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="E473" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: Ưu tiên 1: `A≥60` → cố định 25 `&lt;`. Ưu tiên 2: `A&lt;60` → `A×0.5` `&lt;`. mục số thập phân (M=100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="E474" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: mục số thập phân (M=100); hai nguồn có trung bình 60 và 59.96 (`A=60.00`; `A=59.96`); S = 27, 29.99</t>
         </is>
       </c>
     </row>
-    <row r="474">
-      <c r="D474" s="1" t="inlineStr">
+    <row r="475">
+      <c r="D475" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="475">
-      <c r="E475" s="2" t="inlineStr">
+    <row r="476">
+      <c r="E476" s="2" t="inlineStr">
         <is>
           <t>・Chạy nút cam với từng nguồn.</t>
         </is>
       </c>
     </row>
-    <row r="476">
-      <c r="D476" s="1" t="inlineStr">
+    <row r="477">
+      <c r="D477" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="E477" s="2" t="inlineStr">
-        <is>
-          <t>・`A=60.00` → ưu tiên 1, `T=25`: 27 Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="E478" s="2" t="inlineStr">
         <is>
+          <t>・`A=60.00` → ưu tiên 1, `T=25`: 27 Không đỏ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="E479" s="2" t="inlineStr">
+        <is>
           <t>・`A=59.96` → ưu tiên 2, `T=29.98`: 27 Đỏ; 29.99 Không đỏ.</t>
         </is>
       </c>
     </row>
-    <row r="479">
-      <c r="D479" s="1" t="inlineStr">
+    <row r="480">
+      <c r="D480" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="E480" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Trung bình dùng để chọn nhánh là trước hay sau làm tròn?” (Q8); đặc tả v2 (R18) mục 5.2 “Điều kiện dựa trên trung bình”</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh nguồn, kết quả.</t>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Trung bình dùng để chọn nhánh là trước hay sau làm tròn?” (Q8); đặc tả v2 (R18) mục 5.2 “Điều kiện dựa trên trung bình”</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="E482" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh nguồn, kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="E483" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: Dấu `≥` có trong ví dụ đặc tả v2 mục 5.2 “Điều kiện dựa trên trung bình”; bộ bốn dấu điều kiện là PROPOSED (đề xuất thiết kế chờ review — đặc tả v2 mục 13.1).</t>
         </is>
       </c>
     </row>
-    <row r="483">
-      <c r="D483" s="1" t="inlineStr">
+    <row r="484">
+      <c r="D484" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="484">
-      <c r="E484" s="2" t="n"/>
-    </row>
     <row r="485">
-      <c r="D485" s="1" t="inlineStr">
+      <c r="E485" s="2" t="n"/>
+    </row>
+    <row r="486">
+      <c r="D486" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="489">
-      <c r="C489" s="1" t="inlineStr">
+    <row r="490">
+      <c r="C490" s="1" t="inlineStr">
         <is>
           <t>24. TC-RS-CALC-024 — Tỷ lệ nhóm R = 70% khớp điều kiện ≥ 65%</t>
         </is>
       </c>
     </row>
-    <row r="490">
-      <c r="D490" s="3" t="inlineStr">
+    <row r="491">
+      <c r="D491" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Kế thừa tỷ lệ nhóm” (AC-G15)</t>
         </is>
       </c>
     </row>
-    <row r="491">
-      <c r="D491" s="1" t="inlineStr">
+    <row r="492">
+      <c r="D492" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="E492" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: quy tắc theo tỷ lệ điểm của nhóm từ 65% là quy tắc duy nhất.</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="E493" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: quy tắc theo tỷ lệ điểm của nhóm từ 65% là quy tắc duy nhất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="E494" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: quy tắc theo tỷ lệ điểm của nhóm từ 65%; (a) nhóm có tỷ lệ điểm 70% (cùng M) (60/100, 80/100); (b) nguồn 50/100, 70/100; S = 60, 70, 80</t>
         </is>
       </c>
     </row>
-    <row r="494">
-      <c r="D494" s="1" t="inlineStr">
+    <row r="495">
+      <c r="D495" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="495">
-      <c r="E495" s="2" t="inlineStr">
+    <row r="496">
+      <c r="E496" s="2" t="inlineStr">
         <is>
           <t>・Chạy nút xanh rồi nút cam cho từng nguồn.</t>
         </is>
       </c>
     </row>
-    <row r="496">
-      <c r="D496" s="1" t="inlineStr">
+    <row r="497">
+      <c r="D497" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="E497" s="2" t="inlineStr">
-        <is>
-          <t>(a) `R=140/200×100=70%` → khớp; `T=70`: 60 Đỏ; 70 Không đỏ; 80 Không đỏ.</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="E498" s="2" t="inlineStr">
         <is>
+          <t>(a) `R=140/200×100=70%` → khớp; `T=70`: 60 Đỏ; 70 Không đỏ; 80 Không đỏ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="E499" s="2" t="inlineStr">
+        <is>
           <t>(b) `R=120/200×100=60%` → không khớp → cả ba Không áp dụng.</t>
         </is>
       </c>
     </row>
-    <row r="499">
-      <c r="D499" s="1" t="inlineStr">
+    <row r="500">
+      <c r="D500" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="E500" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Tỷ lệ nhóm có cần xử lý riêng khi các lớp khác điểm tối đa không?” (Q31); đặc tả v2 (R18) mục 5.3 “Tỷ lệ nhóm” (ví dụ 60/100 và 80/100); Figma MW “màn Điều kiện áp dụng – điều kiện tỷ lệ điểm của nhóm” (58:9164) (UI 03B, 65 % 以上)</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="E501" s="2" t="inlineStr">
         <is>
+          <t>・Nguồn: Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Tỷ lệ nhóm có cần xử lý riêng khi các lớp khác điểm tối đa không?” (Q31); đặc tả v2 (R18) mục 5.3 “Tỷ lệ nhóm” (ví dụ 60/100 và 80/100); Figma MW “màn Điều kiện áp dụng – điều kiện tỷ lệ điểm của nhóm” (58:9164) (UI 03B, 65 % 以上)</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="E502" s="2" t="inlineStr">
+        <is>
           <t>・Bằng chứng cần chụp: Ảnh nguồn, kết quả.</t>
         </is>
       </c>
     </row>
-    <row r="502">
-      <c r="D502" s="1" t="inlineStr">
+    <row r="503">
+      <c r="D503" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="503">
-      <c r="E503" s="2" t="n"/>
-    </row>
     <row r="504">
-      <c r="D504" s="1" t="inlineStr">
+      <c r="E504" s="2" t="n"/>
+    </row>
+    <row r="505">
+      <c r="D505" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="508">
-      <c r="C508" s="1" t="inlineStr">
+    <row r="509">
+      <c r="C509" s="1" t="inlineStr">
         <is>
           <t>25. TC-RS-CALC-025 — Tỷ lệ nhóm 64.99% (hiển thị 65.0) không khớp ≥ 65%</t>
         </is>
       </c>
     </row>
-    <row r="509">
-      <c r="D509" s="3" t="inlineStr">
+    <row r="510">
+      <c r="D510" s="3" t="inlineStr">
         <is>
           <t>Priority: TBD ｜ Status: TBD ｜ Requirement ID: tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14)</t>
         </is>
       </c>
     </row>
-    <row r="510">
-      <c r="D510" s="1" t="inlineStr">
+    <row r="511">
+      <c r="D511" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="E511" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: quy tắc theo tỷ lệ điểm của nhóm từ 65%; mục thập phân.</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="E512" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: quy tắc theo tỷ lệ điểm của nhóm từ 65%; mục thập phân.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="E513" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: quy tắc theo tỷ lệ điểm của nhóm từ 65%; (a) Nguồn 64.98/100 và 65.00/100 → `R=64.99%`; (b) 65/100 và 65/100 → `R=65%`; S = 60</t>
         </is>
       </c>
     </row>
-    <row r="513">
-      <c r="D513" s="1" t="inlineStr">
+    <row r="514">
+      <c r="D514" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="514">
-      <c r="E514" s="2" t="inlineStr">
+    <row r="515">
+      <c r="E515" s="2" t="inlineStr">
         <is>
           <t>・Chạy nút xanh rồi nút cam cho từng nguồn.</t>
         </is>
       </c>
     </row>
-    <row r="515">
-      <c r="D515" s="1" t="inlineStr">
+    <row r="516">
+      <c r="D516" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="E516" s="2" t="inlineStr">
-        <is>
-          <t>(a) Kỳ vọng theo đặc tả v2: không khớp → Không áp dụng. Nếu nguồn chỉ cung cấp giá trị đã làm tròn: ghi nhận khoảng trống, không kết luận PASS/FAIL (TBD).</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="E517" s="2" t="inlineStr">
         <is>
+          <t>(a) Kỳ vọng theo đặc tả v2: không khớp → Không áp dụng. Nếu nguồn chỉ cung cấp giá trị đã làm tròn: ghi nhận khoảng trống, không kết luận PASS/FAIL (TBD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="E518" s="2" t="inlineStr">
+        <is>
           <t>(b) Khớp → S=60 Đỏ.</t>
         </is>
       </c>
     </row>
-    <row r="518">
-      <c r="D518" s="1" t="inlineStr">
+    <row r="519">
+      <c r="D519" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="E519" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 5.3 “Tỷ lệ nhóm” (Độ chính xác: giữ yêu cầu dùng `R` trước làm tròn; nguồn có thể chưa đủ độ chính xác)</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="E520" s="2" t="inlineStr">
         <is>
+          <t>・Nguồn: đặc tả v2 (R18) mục 5.3 “Tỷ lệ nhóm” (Độ chính xác: giữ yêu cầu dùng `R` trước làm tròn; nguồn có thể chưa đủ độ chính xác)</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="E521" s="2" t="inlineStr">
+        <is>
           <t>・Bằng chứng cần chụp: Ảnh nguồn (giá trị thô và hiển thị), kết quả.</t>
         </is>
       </c>
     </row>
-    <row r="521">
-      <c r="D521" s="1" t="inlineStr">
+    <row r="522">
+      <c r="D522" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="522">
-      <c r="E522" s="2" t="n"/>
-    </row>
     <row r="523">
-      <c r="D523" s="1" t="inlineStr">
+      <c r="E523" s="2" t="n"/>
+    </row>
+    <row r="524">
+      <c r="D524" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="527">
-      <c r="C527" s="1" t="inlineStr">
+    <row r="528">
+      <c r="C528" s="1" t="inlineStr">
         <is>
           <t>26. TC-RS-CALC-026 — Mẫu số trung bình khi có học sinh bị loại khỏi xếp hạng</t>
         </is>
       </c>
     </row>
-    <row r="528">
-      <c r="D528" s="3" t="inlineStr">
+    <row r="529">
+      <c r="D529" s="3" t="inlineStr">
         <is>
           <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14)</t>
         </is>
       </c>
     </row>
-    <row r="529">
-      <c r="D529" s="1" t="inlineStr">
+    <row r="530">
+      <c r="D530" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="E530" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: nhóm có học sinh bị loại khỏi xếp hạng; công thức `A×0.5`, `&lt;`.</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="E531" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: nhóm có học sinh bị loại khỏi xếp hạng; công thức `A×0.5`, `&lt;`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="E532" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: nhóm có học sinh bị loại khỏi xếp hạng; S = 22</t>
         </is>
       </c>
     </row>
-    <row r="532">
-      <c r="D532" s="1" t="inlineStr">
+    <row r="533">
+      <c r="D533" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="533">
-      <c r="E533" s="2" t="inlineStr">
+    <row r="534">
+      <c r="E534" s="2" t="inlineStr">
         <is>
           <t>・Chạy nút xanh rồi nút cam; ghi `A` đọc được.</t>
         </is>
       </c>
     </row>
-    <row r="534">
-      <c r="D534" s="1" t="inlineStr">
+    <row r="535">
+      <c r="D535" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
-    <row r="535">
-      <c r="E535" s="2" t="inlineStr">
+    <row r="536">
+      <c r="E536" s="2" t="inlineStr">
         <is>
           <t>・`A = (60+40+20)/3 = 40` (mẫu số là số người có điểm của cùng bản) → `T=20` → S=22 Không đỏ. Nếu hệ thống dùng số người thuộc xếp hạng (`A=100/2=50`, `T=25` → Đỏ) là sai.</t>
         </is>
       </c>
     </row>
-    <row r="536">
-      <c r="D536" s="1" t="inlineStr">
+    <row r="537">
+      <c r="D537" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="E537" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” ("Không thay số người có điểm bằng số người thuộc xếp hạng"); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14) ("trung bình dùng số người có điểm cùng bản, không phải số người xếp hạng"); khác biệt đặc tả–code về “Mẫu số trung bình” (SI-07)</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="E538" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh nguồn, kết quả, `A` thực tế.</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” ("Không thay số người có điểm bằng số người thuộc xếp hạng"); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14) ("trung bình dùng số người có điểm cùng bản, không phải số người xếp hạng"); khác biệt đặc tả–code về “Mẫu số trung bình” (SI-07)</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="E539" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh nguồn, kết quả, `A` thực tế.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="E540" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: đặc tả v2 mục 5.5 “Chọn bản nguồn” và tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (cùng tài liệu chia công việc v2 công việc “Hỗ trợ điều kiện và công thức dùng tổng hợp”: "Không thay số người có điểm bằng số người xếp hạng") đã nêu mẫu số là số người có điểm. Việc ánh xạ trường `examinees`/`student_count` của bản nguồn là kiểm tích hợp, không đổi kỳ vọng.</t>
         </is>
       </c>
     </row>
-    <row r="540">
-      <c r="D540" s="1" t="inlineStr">
+    <row r="541">
+      <c r="D541" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="541">
-      <c r="E541" s="2" t="n"/>
-    </row>
     <row r="542">
-      <c r="D542" s="1" t="inlineStr">
+      <c r="E542" s="2" t="n"/>
+    </row>
+    <row r="543">
+      <c r="D543" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="546">
-      <c r="C546" s="1" t="inlineStr">
+    <row r="547">
+      <c r="C547" s="1" t="inlineStr">
         <is>
           <t>27. TC-RS-CALC-027 — Trung bình riêng cho từng đơn vị</t>
         </is>
       </c>
     </row>
-    <row r="547">
-      <c r="D547" s="3" t="inlineStr">
+    <row r="548">
+      <c r="D548" s="3" t="inlineStr">
         <is>
           <t>Priority: TBD ｜ Status: TBD ｜ Requirement ID: đặc tả v2 mục 5.5 “Chọn bản nguồn”</t>
         </is>
       </c>
     </row>
-    <row r="548">
-      <c r="D548" s="1" t="inlineStr">
+    <row r="549">
+      <c r="D549" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="E549" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: mục điểm đơn vị (đơn vị U1 có M riêng 40) có công thức `A×0.5`, `&lt;`.</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="E550" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: mục điểm đơn vị (đơn vị U1 có M riêng 40) có công thức `A×0.5`, `&lt;`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="E551" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: mục điểm đơn vị (đơn vị U1 có M riêng 40); trung bình riêng theo đơn vị (U1=40, U2=70) (U1 `A=40`, U2 `A=70`); S06 U1 = 25, U2 = 30</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="D551" s="1" t="inlineStr">
+    <row r="552">
+      <c r="D552" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="E552" s="2" t="inlineStr">
+    <row r="553">
+      <c r="E553" s="2" t="inlineStr">
         <is>
           <t>・Chạy nút xanh rồi nút cam.</t>
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="D553" s="1" t="inlineStr">
+    <row r="554">
+      <c r="D554" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="E554" s="2" t="inlineStr">
+    <row r="555">
+      <c r="E555" s="2" t="inlineStr">
         <is>
           <t>・Kỳ vọng theo đặc tả v2: U1 `T=20` → 25 Không đỏ; U2 `T=35` → 30 Đỏ. Nguồn trung bình theo đơn vị chưa tích hợp (đặc tả v2 mục 13.1): nếu không tách được thì ghi nhận, không đánh PASS.</t>
         </is>
       </c>
     </row>
-    <row r="555">
-      <c r="D555" s="1" t="inlineStr">
+    <row r="556">
+      <c r="D556" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="E556" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” ("không được bỏ chiều đơn vị"); context điểm đỏ (CTX) khoảng trống tích hợp “Trung bình theo đơn vị” (I07); khác biệt đặc tả–code về “Trung bình cho điểm đơn vị” (SI-08)</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="E557" s="2" t="inlineStr">
         <is>
+          <t>・Nguồn: đặc tả v2 (R18) mục 5.5 “Chọn bản nguồn” ("không được bỏ chiều đơn vị"); context điểm đỏ (CTX) khoảng trống tích hợp “Trung bình theo đơn vị” (I07); khác biệt đặc tả–code về “Trung bình cho điểm đơn vị” (SI-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="E558" s="2" t="inlineStr">
+        <is>
           <t>・Bằng chứng cần chụp: Ảnh nguồn theo đơn vị, kết quả.</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="D558" s="1" t="inlineStr">
+    <row r="559">
+      <c r="D559" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="E559" s="2" t="n"/>
-    </row>
     <row r="560">
-      <c r="D560" s="1" t="inlineStr">
+      <c r="E560" s="2" t="n"/>
+    </row>
+    <row r="561">
+      <c r="D561" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="C564" s="1" t="inlineStr">
+    <row r="565">
+      <c r="C565" s="1" t="inlineStr">
         <is>
           <t>28. TC-RS-CALC-028 — Không sai kết quả do sai số dấu phẩy động</t>
         </is>
       </c>
     </row>
-    <row r="565">
-      <c r="D565" s="3" t="inlineStr">
+    <row r="566">
+      <c r="D566" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giữ chính xác giá trị” (AC-G11)</t>
         </is>
       </c>
     </row>
-    <row r="566">
-      <c r="D566" s="1" t="inlineStr">
+    <row r="567">
+      <c r="D567" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="E567" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: mục số thập phân (M=100); nguồn dummy.</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="E568" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: mục số thập phân (M=100); nguồn dummy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="E569" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: mục số thập phân (M=100); (a) `A=1.1`, công thức `A×3`, S = 3.3; (b) `A=0.1`, công thức `A+0.2`, S = 0.3</t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="D569" s="1" t="inlineStr">
+    <row r="570">
+      <c r="D570" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="570">
-      <c r="E570" s="2" t="inlineStr">
+    <row r="571">
+      <c r="E571" s="2" t="inlineStr">
         <is>
           <t>・Xét với `&lt;` và `≤`.</t>
         </is>
       </c>
     </row>
-    <row r="571">
-      <c r="D571" s="1" t="inlineStr">
+    <row r="572">
+      <c r="D572" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="572">
-      <c r="E572" s="2" t="inlineStr">
-        <is>
-          <t>(a) `T=3.3`: `&lt;` Không đỏ; `≤` Đỏ.</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="E573" s="2" t="inlineStr">
         <is>
+          <t>(a) `T=3.3`: `&lt;` Không đỏ; `≤` Đỏ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="E574" s="2" t="inlineStr">
+        <is>
           <t>(b) `T=0.3`: `&lt;` Không đỏ; `≤` Đỏ.</t>
         </is>
       </c>
     </row>
-    <row r="574">
-      <c r="D574" s="1" t="inlineStr">
+    <row r="575">
+      <c r="D575" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="575">
-      <c r="E575" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 6.8 “Yêu cầu độ chính xác” ("phép so sánh đúng tại `S=T`")</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="E576" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh Trích xuất（tài liệu “Chiến lược kiểm thử” mục 9 “Quy ước thực thi chung”） ô (a), (b) với `&lt;` và với `≤`.</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 6.8 “Yêu cầu độ chính xác” ("phép so sánh đúng tại `S=T`")</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="E577" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh Trích xuất（tài liệu “Chiến lược kiểm thử” mục 9 “Quy ước thực thi chung”） ô (a), (b) với `&lt;` và với `≤`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="E578" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: Số thực nhị phân cho `1.1×3=3.3000000000000003` và `0.1+0.2=0.30000000000000004`; nếu hệ thống so sánh thô thì `&lt;` sẽ Đỏ — sai.</t>
         </is>
       </c>
     </row>
-    <row r="578">
-      <c r="D578" s="1" t="inlineStr">
+    <row r="579">
+      <c r="D579" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="E579" s="2" t="n"/>
-    </row>
     <row r="580">
-      <c r="D580" s="1" t="inlineStr">
+      <c r="E580" s="2" t="n"/>
+    </row>
+    <row r="581">
+      <c r="D581" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="C584" s="1" t="inlineStr">
+    <row r="585">
+      <c r="C585" s="1" t="inlineStr">
         <is>
           <t>29. TC-RS-CALC-029 — Tràn số không tạo kết luận đỏ/không đỏ</t>
         </is>
       </c>
     </row>
-    <row r="585">
-      <c r="D585" s="3" t="inlineStr">
+    <row r="586">
+      <c r="D586" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giữ chính xác giá trị” (AC-G11)</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="D586" s="1" t="inlineStr">
+    <row r="587">
+      <c r="D587" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="587">
-      <c r="E587" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Công thức.</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="E588" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: Công thức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="E589" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: (a) `A × 999999999999999999999` (21 chữ số); `A ÷ 0.000000001`.</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="D589" s="1" t="inlineStr">
+    <row r="590">
+      <c r="D590" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="590">
-      <c r="E590" s="2" t="inlineStr">
-        <is>
-          <t>1. Nhập (a), Lưu.</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="E591" s="2" t="inlineStr">
         <is>
+          <t>1. Nhập (a), Lưu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="E592" s="2" t="inlineStr">
+        <is>
           <t>2. Nhập (b), Lưu, chạy nút cam.</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="D592" s="1" t="inlineStr">
+    <row r="593">
+      <c r="D593" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="593">
-      <c r="E593" s="2" t="inlineStr">
-        <is>
-          <t>1. (a) vượt giới hạn nhập đề xuất (9 chữ số nguyên, 8 chữ số lẻ) → bị từ chối khi lưu, không tự cắt số.</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="E594" s="2" t="inlineStr">
         <is>
+          <t>1. (a) vượt giới hạn nhập đề xuất (9 chữ số nguyên, 8 chữ số lẻ) → bị từ chối khi lưu, không tự cắt số.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="E595" s="2" t="inlineStr">
+        <is>
           <t>2. (b) nằm trong giới hạn nhập nên lưu được; khi chạy, ngưỡng vượt miền số được hỗ trợ → Chưa xét được (đề xuất `reason_code=numeric_overflow`) hoặc lỗi kỹ thuật được báo. Không có ô nào thành Đỏ/Không đỏ từ giá trị tràn.</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="D595" s="1" t="inlineStr">
+    <row r="596">
+      <c r="D596" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="E596" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 6.8 “Yêu cầu độ chính xác” ("tràn số không được tạo kết luận đỏ/không đỏ"; "vượt giới hạn đã công bố thì báo lỗi"); thiết kế DB v2 (RSD-DB) mục 3.4 “`judgment_context`” (tử/mẫu tối đa 256 chữ số — PROPOSED), mục 4.2 “Xử lý phần lẻ và miền lưu trữ” (giới hạn nhập — PROPOSED), mục 4.3 “Trạng thái kết quả” (`numeric_overflow`)</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="E597" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh lỗi hoặc kết quả.</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 6.8 “Yêu cầu độ chính xác” ("tràn số không được tạo kết luận đỏ/không đỏ"; "vượt giới hạn đã công bố thì báo lỗi"); thiết kế DB v2 (RSD-DB) mục 3.4 “`judgment_context`” (tử/mẫu tối đa 256 chữ số — PROPOSED), mục 4.2 “Xử lý phần lẻ và miền lưu trữ” (giới hạn nhập — PROPOSED), mục 4.3 “Trạng thái kết quả” (`numeric_overflow`)</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="E598" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh lỗi hoặc kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="E599" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: Phần CONFIRMED: không tạo kết luận từ giá trị tràn, không âm thầm cắt số. Giới hạn cụ thể là PROPOSED (thiết kế DB v2 mục 4.2 “Xử lý phần lẻ và miền lưu trữ”, giới hạn số chưa chốt — đặc tả v2 mục 13.1); nếu giới hạn cuối khác, chọn lại (b) sao cho lưu được nhưng tràn khi chạy.</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="D599" s="1" t="inlineStr">
+    <row r="600">
+      <c r="D600" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="E600" s="2" t="n"/>
-    </row>
     <row r="601">
-      <c r="D601" s="1" t="inlineStr">
+      <c r="E601" s="2" t="n"/>
+    </row>
+    <row r="602">
+      <c r="D602" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="C605" s="1" t="inlineStr">
+    <row r="606">
+      <c r="C606" s="1" t="inlineStr">
         <is>
           <t>30. TC-RS-CALC-030 — Công thức cho T=0; ô trống vẫn là Không có điểm</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="D606" s="3" t="inlineStr">
+    <row r="607">
+      <c r="D607" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: đặc tả v2 mục 2.3 “Điểm được đưa vào xét”, mục 6.6 “Ngưỡng âm và cảnh báo biên”</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="D607" s="1" t="inlineStr">
+    <row r="608">
+      <c r="D608" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="608">
-      <c r="E608" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Nguồn `A=20`; công thức `A−20`.</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="E609" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: Nguồn `A=20`; công thức `A−20`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="E610" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: học sinh S04 (điểm 0) (0), học sinh S05 (ô trống) (trống)</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="D610" s="1" t="inlineStr">
+    <row r="611">
+      <c r="D611" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="E611" s="2" t="inlineStr">
+    <row r="612">
+      <c r="E612" s="2" t="inlineStr">
         <is>
           <t>・Xét với `&lt;` rồi `≤`.</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="D612" s="1" t="inlineStr">
+    <row r="613">
+      <c r="D613" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="E613" s="2" t="inlineStr">
+    <row r="614">
+      <c r="E614" s="2" t="inlineStr">
         <is>
           <t>・`T=0`. `&lt;`: S04 Không đỏ. `≤`: S04 Đỏ. S05: Không có điểm ở cả hai (không bị coi là 0).</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="D614" s="1" t="inlineStr">
+    <row r="615">
+      <c r="D615" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="E615" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 2.3 “Điểm được đưa vào xét”, mục 6.6 “Ngưỡng âm và cảnh báo biên”; Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Dùng điểm nào để xét, và phân biệt điểm 0 với ô trống thế nào?” (Q3)</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="E616" s="2" t="inlineStr">
         <is>
+          <t>・Nguồn: đặc tả v2 (R18) mục 2.3 “Điểm được đưa vào xét”, mục 6.6 “Ngưỡng âm và cảnh báo biên”; Q&amp;A nghiệp vụ đã xác nhận (QAC) câu “Dùng điểm nào để xét, và phân biệt điểm 0 với ô trống thế nào?” (Q3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="E617" s="2" t="inlineStr">
+        <is>
           <t>・Bằng chứng cần chụp: Ảnh Trích xuất（tài liệu “Chiến lược kiểm thử” mục 9 “Quy ước thực thi chung”） S04, S05 với `&lt;` và với `≤`; ảnh SELECT trạng thái của S05.</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="D617" s="1" t="inlineStr">
+    <row r="618">
+      <c r="D618" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="E618" s="2" t="n"/>
-    </row>
     <row r="619">
-      <c r="D619" s="1" t="inlineStr">
+      <c r="E619" s="2" t="n"/>
+    </row>
+    <row r="620">
+      <c r="D620" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="C623" s="1" t="inlineStr">
+    <row r="624">
+      <c r="C624" s="1" t="inlineStr">
         <is>
           <t>31. TC-RS-CALC-031 — Nguồn không có mẫu số hợp lệ (tổng điểm tối đa 0, số người có điểm 0) → Chưa xét được</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="D624" s="3" t="inlineStr">
+    <row r="625">
+      <c r="D625" s="3" t="inlineStr">
         <is>
           <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14)</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="D625" s="1" t="inlineStr">
+    <row r="626">
+      <c r="D626" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="E626" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: Quy tắc 1: quy tắc theo tỷ lệ điểm của nhóm từ 65% (điều kiện tỷ lệ nhóm). Quy tắc 2 (mục khác): công thức `A×0.5`. Cách tạo dữ liệu: hỏi team dev khi chuẩn bị.</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="E627" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: Quy tắc 1: quy tắc theo tỷ lệ điểm của nhóm từ 65% (điều kiện tỷ lệ nhóm). Quy tắc 2 (mục khác): công thức `A×0.5`. Cách tạo dữ liệu: hỏi team dev khi chuẩn bị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="E628" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: quy tắc theo tỷ lệ điểm của nhóm từ 65%; (a) Bản tổng hợp của nhóm có tổng điểm tối đa = 0; (b) bản tổng hợp tồn tại nhưng không học sinh nào có điểm; S01 = 29</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="D628" s="1" t="inlineStr">
+    <row r="629">
+      <c r="D629" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="E629" s="2" t="inlineStr">
+    <row r="630">
+      <c r="E630" s="2" t="inlineStr">
         <is>
           <t>・Với từng nguồn: chạy nút xanh (nếu cần) rồi nút cam; xem kết quả S01.</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="D630" s="1" t="inlineStr">
+    <row r="631">
+      <c r="D631" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
-      <c r="E631" s="2" t="inlineStr">
-        <is>
-          <t>(a) Điều kiện tỷ lệ nhóm không xác định được → Chưa xét được; không coi `R=0` là không khớp để thành Không áp dụng hay chuyển xuống ưu tiên thấp hơn.</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="E632" s="2" t="inlineStr">
         <is>
-          <t>(b) `A` không xác định được → Chưa xét được; không coi `A=0` (nếu coi 0 thì `T=0`, S01 Không đỏ — sai).</t>
+          <t>(a) Điều kiện tỷ lệ nhóm không xác định được → Chưa xét được; không coi `R=0` là không khớp để thành Không áp dụng hay chuyển xuống ưu tiên thấp hơn.</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="E633" s="2" t="inlineStr">
         <is>
+          <t>(b) `A` không xác định được → Chưa xét được; không coi `A=0` (nếu coi 0 thì `T=0`, S01 Không đỏ — sai).</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="E634" s="2" t="inlineStr">
+        <is>
           <t>・Cả hai: ngừng dấu đỏ cũ; không lấy nguồn khác.</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="D634" s="1" t="inlineStr">
+    <row r="635">
+      <c r="D635" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="E635" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 5.3 “Tỷ lệ nhóm” (Phạm vi vận hành: dữ liệu không hợp lệ theo quy tắc chung, không thay bằng 0), mục 5.5 “Chọn bản nguồn”, mục 8.3 “Không tạo được ngưỡng hợp lệ”; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14) ("số người 0, tổng maximum sai hoặc tập đóng góp không xác định thì chưa xét được"); thiết kế DB v2 (RSD-DB) mục 4.3 “Trạng thái kết quả” (mã nguyên nhân — PROPOSED)</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="E636" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả; SELECT `reason_code` (khi có schema).</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 5.3 “Tỷ lệ nhóm” (Phạm vi vận hành: dữ liệu không hợp lệ theo quy tắc chung, không thay bằng 0), mục 5.5 “Chọn bản nguồn”, mục 8.3 “Không tạo được ngưỡng hợp lệ”; tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14) ("số người 0, tổng maximum sai hoặc tập đóng góp không xác định thì chưa xét được"); thiết kế DB v2 (RSD-DB) mục 4.3 “Trạng thái kết quả” (mã nguyên nhân — PROPOSED)</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="E637" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả; SELECT `reason_code` (khi có schema).</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="E638" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: Mã nguyên nhân cụ thể là PROPOSED. Không tạo được dữ liệu (a)/(b): BLOCKED.</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="D638" s="1" t="inlineStr">
+    <row r="639">
+      <c r="D639" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="E639" s="2" t="n"/>
-    </row>
     <row r="640">
-      <c r="D640" s="1" t="inlineStr">
+      <c r="E640" s="2" t="n"/>
+    </row>
+    <row r="641">
+      <c r="D641" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="C644" s="1" t="inlineStr">
+    <row r="645">
+      <c r="C645" s="1" t="inlineStr">
         <is>
           <t>32. TC-RS-CALC-032 — Tỷ lệ nhóm: tử số và mẫu số lấy cùng tập đóng góp</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="D645" s="3" t="inlineStr">
+    <row r="646">
+      <c r="D646" s="3" t="inlineStr">
         <is>
           <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14)</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="D646" s="1" t="inlineStr">
+    <row r="647">
+      <c r="D647" s="1" t="inlineStr">
         <is>
           <t>前提条件（Điều kiện trước）</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="E647" s="2" t="inlineStr">
-        <is>
-          <t>・Điều kiện: quy tắc theo tỷ lệ điểm của nhóm từ 65% là quy tắc duy nhất. Nhóm tham chiếu có 3 học sinh: 60/100, 80/100 và một học sinh chưa có điểm (M=100).</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="E648" s="2" t="inlineStr">
         <is>
+          <t>・Điều kiện: quy tắc theo tỷ lệ điểm của nhóm từ 65% là quy tắc duy nhất. Nhóm tham chiếu có 3 học sinh: 60/100, 80/100 và một học sinh chưa có điểm (M=100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="E649" s="2" t="inlineStr">
+        <is>
           <t>・Dữ liệu test: quy tắc theo tỷ lệ điểm của nhóm từ 65%; S = 60</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="D649" s="1" t="inlineStr">
+    <row r="650">
+      <c r="D650" s="1" t="inlineStr">
         <is>
           <t>操作（Thao tác）</t>
-        </is>
-      </c>
-    </row>
-    <row r="650">
-      <c r="E650" s="2" t="inlineStr">
-        <is>
-          <t>1. Chạy nút xanh; ghi tổng điểm và tổng điểm tối đa hiển thị ở kết quả tổng hợp.</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="E651" s="2" t="inlineStr">
         <is>
+          <t>1. Chạy nút xanh; ghi tổng điểm và tổng điểm tối đa hiển thị ở kết quả tổng hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="E652" s="2" t="inlineStr">
+        <is>
           <t>2. Chạy nút cam; xem kết quả S=60.</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="D652" s="1" t="inlineStr">
+    <row r="653">
+      <c r="D653" s="1" t="inlineStr">
         <is>
           <t>期待結果（Kết quả mong đợi）</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="E653" s="2" t="inlineStr">
-        <is>
-          <t>1. Tổng điểm và tổng điểm tối đa lấy cùng tập học sinh có điểm theo cấu hình tổng hợp.</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="E654" s="2" t="inlineStr">
         <is>
+          <t>1. Tổng điểm và tổng điểm tối đa lấy cùng tập học sinh có điểm theo cấu hình tổng hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="E655" s="2" t="inlineStr">
+        <is>
           <t>2. Với cấu hình tổng hợp không tính học sinh chưa có điểm: `R=140/200×100=70%` → khớp `≥65%` → `T=70` → S=60 Đỏ. Ghép tổng điểm của 2 người với tổng tối đa của 3 người (`140/300=46.7%` → Không áp dụng) là sai.</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="D655" s="1" t="inlineStr">
+    <row r="656">
+      <c r="D656" s="1" t="inlineStr">
         <is>
           <t>補足（Bổ sung）</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
-      <c r="E656" s="2" t="inlineStr">
-        <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 5.3 “Tỷ lệ nhóm” (công thức `R`), mục 5.5 “Chọn bản nguồn” ("tử số và mẫu số phải tương ứng cùng tập đóng góp theo cấu hình tổng hợp"); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14) ("tử/mẫu tỷ lệ dùng cùng tập đóng góp")</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="E657" s="2" t="inlineStr">
         <is>
-          <t>・Bằng chứng cần chụp: Ảnh kết quả tổng hợp (tổng điểm, tổng tối đa, số người); ảnh kết quả xét.</t>
+          <t>・Nguồn: đặc tả v2 (R18) mục 5.3 “Tỷ lệ nhóm” (công thức `R`), mục 5.5 “Chọn bản nguồn” ("tử số và mẫu số phải tương ứng cùng tập đóng góp theo cấu hình tổng hợp"); tiêu chí nghiệm thu v2 (RSD-AC) tiêu chí nghiệm thu “Giá trị thô từ cùng tập dữ liệu” (AC-G14) ("tử/mẫu tỷ lệ dùng cùng tập đóng góp")</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="E658" s="2" t="inlineStr">
         <is>
+          <t>・Bằng chứng cần chụp: Ảnh kết quả tổng hợp (tổng điểm, tổng tối đa, số người); ảnh kết quả xét.</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="E659" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: Nếu cấu hình tổng hợp hiện có đưa học sinh chưa có điểm vào cả tử và mẫu theo cùng quy tắc thì ghi nhận giá trị thực tế; điều kiện kiểm là tử/mẫu cùng tập, không phải con số 70% cố định.</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="D659" s="1" t="inlineStr">
+    <row r="660">
+      <c r="D660" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="E660" s="2" t="n"/>
-    </row>
     <row r="661">
-      <c r="D661" s="1" t="inlineStr">
+      <c r="E661" s="2" t="n"/>
+    </row>
+    <row r="662">
+      <c r="D662" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
@@ -17258,7 +17394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:F515"/>
+  <dimension ref="C2:F537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.13" customWidth="1" min="1" max="1"/>
@@ -17272,7 +17408,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>25 test case TC-RS-UI-…, nguồn: 05-ui-test-cases.vi.md. Điền 結果（Kết quả） và dán 証跡（Bằng chứng） khi chạy.</t>
+          <t>26 test case TC-RS-UI-…, nguồn: 05-ui-test-cases.vi.md. Điền 結果（Kết quả） và dán 証跡（Bằng chứng） khi chạy.</t>
         </is>
       </c>
     </row>
@@ -20137,14 +20273,14 @@
     <row r="498">
       <c r="C498" s="1" t="inlineStr">
         <is>
-          <t>25. TC-RS-UI-025 — Loại ngưỡng/điều kiện chưa thuộc phạm vi phát hành không hiện như đang hoạt động</t>
+          <t>25. TC-RS-UI-026 — Bộ chọn hiệu ứng đỏ của điểm thường và điểm đơn vị hiển thị độc lập</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="D499" s="3" t="inlineStr">
         <is>
-          <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Phạm vi từng đợt” (AC-G40)</t>
+          <t>Priority: Cao ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Cấu hình công khai và ẩn điểm” (AC-G32)</t>
         </is>
       </c>
     </row>
@@ -20158,14 +20294,14 @@
     <row r="501">
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>・Điều kiện: Có danh sách phạm vi phát hành (đặc tả v2 mục 1.4, mục 13.1).</t>
+          <t>・Điều kiện: Có một cấu hình công khai chứa cả mục điểm thường và mục điểm đơn vị; tài khoản có quyền sửa cấu hình công khai.</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>・Dữ liệu test: —</t>
+          <t>・Dữ liệu test: mục thường và mục đơn vị cùng có kết quả đỏ; lựa chọn hiển thị khác nhau cho hai loại.</t>
         </is>
       </c>
     </row>
@@ -20179,21 +20315,21 @@
     <row r="504">
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>1. Mở màn Điều kiện áp dụng（適用条件設定）, xem các loại điều kiện.</t>
+          <t>1. Mở màn hình cấu hình công khai và đến khu vực hiển thị điểm đỏ.</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>2. Mở màn Ngưỡng đỏ（赤点の基準）, xem các loại ngưỡng.</t>
+          <t>2. Kiểm tra panel điểm thường và panel điểm đơn vị.</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>3. Với loại không có trong danh sách phát hành (ví dụ Công thức（計算式）, điều kiện Trung bình（平均点））: nếu chọn được thì thử Lưu.</t>
+          <t>3. Chọn hiệu ứng khác nhau cho hai panel, lưu, đóng và mở lại.</t>
         </is>
       </c>
     </row>
@@ -20207,50 +20343,179 @@
     <row r="508">
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>・Loại ngoài phạm vi không hiện như lựa chọn dùng được; không lưu được cấu hình dùng loại đó.</t>
+          <t>1. Cả hai panel đều hiển thị bộ chọn tương ứng; panel điểm đơn vị không bị nền hoặc lớp khác che.</t>
         </is>
       </c>
     </row>
     <row r="509">
-      <c r="D509" s="1" t="inlineStr">
-        <is>
-          <t>補足（Bổ sung）</t>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>2. Có thể thao tác hai bộ chọn độc lập.</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>・Nguồn: đặc tả v2 (R18) mục 1.4 “Ranh giới giữa thiết kế đầy đủ và phạm vi triển khai”</t>
+          <t>3. Sau khi mở lại, mỗi panel giữ đúng lựa chọn của mình; lựa chọn điểm thường không ghi đè lựa chọn điểm đơn vị và ngược lại.</t>
         </is>
       </c>
     </row>
     <row r="511">
-      <c r="E511" s="2" t="inlineStr">
-        <is>
-          <t>・Bằng chứng cần chụp: Ảnh màn.</t>
+      <c r="D511" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="E512" s="2" t="inlineStr">
         <is>
+          <t>・Nguồn: xác nhận thiết kế ngày 30/09 (Q38: hai phía thường/đơn vị phải hiển thị và kiểm được lựa chọn độc lập); đặc tả v2 (R18) mục 10.1; checklist cập nhật Figma mục 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh trước khi thao tác; ảnh từng panel sau khi chọn; ảnh mở lại sau khi lưu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="D514" s="1" t="inlineStr">
+        <is>
+          <t>結果（Kết quả）</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="E515" s="2" t="n"/>
+    </row>
+    <row r="516">
+      <c r="D516" s="1" t="inlineStr">
+        <is>
+          <t>証跡（Bằng chứng）</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="C520" s="1" t="inlineStr">
+        <is>
+          <t>26. TC-RS-UI-025 — Loại ngưỡng/điều kiện chưa thuộc phạm vi phát hành không hiện như đang hoạt động</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="D521" s="3" t="inlineStr">
+        <is>
+          <t>Priority: TBD ｜ Status: CONFIRMED ｜ Requirement ID: tiêu chí nghiệm thu “Phạm vi từng đợt” (AC-G40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="D522" s="1" t="inlineStr">
+        <is>
+          <t>前提条件（Điều kiện trước）</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>・Điều kiện: Có danh sách phạm vi phát hành (đặc tả v2 mục 1.4, mục 13.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>・Dữ liệu test: —</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="D525" s="1" t="inlineStr">
+        <is>
+          <t>操作（Thao tác）</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>1. Mở màn Điều kiện áp dụng（適用条件設定）, xem các loại điều kiện.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>2. Mở màn Ngưỡng đỏ（赤点の基準）, xem các loại ngưỡng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>3. Với loại không có trong danh sách phát hành (ví dụ Công thức（計算式）, điều kiện Trung bình（平均点））: nếu chọn được thì thử Lưu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="D529" s="1" t="inlineStr">
+        <is>
+          <t>期待結果（Kết quả mong đợi）</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>・Loại ngoài phạm vi không hiện như lựa chọn dùng được; không lưu được cấu hình dùng loại đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="D531" s="1" t="inlineStr">
+        <is>
+          <t>補足（Bổ sung）</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>・Nguồn: đặc tả v2 (R18) mục 1.4 “Ranh giới giữa thiết kế đầy đủ và phạm vi triển khai”</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>・Bằng chứng cần chụp: Ảnh màn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="E534" s="2" t="inlineStr">
+        <is>
           <t>・Ghi chú: BLOCKED cho tới khi có danh sách phạm vi phát hành (đặc tả v2 mục 13.1). Các case của loại không được chọn: SKIPPED (tài liệu “Chiến lược kiểm thử” mục 1 “Phạm vi”).</t>
         </is>
       </c>
     </row>
-    <row r="513">
-      <c r="D513" s="1" t="inlineStr">
+    <row r="535">
+      <c r="D535" s="1" t="inlineStr">
         <is>
           <t>結果（Kết quả）</t>
         </is>
       </c>
     </row>
-    <row r="514">
-      <c r="E514" s="2" t="n"/>
-    </row>
-    <row r="515">
-      <c r="D515" s="1" t="inlineStr">
+    <row r="536">
+      <c r="E536" s="2" t="n"/>
+    </row>
+    <row r="537">
+      <c r="D537" s="1" t="inlineStr">
         <is>
           <t>証跡（Bằng chứng）</t>
         </is>
@@ -23047,7 +23312,7 @@
     <row r="59">
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1. Sáu trạng thái phân biệt được, không gộp Chưa xét được với Không áp dụng hay Không đỏ. Ánh xạ đề xuất (PROPOSED): Chưa từng xét = không có dòng, hoặc dòng điều khiển khởi tạo có `judgment_status`/`is_red` NULL (đã đặt chỗ lần đầu nhưng chưa hoàn tất) — cả hai không được đọc thành Không đỏ hay Đỏ; Đỏ = 1, `is_red=1`; Không đỏ = 1, `is_red=0`; Chưa xét được = 2, `is_red` NULL, có `reason_code`; Không áp dụng = 3, `no_applicable_rule`; Không có điểm = 4, `no_score`. `red_score_setting_id` (PROPOSED): trạng thái 1 bắt buộc có; trạng thái 2 chỉ có khi đã chọn được quy tắc (ví dụ case “Chạy lại không tạo được ngưỡng hợp lệ → Chưa xét được, ngừng kết quả cũ, giữ điểm”: có; case “Ưu tiên 1 khớp nhưng thiếu dữ liệu → Chưa xét được, không chuyển xuống ưu tiên 2”, điều kiện không xác định được: NULL); trạng thái 3 và 4: NULL.</t>
+          <t>1. Sáu trạng thái phân biệt được, không gộp Chưa xét được với Không áp dụng hay Không đỏ. Việc dùng cột, mã số, `reason_code` hoặc `red_score_setting_id` cụ thể là phần thiết kế DB cần đối chiếu khi schema được chốt; không dùng mapping đề xuất làm business oracle. Bất kể cách lưu, kết quả quan sát phải phân biệt rõ sáu trạng thái và trạng thái Đang chờ chạy lại.</t>
         </is>
       </c>
     </row>
@@ -24030,7 +24295,7 @@
     <row r="228">
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>1. Có phạm vi trường/năm, cột audit và comment theo quy tắc schema hiện hành. Đối chiếu thêm với thiết kế (PROPOSED): InnoDB, `utf8mb4`/`utf8mb4_general_ci`, không khai báo foreign key, có `idx_red_score_settings_01`, `uk_red_score_results_01`, `idx_red_score_results_01`, `active` mặc định 0; `red_score_results` có thêm `cell_generation`, `write_version` (mặc định 0), `judged_version`, `rule_revision` (cho phép NULL); bảng/cột cũ (`red_score`, `changed_red_score`) không đổi.</t>
+          <t>1. Có phạm vi trường/năm, cột audit và comment theo quy tắc schema hiện hành. Đối chiếu thêm với thiết kế (PROPOSED): InnoDB, `utf8mb4`/`utf8mb4_general_ci`, không khai báo foreign key, có `idx_red_score_settings_01`, `uk_red_score_results_01`, `idx_red_score_results_01`, `setting_status` mặc định 0 và phân biệt rõ trạng thái 0/1/2; `red_score_results` có thêm `cell_generation`, `write_version` (mặc định 0), `judged_version`, `rule_revision` (cho phép NULL); bảng/cột cũ (`red_score`, `changed_red_score`) không đổi.</t>
         </is>
       </c>
     </row>

--- a/features/RC-001-red-score/docs/v2/test-spec/test-case-report.xlsx
+++ b/features/RC-001-red-score/docs/v2/test-spec/test-case-report.xlsx
@@ -18797,7 +18797,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>v2 working tree based on fd0bc963c075cb4a8d6846bf210d1761344a1355; exact source hashes in manifest; pinned link pending commit</t>
+          <t>v2 working tree based on ffa72dc90f27fd128d62c5c092a5d3e8447a466a; exact source hashes in manifest; pinned link pending commit</t>
         </is>
       </c>
     </row>
@@ -54965,7 +54965,7 @@
   </sheetData>
   <autoFilter ref="A1:M570"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="0" sqref="D2:D570" showDropDown="0" showErrorMessage="1" errorStyle="stop">
+    <dataValidation showErrorMessage="1" type="list" allowBlank="0" sqref="D2:D570" errorStyle="stop" showDropDown="0">
       <formula1>"NOT RUN,PASS,FAIL,BLOCKED,SKIPPED"</formula1>
     </dataValidation>
   </dataValidations>
